--- a/dados/Registro_Alteracoes_Amazon_Ads_Winnet.xlsx
+++ b/dados/Registro_Alteracoes_Amazon_Ads_Winnet.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="229">
   <si>
     <t>REGISTRO DE ALTERAÇÕES — AMAZON ADS | WINNET METAIS</t>
   </si>
@@ -692,6 +692,21 @@
   </si>
   <si>
     <t>INCLUIR EM PROMOÇÃO</t>
+  </si>
+  <si>
+    <t>EC-002</t>
+  </si>
+  <si>
+    <t>Monitoramento de 31/08 encontrou a campanha ATIVADA com impressões até 30/08, contrariando a O4-006 registrada como executada em 25/08. Gasto zero na janela.</t>
+  </si>
+  <si>
+    <t>Gerenciador 31/08 + ciclos/Monitoramento-31-08.md</t>
+  </si>
+  <si>
+    <t>Não é decisão nova — execução tardia da O4-006. Na linha O4-006, adicionar na coluna de observação: "pausa não vigorou no console; ver EC-002".</t>
+  </si>
+  <si>
+    <t>"pausa não vigorou no console; ver EC-002".</t>
   </si>
 </sst>
 </file>
@@ -1041,6 +1056,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1062,7 +1078,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1400,82 +1415,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
-      <c r="V1" s="43"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="44"/>
     </row>
     <row r="2" spans="1:22" ht="30" customHeight="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="44"/>
-      <c r="S2" s="44"/>
-      <c r="T2" s="44"/>
-      <c r="U2" s="44"/>
-      <c r="V2" s="44"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
+      <c r="V2" s="45"/>
     </row>
     <row r="3" spans="1:22" ht="27.95" customHeight="1">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="45"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="46"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="46"/>
+      <c r="T3" s="46"/>
+      <c r="U3" s="46"/>
+      <c r="V3" s="46"/>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1" t="s">
@@ -1496,36 +1511,36 @@
       <c r="F5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="46" t="s">
+      <c r="H5" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="46"/>
-      <c r="P5" s="46"/>
-      <c r="Q5" s="46"/>
-      <c r="R5" s="46"/>
-      <c r="S5" s="46"/>
-      <c r="T5" s="46"/>
-      <c r="U5" s="46"/>
-      <c r="V5" s="46"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
+      <c r="Q5" s="47"/>
+      <c r="R5" s="47"/>
+      <c r="S5" s="47"/>
+      <c r="T5" s="47"/>
+      <c r="U5" s="47"/>
+      <c r="V5" s="47"/>
     </row>
     <row r="6" spans="1:22" ht="26.1" customHeight="1">
       <c r="A6" s="2">
         <f>COUNTIF(A11:A210,"&lt;&gt;")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" s="3">
         <f>COUNTIF(N11:N210,"SIM")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3">
         <f>COUNTIF(O11:O210,"SIM")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="3">
         <f>COUNTIF(P11:P210,"BLOQUEADA*")</f>
@@ -1533,53 +1548,53 @@
       </c>
       <c r="E6" s="3">
         <f>COUNTIF(P11:P210,"EXECUTADA - EM MATURAÇÃO")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" s="4">
         <f>COUNTIF(P11:P210,"EXECUTADA - AVALIADA")</f>
         <v>0</v>
       </c>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="46"/>
-      <c r="O6" s="46"/>
-      <c r="P6" s="46"/>
-      <c r="Q6" s="46"/>
-      <c r="R6" s="46"/>
-      <c r="S6" s="46"/>
-      <c r="T6" s="46"/>
-      <c r="U6" s="46"/>
-      <c r="V6" s="46"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="47"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="47"/>
+      <c r="T6" s="47"/>
+      <c r="U6" s="47"/>
+      <c r="V6" s="47"/>
     </row>
     <row r="8" spans="1:22" ht="21.95" customHeight="1">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47"/>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="47"/>
-      <c r="N8" s="47"/>
-      <c r="O8" s="47"/>
-      <c r="P8" s="47"/>
-      <c r="Q8" s="47"/>
-      <c r="R8" s="47"/>
-      <c r="S8" s="47"/>
-      <c r="T8" s="47"/>
-      <c r="U8" s="47"/>
-      <c r="V8" s="47"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="48"/>
+      <c r="R8" s="48"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="48"/>
+      <c r="V8" s="48"/>
     </row>
     <row r="10" spans="1:22" ht="38.1" customHeight="1">
       <c r="A10" s="5" t="s">
@@ -1702,7 +1717,7 @@
       </c>
       <c r="R11" s="17">
         <f t="shared" ref="R11:R42" ca="1" si="1">IF(E11="","",TODAY()-E11)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S11" s="22"/>
       <c r="T11" s="22"/>
@@ -1764,7 +1779,7 @@
       </c>
       <c r="R12" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S12" s="23"/>
       <c r="T12" s="23"/>
@@ -1824,7 +1839,7 @@
       </c>
       <c r="R13" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S13" s="23"/>
       <c r="T13" s="42"/>
@@ -1888,7 +1903,7 @@
       </c>
       <c r="R14" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S14" s="23"/>
       <c r="T14" s="23"/>
@@ -1954,7 +1969,7 @@
       </c>
       <c r="R15" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
@@ -2020,7 +2035,7 @@
       </c>
       <c r="R16" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S16" s="23"/>
       <c r="T16" s="23"/>
@@ -2086,7 +2101,7 @@
       </c>
       <c r="R17" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S17" s="23"/>
       <c r="T17" s="23"/>
@@ -2150,7 +2165,7 @@
       </c>
       <c r="R18" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S18" s="23"/>
       <c r="T18" s="23"/>
@@ -2216,7 +2231,7 @@
       </c>
       <c r="R19" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S19" s="23"/>
       <c r="T19" s="23"/>
@@ -2282,12 +2297,14 @@
       </c>
       <c r="R20" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S20" s="23"/>
       <c r="T20" s="23"/>
       <c r="U20" s="7"/>
-      <c r="V20" s="28"/>
+      <c r="V20" s="28" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="21" spans="1:22" ht="42.75">
       <c r="A21" s="40" t="s">
@@ -2344,7 +2361,7 @@
       </c>
       <c r="R21" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S21" s="23"/>
       <c r="T21" s="23"/>
@@ -2406,7 +2423,7 @@
       </c>
       <c r="R22" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S22" s="23"/>
       <c r="T22" s="23"/>
@@ -2468,7 +2485,7 @@
       </c>
       <c r="R23" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S23" s="23"/>
       <c r="T23" s="23"/>
@@ -2530,7 +2547,7 @@
       </c>
       <c r="R24" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S24" s="23"/>
       <c r="T24" s="23"/>
@@ -2596,7 +2613,7 @@
       </c>
       <c r="R25" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S25" s="23"/>
       <c r="T25" s="23"/>
@@ -2658,7 +2675,7 @@
       </c>
       <c r="R26" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S26" s="23"/>
       <c r="T26" s="23"/>
@@ -2722,7 +2739,7 @@
       </c>
       <c r="R27" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S27" s="23"/>
       <c r="T27" s="23"/>
@@ -2788,7 +2805,7 @@
       </c>
       <c r="R28" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S28" s="23"/>
       <c r="T28" s="23"/>
@@ -2854,7 +2871,7 @@
       </c>
       <c r="R29" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S29" s="23"/>
       <c r="T29" s="23"/>
@@ -2872,13 +2889,13 @@
       <c r="B30" t="s">
         <v>215</v>
       </c>
-      <c r="C30" s="50">
+      <c r="C30" s="43">
         <v>46262</v>
       </c>
-      <c r="D30" s="50">
+      <c r="D30" s="43">
         <v>46262</v>
       </c>
-      <c r="E30" s="50">
+      <c r="E30" s="43">
         <v>46262</v>
       </c>
       <c r="F30" t="s">
@@ -2920,11 +2937,11 @@
       </c>
       <c r="R30" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S30" s="23"/>
       <c r="T30" s="23"/>
-      <c r="U30" s="50">
+      <c r="U30" s="43">
         <v>46273</v>
       </c>
       <c r="V30" t="s">
@@ -2932,34 +2949,70 @@
       </c>
     </row>
     <row r="31" spans="1:22">
-      <c r="A31" s="10"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="40"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
-      <c r="O31" s="11"/>
-      <c r="P31" s="11"/>
-      <c r="Q31" s="18" t="str">
+      <c r="A31" t="s">
+        <v>224</v>
+      </c>
+      <c r="B31" t="s">
+        <v>215</v>
+      </c>
+      <c r="C31" s="43">
+        <v>46265</v>
+      </c>
+      <c r="D31" s="43">
+        <v>46265</v>
+      </c>
+      <c r="E31" s="43">
+        <v>46265</v>
+      </c>
+      <c r="F31" t="s">
+        <v>104</v>
+      </c>
+      <c r="G31" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I31" t="s">
+        <v>142</v>
+      </c>
+      <c r="J31" t="s">
+        <v>143</v>
+      </c>
+      <c r="K31" t="s">
+        <v>225</v>
+      </c>
+      <c r="L31" t="s">
+        <v>226</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N31" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="O31" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="P31" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q31" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="R31" s="19" t="str">
+        <v>46266</v>
+      </c>
+      <c r="R31" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S31" s="23"/>
       <c r="T31" s="23"/>
-      <c r="U31" s="7"/>
-      <c r="V31" s="28"/>
+      <c r="U31" s="43">
+        <v>46273</v>
+      </c>
+      <c r="V31" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="32" spans="1:22">
       <c r="A32" s="10"/>
@@ -8419,16 +8472,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="32" t="s">
@@ -8547,16 +8600,16 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="15">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="50"/>
     </row>
     <row r="19" spans="1:8" ht="29.25">
       <c r="A19" s="33" t="s">

--- a/dados/Registro_Alteracoes_Amazon_Ads_Winnet.xlsx
+++ b/dados/Registro_Alteracoes_Amazon_Ads_Winnet.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="243">
   <si>
     <t>REGISTRO DE ALTERAÇÕES — AMAZON ADS | WINNET METAIS</t>
   </si>
@@ -707,13 +707,65 @@
   </si>
   <si>
     <t>"pausa não vigorou no console; ver EC-002".</t>
+  </si>
+  <si>
+    <t>EC-003</t>
+  </si>
+  <si>
+    <t>EC-004</t>
+  </si>
+  <si>
+    <t>Promoção ofertas 9/9</t>
+  </si>
+  <si>
+    <t>Promoção ofertas 9/10</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">11 </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>SKUs: PXM 173,01 (−15%) · L2460-CP 285,33 (−15%) · L2025-T 112,97 (−15%) · L2030 101,34 (−15%) · PXP 151,10 (−10%) · L3085-B 578,02 · L3070-B 489,46 · EGC 607,16 · L2460-AML 261,15 · PG2460 223,88 · Q4070-A 947,85 (todos −10%)</t>
+    </r>
+  </si>
+  <si>
+    <t>CRIAR OFERTAS — Melhor Oferta, Clientes Prime, taxa R$ 0,00</t>
+  </si>
+  <si>
+    <t>Sem oferta</t>
+  </si>
+  <si>
+    <t>11 Melhores Ofertas programadas 07–13/09</t>
+  </si>
+  <si>
+    <t>Evento 9.9; descontos no teto da margem (medida p/ quem vendeu, Simulador piso 15% p/ o resto), cap de prudência 15%</t>
+  </si>
+  <si>
+    <t>docs/PLANO_9-9.md + Simulador Mestra v4.3.2 + Registro_Vendas</t>
+  </si>
+  <si>
+    <t>Q3060-A 499,25 (−14%) · P3060 439,82 (−14%) · P3070 554,56 (−10%) · P3050 420,90 (−10%) · P4080 963,15 (−10%)</t>
+  </si>
+  <si>
+    <t>CRIAR OFERTAS — Relâmpago, Clientes Prime, taxa R$ 0,00; dia exato definido pela Amazon (~1 semana antes)</t>
+  </si>
+  <si>
+    <t>5 Ofertas relãmpago programadas 07-13/09</t>
+  </si>
+  <si>
+    <t>Destrave de conversão (P3070 e P3050 com tráfego sem venda) + tickets do Núcleo A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -786,6 +838,12 @@
     <font>
       <u/>
       <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFF0F6FC"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -932,7 +990,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1078,6 +1136,7 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1532,15 +1591,15 @@
     <row r="6" spans="1:22" ht="26.1" customHeight="1">
       <c r="A6" s="2">
         <f>COUNTIF(A11:A210,"&lt;&gt;")</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B6" s="3">
         <f>COUNTIF(N11:N210,"SIM")</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3">
         <f>COUNTIF(O11:O210,"SIM")</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D6" s="3">
         <f>COUNTIF(P11:P210,"BLOQUEADA*")</f>
@@ -1548,7 +1607,7 @@
       </c>
       <c r="E6" s="3">
         <f>COUNTIF(P11:P210,"EXECUTADA - EM MATURAÇÃO")</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F6" s="4">
         <f>COUNTIF(P11:P210,"EXECUTADA - AVALIADA")</f>
@@ -1717,7 +1776,7 @@
       </c>
       <c r="R11" s="17">
         <f t="shared" ref="R11:R42" ca="1" si="1">IF(E11="","",TODAY()-E11)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S11" s="22"/>
       <c r="T11" s="22"/>
@@ -1779,7 +1838,7 @@
       </c>
       <c r="R12" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S12" s="23"/>
       <c r="T12" s="23"/>
@@ -1839,7 +1898,7 @@
       </c>
       <c r="R13" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S13" s="23"/>
       <c r="T13" s="42"/>
@@ -1903,7 +1962,7 @@
       </c>
       <c r="R14" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S14" s="23"/>
       <c r="T14" s="23"/>
@@ -1969,7 +2028,7 @@
       </c>
       <c r="R15" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
@@ -2035,7 +2094,7 @@
       </c>
       <c r="R16" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S16" s="23"/>
       <c r="T16" s="23"/>
@@ -2101,7 +2160,7 @@
       </c>
       <c r="R17" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S17" s="23"/>
       <c r="T17" s="23"/>
@@ -2165,7 +2224,7 @@
       </c>
       <c r="R18" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S18" s="23"/>
       <c r="T18" s="23"/>
@@ -2231,7 +2290,7 @@
       </c>
       <c r="R19" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S19" s="23"/>
       <c r="T19" s="23"/>
@@ -2297,7 +2356,7 @@
       </c>
       <c r="R20" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S20" s="23"/>
       <c r="T20" s="23"/>
@@ -2361,7 +2420,7 @@
       </c>
       <c r="R21" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S21" s="23"/>
       <c r="T21" s="23"/>
@@ -2423,7 +2482,7 @@
       </c>
       <c r="R22" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S22" s="23"/>
       <c r="T22" s="23"/>
@@ -2485,7 +2544,7 @@
       </c>
       <c r="R23" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S23" s="23"/>
       <c r="T23" s="23"/>
@@ -2547,7 +2606,7 @@
       </c>
       <c r="R24" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S24" s="23"/>
       <c r="T24" s="23"/>
@@ -2613,7 +2672,7 @@
       </c>
       <c r="R25" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S25" s="23"/>
       <c r="T25" s="23"/>
@@ -2675,7 +2734,7 @@
       </c>
       <c r="R26" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S26" s="23"/>
       <c r="T26" s="23"/>
@@ -2739,7 +2798,7 @@
       </c>
       <c r="R27" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S27" s="23"/>
       <c r="T27" s="23"/>
@@ -2805,7 +2864,7 @@
       </c>
       <c r="R28" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S28" s="23"/>
       <c r="T28" s="23"/>
@@ -2871,7 +2930,7 @@
       </c>
       <c r="R29" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S29" s="23"/>
       <c r="T29" s="23"/>
@@ -2937,7 +2996,7 @@
       </c>
       <c r="R30" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S30" s="23"/>
       <c r="T30" s="23"/>
@@ -3003,7 +3062,7 @@
       </c>
       <c r="R31" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S31" s="23"/>
       <c r="T31" s="23"/>
@@ -3014,64 +3073,132 @@
         <v>227</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
-      <c r="A32" s="10"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="26"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="11"/>
-      <c r="P32" s="11"/>
-      <c r="Q32" s="18" t="str">
+    <row r="32" spans="1:22" ht="57">
+      <c r="A32" t="s">
+        <v>229</v>
+      </c>
+      <c r="B32" t="s">
+        <v>215</v>
+      </c>
+      <c r="C32" s="12">
+        <v>46267</v>
+      </c>
+      <c r="D32" s="12">
+        <v>46267</v>
+      </c>
+      <c r="E32" s="12">
+        <v>46267</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="G32" s="51" t="s">
+        <v>233</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="I32" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="J32" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="K32" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="L32" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N32" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="P32" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q32" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="R32" s="19" t="str">
+        <v>46268</v>
+      </c>
+      <c r="R32" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S32" s="23"/>
       <c r="T32" s="23"/>
-      <c r="U32" s="7"/>
+      <c r="U32" s="7">
+        <v>46279</v>
+      </c>
       <c r="V32" s="28"/>
     </row>
-    <row r="33" spans="1:22">
-      <c r="A33" s="10"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-      <c r="K33" s="26"/>
-      <c r="L33" s="26"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="11"/>
-      <c r="P33" s="11"/>
-      <c r="Q33" s="18" t="str">
+    <row r="33" spans="1:22" ht="57">
+      <c r="A33" t="s">
+        <v>230</v>
+      </c>
+      <c r="B33" t="s">
+        <v>215</v>
+      </c>
+      <c r="C33" s="12">
+        <v>46267</v>
+      </c>
+      <c r="D33" s="12">
+        <v>46267</v>
+      </c>
+      <c r="E33" s="12">
+        <v>46267</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="G33" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="I33" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="J33" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="K33" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="L33" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N33" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="O33" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="P33" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q33" s="18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="R33" s="19" t="str">
+        <v>46268</v>
+      </c>
+      <c r="R33" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S33" s="23"/>
       <c r="T33" s="23"/>
-      <c r="U33" s="7"/>
+      <c r="U33" s="7">
+        <v>46279</v>
+      </c>
       <c r="V33" s="28"/>
     </row>
     <row r="34" spans="1:22">

--- a/dados/Registro_Alteracoes_Amazon_Ads_Winnet.xlsx
+++ b/dados/Registro_Alteracoes_Amazon_Ads_Winnet.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="362">
   <si>
     <t>REGISTRO DE ALTERAÇÕES — AMAZON ADS | WINNET METAIS</t>
   </si>
@@ -760,11 +760,371 @@
   <si>
     <t>Destrave de conversão (P3070 e P3050 com tráfego sem venda) + tickets do Núcleo A</t>
   </si>
+  <si>
+    <t>EC-005</t>
+  </si>
+  <si>
+    <t>EC-006</t>
+  </si>
+  <si>
+    <t>O5-001</t>
+  </si>
+  <si>
+    <t>O5-002</t>
+  </si>
+  <si>
+    <t>O5-003</t>
+  </si>
+  <si>
+    <t>O5-004</t>
+  </si>
+  <si>
+    <t>O5-005</t>
+  </si>
+  <si>
+    <t>O5-006</t>
+  </si>
+  <si>
+    <t>O5-007</t>
+  </si>
+  <si>
+    <t>O5-008</t>
+  </si>
+  <si>
+    <t>O5-009</t>
+  </si>
+  <si>
+    <t>O5-010</t>
+  </si>
+  <si>
+    <t>O5-011</t>
+  </si>
+  <si>
+    <t>O5-012</t>
+  </si>
+  <si>
+    <t>O5-013</t>
+  </si>
+  <si>
+    <t>O5-014</t>
+  </si>
+  <si>
+    <t>O5-015</t>
+  </si>
+  <si>
+    <t>O5-016</t>
+  </si>
+  <si>
+    <t>O5-017</t>
+  </si>
+  <si>
+    <t>O5</t>
+  </si>
+  <si>
+    <t>Geral DBA-o59/09 (era DBA-o311/08)</t>
+  </si>
+  <si>
+    <t>Geral DBA-o59/09</t>
+  </si>
+  <si>
+    <t>PI L2470-CZ-o425/08</t>
+  </si>
+  <si>
+    <t>PI PG3070-o425/08</t>
+  </si>
+  <si>
+    <t>Auto PXM-o425/08</t>
+  </si>
+  <si>
+    <t>Manual L3070-B</t>
+  </si>
+  <si>
+    <t>Auto SP-PP-o59/09 (era SP-PP-o425/08)</t>
+  </si>
+  <si>
+    <t>PI P3070-o228/07</t>
+  </si>
+  <si>
+    <t>Cinzeiros · Bituqueiras · Extintor</t>
+  </si>
+  <si>
+    <t>PI PXM-o311/08</t>
+  </si>
+  <si>
+    <t>PI L2030-B-o311/08 · Auto PXP-o311/08</t>
+  </si>
+  <si>
+    <t>segmentação substitutes / Substitutos</t>
+  </si>
+  <si>
+    <t>segmentação close-match / Correspondência aproximada</t>
+  </si>
+  <si>
+    <t>orçamento diário</t>
+  </si>
+  <si>
+    <t>segmentação loose-match / Correspondência vaga</t>
+  </si>
+  <si>
+    <t>palavra-chave nova — exata lixeira banheiro 10 com tampa</t>
+  </si>
+  <si>
+    <t>SKU L2025-B no grupo de anúncios</t>
+  </si>
+  <si>
+    <t>estratégia de lances e orçamento</t>
+  </si>
+  <si>
+    <t>VIGIA — contrato prorrogado 1 Era</t>
+  </si>
+  <si>
+    <t>MANTER (piloto confirmado)</t>
+  </si>
+  <si>
+    <t>ALTERAR ESTRATÉGIA — Fixo → Dinâmicos (aumento e redução)</t>
+  </si>
+  <si>
+    <t>PAUSAR ALVO (segmentação)</t>
+  </si>
+  <si>
+    <t>MANTER CONGELADA (gatilho definido)</t>
+  </si>
+  <si>
+    <t>REVISAR (sem ação agora)</t>
+  </si>
+  <si>
+    <t>CORRIGIR CTR / CRIATIVO</t>
+  </si>
+  <si>
+    <t>R$ 90/dia — ACOS 30d 10,5%, régua mandaria +20%</t>
+  </si>
+  <si>
+    <t>Ativa — radar O4-004, alvos 0,66 / 0,60</t>
+  </si>
+  <si>
+    <t>Ativa — radar O4-005, 57 alvos a 0,66</t>
+  </si>
+  <si>
+    <t>Ativa — radar O4-010</t>
+  </si>
+  <si>
+    <t>Radar O4-012, lance R$ 0,84 fixo; o contrato comum mandaria pausar</t>
+  </si>
+  <si>
+    <t>Dinâmicos (aumento e redução) desde a O4-014</t>
+  </si>
+  <si>
+    <t>Lances fixos: exata 1,20, frase 1,00, topo +25%</t>
+  </si>
+  <si>
+    <t>Ativa — lance R$ 1,32 (as 4 segmentações têm o mesmo lance)</t>
+  </si>
+  <si>
+    <t>Congelada desde a O4. Era: 30 cliques, R$ 34,41, zero venda</t>
+  </si>
+  <si>
+    <t>Ativa (reativada pela O4-R03); zero impressão de 18/08 a 07/09</t>
+  </si>
+  <si>
+    <t>Termo só na Geral (close-match)</t>
+  </si>
+  <si>
+    <t>L2025-B no grupo. No termo lixeira banheiro 7 litros a perna L2025-B tem 4 cliques, R$ 6,52 e zero venda — 56% do gasto do termo</t>
+  </si>
+  <si>
+    <t>Fixos. Extintor R$ 8/dia, topo +75%</t>
+  </si>
+  <si>
+    <t>Ativa, lance R$ 1,10 em 52 alvos</t>
+  </si>
+  <si>
+    <t>Ativas</t>
+  </si>
+  <si>
+    <t>R$ 0,45 (−17%)</t>
+  </si>
+  <si>
+    <t>R$ 0,54 (+20%)</t>
+  </si>
+  <si>
+    <t>Ativa, lance 0,84 mantido. GATILHO O6: zero vendas E CTR &lt; 0,3% → pausar</t>
+  </si>
+  <si>
+    <t>Sem alteração</t>
+  </si>
+  <si>
+    <t>Dinâmicos (aumento e redução), mesmos lances e mesmo topo</t>
+  </si>
+  <si>
+    <t>Pausada. VIGIA da campanha, GATILHO O6: zero cliques relevantes → PAUSAR CAMPANHA</t>
+  </si>
+  <si>
+    <t>Sem alteração até 14/09. GATILHO O6: sem venda atribuída pós-Relâmpago E ≥15 cliques na Era O5→O6 → REDUZIR lances −20% nos asin-expanded</t>
+  </si>
+  <si>
+    <t>NÃO EXECUTADA — condição da própria linha não atendida</t>
+  </si>
+  <si>
+    <t>Decisão em 14/09</t>
+  </si>
+  <si>
+    <t>Sem alteração de configuração — entra na fila de CTR junto com a EGC</t>
+  </si>
+  <si>
+    <t>Cupom P2025</t>
+  </si>
+  <si>
+    <t>P2025 — cupom 12%</t>
+  </si>
+  <si>
+    <t>CRIAR CUPOM</t>
+  </si>
+  <si>
+    <t>Sem cupom</t>
+  </si>
+  <si>
+    <t>Cupom 12% ativo</t>
+  </si>
+  <si>
+    <t>Decisão do LEO. SKU fora do pacote 9.9, sem conflito de oferta. Margem 12,8% após o cupom; empilha com a promo de quantidade (5+ → 19% de desconto, margem 7,2%)</t>
+  </si>
+  <si>
+    <t>docs/PLANO_9-9.md + ciclos/EC-04-09.md + Simulador Mestra v4.3.4</t>
+  </si>
+  <si>
+    <t>Cupom lixeiras de embutir</t>
+  </si>
+  <si>
+    <t>EMB-05, EMB-05P e EMB-08 — cupom 50%</t>
+  </si>
+  <si>
+    <t>Cupom 50% ativo, sem teto de unidades</t>
+  </si>
+  <si>
+    <t>Decisão da Dianna: LIQUIDAÇÃO DELIBERADA ABAIXO DO CUSTO para liberar espaço físico. Perda conhecida de R$ 53 a R$ 61 por unidade; até R$ 71 no EMB-08 com a promo de quantidade. Sem contagem de estoque — o teto prático é o orçamento do cupom</t>
+  </si>
+  <si>
+    <t>30d (08/08–06/09): 167 cliques, R$ 107,60, 1 compra, ACOS 81% — acima da Emergência. Consumia 39% do gasto da Geral. Vitalício 20,9%. Ação no nível da segmentação, não da campanha</t>
+  </si>
+  <si>
+    <t>ciclos/O5-08-09.md + relatorios/amazon/o5-08-09/</t>
+  </si>
+  <si>
+    <t>Melhor eficiência da Geral com o MENOR lance: 30d 24 cliques, 2 compras, ACOS 2,5%; vitalício 128 cliques, 4 compras, 6,9%. Corrige a inversão de funil em que substitutes gastava mais que close</t>
+  </si>
+  <si>
+    <t>Gasto da Era R$ 10,55/dia ≈ 12% do orçamento — o orçamento não é a restrição (regra consolidada). O ACOS de 30d é sustentado por 1 pedido halo; sem ele seria 31,4%</t>
+  </si>
+  <si>
+    <t>Contrato de saída da O4-004 acionado: Era 4 cliques, R$ 2,51, zero venda; vitalício 18 cliques e zero venda em 32 alvos</t>
+  </si>
+  <si>
+    <t>Contrato de saída da O4-005 acionado: Era 1 clique, R$ 0,99; vitalício 8 cliques e zero venda em 83 alvos. A migração para exatos fica sem objeto</t>
+  </si>
+  <si>
+    <t>Contrato de saída da O4-010 acionado: Era 2 cliques, R$ 2,02, zero venda. Redundante com o Extintor manual (vendeu na Era), a PI PXM-o3 e a auto PXP-o3</t>
+  </si>
+  <si>
+    <t>O radar cumpriu a entrega: 361 → 2.391 impressões em 30d. O problema migrou de entrega para CTR (0,13%). Único termo com clique foi um ASIN substitute. Nicho de busca rara. Melhor Oferta −10% ativa 08–13/09 funciona como teste de conversão</t>
+  </si>
+  <si>
+    <t>Piloto POSITIVO PRELIMINAR: pré-Era 6 cliques em 15 dias e zero venda → Era 11 cliques em 13 dias e 1 venda de R$ 265,80. CPC subiu de 1,33 para 1,60. Os controles fixos ficaram em 0–1 clique na Era</t>
+  </si>
+  <si>
+    <t>Controle com zero clique na Era (4 no pré-Era). O termo lixeira basculante 50 litros é rank 1 com share de 42% → há leilões a capturar. Margem 24,2% no Simulador SP Interior</t>
+  </si>
+  <si>
+    <t>Depois da O4-001, 6 dos 7 cliques da Era (R$ 7,66 de R$ 8,98) vieram da loose-match, em 6 termos parede irrelevantes. CTR ~0,06%. Vitalício 26 cliques e zero venda</t>
+  </si>
+  <si>
+    <t>Consome 16% do gasto da Era sem atribuição. Nenhum alvo atinge a régua de 15 cliques vitalícios (o maior é B09YDLC69D com 12, em revisão). O SKU converteu ORGANICAMENTE em 03/09 (1 venda em 43 sessões). Relâmpago −10% em curso é o teste</t>
+  </si>
+  <si>
+    <t>PAUSA POR INELEGIBILIDADE PUBLICITÁRIA — o ANÚNCIO dentro desta campanha está suspenso por política. NÃO é falha de desempenho e NÃO é supressão do ASIN: o listing está ativo e o SP-01 segue anunciado normalmente pela Manual Bituqueiras Space (14 impressões entre 20/08 e 04/09)</t>
+  </si>
+  <si>
+    <t>1 venda em close-match (L2030-T, R$ 143,13); mesma família da 6B; margem do L2030-T 19,4%</t>
+  </si>
+  <si>
+    <t>Achado C2 da auditoria do Claude Code: o relatório de Termos é por LINHA DE SKU e não por termo. O termo custa R$ 11,71 no total (L2025-T 3 cliques e 1 venda + L2025-B 4 cliques e zero venda), não os R$ 5,19 da linha que vendeu</t>
+  </si>
+  <si>
+    <t>Rank 1 e share 100% em TODOS os termos com impressão — o lance não é a barreira, e lance dinâmico só compra leilão que se está perdendo. O Extintor vendeu (ACOS 30d 1,4%) e gasta 1% do próprio orçamento</t>
+  </si>
+  <si>
+    <t>⚠️ CATEGORIA CORRIGIDA APÓS CONFERÊNCIA NO CONSOLE (achado C7 da auditoria). O diagnóstico dizia SEM ENTREGA e mandava investigar entrega. A campanha ENTREGA: 2.500 impressões vitalícias, 638 em 30 dias, os 52 alvos com impressão. O problema é CTR: 0,28% vitalício, 0,16% em 30d. Os 7 cliques vitalícios geraram 1 compra de R$ 203,54 com R$ 5,50 de gasto (ROAS 37,01)</t>
+  </si>
+  <si>
+    <t>CONTRAPESO VITALÍCIO: as duas têm vitalício saudável e Era fria. PI L2030-B: 16 cliques, 3 compras, R$ 497,34 (ROAS 41,8). Auto PXP: 28 cliques, 4 compras, R$ 690,42 (ROAS 27,1) — a segunda melhor da conta</t>
+  </si>
+  <si>
+    <t>quando o anúncio for liberado</t>
+  </si>
+  <si>
+    <t>Atenção ao empilhamento com a promo de quantidade</t>
+  </si>
+  <si>
+    <t>⚠️ VENDAS COM MARGEM NEGATIVA POR DESENHO — segregar de qualquer média de margem do catálogo e dos rankings de lucro. Linha de base em ciclos/EC-04-09.md</t>
+  </si>
+  <si>
+    <t>Conferido no console em 09/09. Não isolável na Era; ler na O6 pelo relatório de Segmentação. Ler junto com O5-002</t>
+  </si>
+  <si>
+    <t>Conferido no console em 09/09. Amostra de 24 cliques em 30d. Ler junto com O5-001</t>
+  </si>
+  <si>
+    <t>O lance padrão do grupo (R$ 0,48) é INERTE — as 4 segmentações têm lance próprio. A escala real da Geral é por segmentação</t>
+  </si>
+  <si>
+    <t>Conferido no export de 09/09. Sem prorrogação. A família cinzeiro segue coberta pela Geral</t>
+  </si>
+  <si>
+    <t>Conferido no export de 09/09. A família PG vendeu via Geral + Melhor Oferta (PG2460, 07/09)</t>
+  </si>
+  <si>
+    <t>CONTRAPESO VITALÍCIO APLICADO E SUPERADO PELA REDUNDÂNCIA: esta campanha TEM venda vitalícia de R$ 610,62 (pedido de 08/07, 3 un de PXM). Não é campanha sem histórico. Corrigir também o texto da O4-010: PXM é suporte de extintor 6 kg, não porta-guarda-chuva</t>
+  </si>
+  <si>
+    <t>Desvio explícito do contrato comum de radar, decidido pelo LEO em 08/09. O CTR atual (0,125%) já está abaixo do gatilho — se a oferta não converter, a pausa dispara na O6</t>
+  </si>
+  <si>
+    <t>n = 1 venda. O custo REAL do termo lixeira banheiro 7 litros é R$ 11,71 e não R$ 5,19 — a perna L2025-B levou R$ 6,52 sem venda (ver O5-014)</t>
+  </si>
+  <si>
+    <t>Conferido no export de 09/09. ⚠️ O share de 42,44% é DA CONTA e soma Geral (19 impressões / 4 cliques) + manual (54 / 3) no mesmo termo — parte do espaço é disputa interna. Ler as duas campanhas juntas na O6</t>
+  </si>
+  <si>
+    <t>⚠️ EXECUTADA INVERTIDA E CORRIGIDA NO MESMO DIA: a primeira execução pausou a close-match e deixou a loose ativa. Causa: em PT-BR, Correspondência vaga = loose-match e Correspondência aproximada = close-match. Detectado pela conferência pós-execução e corrigido em 09/09. Estado final conferido: substitutes e loose pausadas, close e complements ativas. Termos: saboneteira parede, suporte planta parede, mandalas decorativas parede, mop para limpar paredes, organizador de fios parede, suporte secador de cabelo parede</t>
+  </si>
+  <si>
+    <t>Reavaliar em 14/09 (leitura do 9.9) e de novo na O6</t>
+  </si>
+  <si>
+    <t>NÃO ENTRA EM CONTRAPESO VITALÍCIO NEM EM LEITURA DE PERFORMANCE (Playbook §30). Reativação condicionada à liberação do anúncio nesta campanha. Nota de fonte: o export do Gerenciador NÃO mostra suspensão no nível do anúncio — só o console mostra</t>
+  </si>
+  <si>
+    <t>BLOQUEADA: o L2030-T NÃO está no grupo de anúncios da 6B, e a linha exigia essa conferência antes de adicionar. Adicionar produto e palavra-chave no meio do piloto de lance introduziria uma segunda variável e estragaria a leitura da O6. Nada se perde: o termo segue convertendo pela Geral. Decisão volta na O6</t>
+  </si>
+  <si>
+    <t>Amostra pequena. Decidir em 14/09 se o L2025-B sai do grupo</t>
+  </si>
+  <si>
+    <t>Bituqueiras: primeira leitura real. Entrega limitada pelo volume dos termos exatos — MÉTRICA BRUTA, não inferir teto de mercado. Estas três seguem como grupo de controle do piloto de lance</t>
+  </si>
+  <si>
+    <t>O erro original veio de derivar impressões como cliques ÷ CTR: com zero cliques a conta é 0÷0, indefinido, e o zero virou premissa. REGRA: campanha com zero clique no export não tem impressão derivável. Custo vitalício de R$ 5,50 — sem urgência</t>
+  </si>
+  <si>
+    <t>A auto PXP ganhou 1 compra entre 07/09 e 09/09 (+R$ 151,10) e o Extintor ganhou outra (+R$ 302,20). Export vitalício não separa data — pode ser venda nova ou maturação de atribuição. Resolver em 14/09 contra o Registro_Vendas. NÃO INFERIDO</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
+  </numFmts>
   <fonts count="14">
     <font>
       <sz val="11"/>
@@ -990,7 +1350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1115,6 +1475,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1136,7 +1497,7 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1474,82 +1835,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="45"/>
     </row>
     <row r="2" spans="1:22" ht="30" customHeight="1">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
-      <c r="V2" s="45"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="46"/>
+      <c r="V2" s="46"/>
     </row>
     <row r="3" spans="1:22" ht="27.95" customHeight="1">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="46"/>
-      <c r="P3" s="46"/>
-      <c r="Q3" s="46"/>
-      <c r="R3" s="46"/>
-      <c r="S3" s="46"/>
-      <c r="T3" s="46"/>
-      <c r="U3" s="46"/>
-      <c r="V3" s="46"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="47"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="47"/>
+      <c r="V3" s="47"/>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1" t="s">
@@ -1570,90 +1931,90 @@
       <c r="F5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="47" t="s">
+      <c r="H5" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="47"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="47"/>
-      <c r="O5" s="47"/>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="47"/>
-      <c r="R5" s="47"/>
-      <c r="S5" s="47"/>
-      <c r="T5" s="47"/>
-      <c r="U5" s="47"/>
-      <c r="V5" s="47"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="48"/>
+      <c r="S5" s="48"/>
+      <c r="T5" s="48"/>
+      <c r="U5" s="48"/>
+      <c r="V5" s="48"/>
     </row>
     <row r="6" spans="1:22" ht="26.1" customHeight="1">
       <c r="A6" s="2">
         <f>COUNTIF(A11:A210,"&lt;&gt;")</f>
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B6" s="3">
         <f>COUNTIF(N11:N210,"SIM")</f>
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C6" s="3">
         <f>COUNTIF(O11:O210,"SIM")</f>
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D6" s="3">
         <f>COUNTIF(P11:P210,"BLOQUEADA*")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="3">
         <f>COUNTIF(P11:P210,"EXECUTADA - EM MATURAÇÃO")</f>
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F6" s="4">
         <f>COUNTIF(P11:P210,"EXECUTADA - AVALIADA")</f>
         <v>0</v>
       </c>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="47"/>
-      <c r="Q6" s="47"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="47"/>
-      <c r="T6" s="47"/>
-      <c r="U6" s="47"/>
-      <c r="V6" s="47"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="48"/>
+      <c r="U6" s="48"/>
+      <c r="V6" s="48"/>
     </row>
     <row r="8" spans="1:22" ht="21.95" customHeight="1">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="48"/>
-      <c r="N8" s="48"/>
-      <c r="O8" s="48"/>
-      <c r="P8" s="48"/>
-      <c r="Q8" s="48"/>
-      <c r="R8" s="48"/>
-      <c r="S8" s="48"/>
-      <c r="T8" s="48"/>
-      <c r="U8" s="48"/>
-      <c r="V8" s="48"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="49"/>
+      <c r="P8" s="49"/>
+      <c r="Q8" s="49"/>
+      <c r="R8" s="49"/>
+      <c r="S8" s="49"/>
+      <c r="T8" s="49"/>
+      <c r="U8" s="49"/>
+      <c r="V8" s="49"/>
     </row>
     <row r="10" spans="1:22" ht="38.1" customHeight="1">
       <c r="A10" s="5" t="s">
@@ -1776,7 +2137,7 @@
       </c>
       <c r="R11" s="17">
         <f t="shared" ref="R11:R42" ca="1" si="1">IF(E11="","",TODAY()-E11)</f>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="S11" s="22"/>
       <c r="T11" s="22"/>
@@ -1838,7 +2199,7 @@
       </c>
       <c r="R12" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="S12" s="23"/>
       <c r="T12" s="23"/>
@@ -1898,7 +2259,7 @@
       </c>
       <c r="R13" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S13" s="23"/>
       <c r="T13" s="42"/>
@@ -1962,7 +2323,7 @@
       </c>
       <c r="R14" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S14" s="23"/>
       <c r="T14" s="23"/>
@@ -2028,7 +2389,7 @@
       </c>
       <c r="R15" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
@@ -2094,7 +2455,7 @@
       </c>
       <c r="R16" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S16" s="23"/>
       <c r="T16" s="23"/>
@@ -2160,7 +2521,7 @@
       </c>
       <c r="R17" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S17" s="23"/>
       <c r="T17" s="23"/>
@@ -2224,7 +2585,7 @@
       </c>
       <c r="R18" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S18" s="23"/>
       <c r="T18" s="23"/>
@@ -2290,7 +2651,7 @@
       </c>
       <c r="R19" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S19" s="23"/>
       <c r="T19" s="23"/>
@@ -2356,7 +2717,7 @@
       </c>
       <c r="R20" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S20" s="23"/>
       <c r="T20" s="23"/>
@@ -2420,7 +2781,7 @@
       </c>
       <c r="R21" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S21" s="23"/>
       <c r="T21" s="23"/>
@@ -2482,7 +2843,7 @@
       </c>
       <c r="R22" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S22" s="23"/>
       <c r="T22" s="23"/>
@@ -2544,7 +2905,7 @@
       </c>
       <c r="R23" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S23" s="23"/>
       <c r="T23" s="23"/>
@@ -2606,7 +2967,7 @@
       </c>
       <c r="R24" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S24" s="23"/>
       <c r="T24" s="23"/>
@@ -2672,7 +3033,7 @@
       </c>
       <c r="R25" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S25" s="23"/>
       <c r="T25" s="23"/>
@@ -2734,7 +3095,7 @@
       </c>
       <c r="R26" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S26" s="23"/>
       <c r="T26" s="23"/>
@@ -2798,7 +3159,7 @@
       </c>
       <c r="R27" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S27" s="23"/>
       <c r="T27" s="23"/>
@@ -2864,7 +3225,7 @@
       </c>
       <c r="R28" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S28" s="23"/>
       <c r="T28" s="23"/>
@@ -2930,7 +3291,7 @@
       </c>
       <c r="R29" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S29" s="23"/>
       <c r="T29" s="23"/>
@@ -2996,7 +3357,7 @@
       </c>
       <c r="R30" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="S30" s="23"/>
       <c r="T30" s="23"/>
@@ -3062,7 +3423,7 @@
       </c>
       <c r="R31" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="S31" s="23"/>
       <c r="T31" s="23"/>
@@ -3092,7 +3453,7 @@
       <c r="F32" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="G32" s="51" t="s">
+      <c r="G32" s="44" t="s">
         <v>233</v>
       </c>
       <c r="H32" s="11" t="s">
@@ -3128,7 +3489,7 @@
       </c>
       <c r="R32" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S32" s="23"/>
       <c r="T32" s="23"/>
@@ -3192,7 +3553,7 @@
       </c>
       <c r="R33" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S33" s="23"/>
       <c r="T33" s="23"/>
@@ -3202,574 +3563,1233 @@
       <c r="V33" s="28"/>
     </row>
     <row r="34" spans="1:22">
-      <c r="A34" s="10"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
-      <c r="O34" s="11"/>
-      <c r="P34" s="11"/>
-      <c r="Q34" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="R34" s="19" t="str">
+      <c r="A34" t="s">
+        <v>243</v>
+      </c>
+      <c r="B34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" s="43">
+        <v>46269</v>
+      </c>
+      <c r="D34" s="43">
+        <v>46269</v>
+      </c>
+      <c r="E34" s="43">
+        <v>46269</v>
+      </c>
+      <c r="F34" t="s">
+        <v>313</v>
+      </c>
+      <c r="G34" t="s">
+        <v>314</v>
+      </c>
+      <c r="H34" t="s">
+        <v>315</v>
+      </c>
+      <c r="I34" t="s">
+        <v>316</v>
+      </c>
+      <c r="J34" t="s">
+        <v>317</v>
+      </c>
+      <c r="K34" t="s">
+        <v>318</v>
+      </c>
+      <c r="L34" t="s">
+        <v>319</v>
+      </c>
+      <c r="M34" t="s">
+        <v>45</v>
+      </c>
+      <c r="N34" t="s">
+        <v>40</v>
+      </c>
+      <c r="O34" t="s">
+        <v>40</v>
+      </c>
+      <c r="P34" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q34" s="43">
+        <v>46270</v>
+      </c>
+      <c r="R34" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="S34" s="23"/>
       <c r="T34" s="23"/>
-      <c r="U34" s="7"/>
-      <c r="V34" s="28"/>
+      <c r="U34" s="43">
+        <v>46283</v>
+      </c>
+      <c r="V34" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="35" spans="1:22">
-      <c r="A35" s="10"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="11"/>
-      <c r="P35" s="11"/>
-      <c r="Q35" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="R35" s="19" t="str">
+      <c r="A35" t="s">
+        <v>244</v>
+      </c>
+      <c r="B35" t="s">
+        <v>215</v>
+      </c>
+      <c r="C35" s="43">
+        <v>46269</v>
+      </c>
+      <c r="D35" s="43">
+        <v>46269</v>
+      </c>
+      <c r="E35" s="43">
+        <v>46269</v>
+      </c>
+      <c r="F35" t="s">
+        <v>320</v>
+      </c>
+      <c r="G35" t="s">
+        <v>321</v>
+      </c>
+      <c r="H35" t="s">
+        <v>315</v>
+      </c>
+      <c r="I35" t="s">
+        <v>316</v>
+      </c>
+      <c r="J35" t="s">
+        <v>322</v>
+      </c>
+      <c r="K35" t="s">
+        <v>323</v>
+      </c>
+      <c r="L35" t="s">
+        <v>319</v>
+      </c>
+      <c r="M35" t="s">
+        <v>41</v>
+      </c>
+      <c r="N35" t="s">
+        <v>40</v>
+      </c>
+      <c r="O35" t="s">
+        <v>40</v>
+      </c>
+      <c r="P35" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q35" s="43">
+        <v>46270</v>
+      </c>
+      <c r="R35" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="S35" s="23"/>
       <c r="T35" s="23"/>
-      <c r="U35" s="7"/>
-      <c r="V35" s="28"/>
+      <c r="U35" s="43">
+        <v>46283</v>
+      </c>
+      <c r="V35" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="36" spans="1:22">
-      <c r="A36" s="10"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-      <c r="O36" s="11"/>
-      <c r="P36" s="11"/>
-      <c r="Q36" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="R36" s="19" t="str">
+      <c r="A36" t="s">
+        <v>245</v>
+      </c>
+      <c r="B36" t="s">
+        <v>262</v>
+      </c>
+      <c r="C36" s="43">
+        <v>46273</v>
+      </c>
+      <c r="D36" s="43">
+        <v>46273</v>
+      </c>
+      <c r="E36" s="43">
+        <v>46274</v>
+      </c>
+      <c r="F36" t="s">
+        <v>263</v>
+      </c>
+      <c r="G36" t="s">
+        <v>274</v>
+      </c>
+      <c r="H36" t="s">
+        <v>42</v>
+      </c>
+      <c r="I36" s="52">
+        <v>0.54</v>
+      </c>
+      <c r="J36" t="s">
+        <v>303</v>
+      </c>
+      <c r="K36" t="s">
+        <v>324</v>
+      </c>
+      <c r="L36" t="s">
+        <v>325</v>
+      </c>
+      <c r="M36" t="s">
+        <v>45</v>
+      </c>
+      <c r="N36" t="s">
+        <v>40</v>
+      </c>
+      <c r="O36" t="s">
+        <v>40</v>
+      </c>
+      <c r="P36" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>46275</v>
+      </c>
+      <c r="R36" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S36" s="23"/>
       <c r="T36" s="23"/>
-      <c r="U36" s="7"/>
-      <c r="V36" s="28"/>
+      <c r="U36" s="43">
+        <v>46287</v>
+      </c>
+      <c r="V36" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="37" spans="1:22">
-      <c r="A37" s="10"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="26"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="11"/>
-      <c r="P37" s="11"/>
-      <c r="Q37" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="R37" s="19" t="str">
+      <c r="A37" t="s">
+        <v>246</v>
+      </c>
+      <c r="B37" t="s">
+        <v>262</v>
+      </c>
+      <c r="C37" s="43">
+        <v>46273</v>
+      </c>
+      <c r="D37" s="43">
+        <v>46273</v>
+      </c>
+      <c r="E37" s="43">
+        <v>46274</v>
+      </c>
+      <c r="F37" t="s">
+        <v>263</v>
+      </c>
+      <c r="G37" t="s">
+        <v>275</v>
+      </c>
+      <c r="H37" t="s">
+        <v>38</v>
+      </c>
+      <c r="I37" s="52">
+        <v>0.45</v>
+      </c>
+      <c r="J37" t="s">
+        <v>304</v>
+      </c>
+      <c r="K37" t="s">
+        <v>326</v>
+      </c>
+      <c r="L37" t="s">
+        <v>325</v>
+      </c>
+      <c r="M37" t="s">
+        <v>45</v>
+      </c>
+      <c r="N37" t="s">
+        <v>40</v>
+      </c>
+      <c r="O37" t="s">
+        <v>40</v>
+      </c>
+      <c r="P37" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q37" s="43">
+        <v>46275</v>
+      </c>
+      <c r="R37" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S37" s="23"/>
       <c r="T37" s="23"/>
-      <c r="U37" s="7"/>
-      <c r="V37" s="28"/>
+      <c r="U37" s="43">
+        <v>46287</v>
+      </c>
+      <c r="V37" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="38" spans="1:22">
-      <c r="A38" s="10"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-      <c r="K38" s="26"/>
-      <c r="L38" s="26"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
-      <c r="O38" s="11"/>
-      <c r="P38" s="11"/>
-      <c r="Q38" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="R38" s="19" t="str">
+      <c r="A38" t="s">
+        <v>247</v>
+      </c>
+      <c r="B38" t="s">
+        <v>262</v>
+      </c>
+      <c r="C38" s="43">
+        <v>46273</v>
+      </c>
+      <c r="D38" s="43">
+        <v>46273</v>
+      </c>
+      <c r="E38" s="43">
+        <v>46274</v>
+      </c>
+      <c r="F38" t="s">
+        <v>264</v>
+      </c>
+      <c r="G38" t="s">
+        <v>276</v>
+      </c>
+      <c r="H38" t="s">
+        <v>136</v>
+      </c>
+      <c r="I38" t="s">
+        <v>288</v>
+      </c>
+      <c r="J38" t="s">
+        <v>160</v>
+      </c>
+      <c r="K38" t="s">
+        <v>327</v>
+      </c>
+      <c r="L38" t="s">
+        <v>325</v>
+      </c>
+      <c r="M38" t="s">
+        <v>41</v>
+      </c>
+      <c r="N38" t="s">
+        <v>40</v>
+      </c>
+      <c r="O38" t="s">
+        <v>40</v>
+      </c>
+      <c r="P38" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q38" s="43">
+        <v>46275</v>
+      </c>
+      <c r="R38" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S38" s="23"/>
       <c r="T38" s="23"/>
-      <c r="U38" s="7"/>
-      <c r="V38" s="28"/>
+      <c r="U38" s="43">
+        <v>46287</v>
+      </c>
+      <c r="V38" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="39" spans="1:22">
-      <c r="A39" s="10"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-      <c r="K39" s="26"/>
-      <c r="L39" s="26"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="11"/>
-      <c r="O39" s="11"/>
-      <c r="P39" s="11"/>
-      <c r="Q39" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="R39" s="19" t="str">
+      <c r="A39" t="s">
+        <v>248</v>
+      </c>
+      <c r="B39" t="s">
+        <v>262</v>
+      </c>
+      <c r="C39" s="43">
+        <v>46273</v>
+      </c>
+      <c r="D39" s="43">
+        <v>46273</v>
+      </c>
+      <c r="E39" s="43">
+        <v>46274</v>
+      </c>
+      <c r="F39" t="s">
+        <v>265</v>
+      </c>
+      <c r="G39" t="s">
+        <v>114</v>
+      </c>
+      <c r="H39" t="s">
+        <v>54</v>
+      </c>
+      <c r="I39" t="s">
+        <v>289</v>
+      </c>
+      <c r="J39" t="s">
+        <v>143</v>
+      </c>
+      <c r="K39" t="s">
+        <v>328</v>
+      </c>
+      <c r="L39" t="s">
+        <v>325</v>
+      </c>
+      <c r="M39" t="s">
+        <v>41</v>
+      </c>
+      <c r="N39" t="s">
+        <v>40</v>
+      </c>
+      <c r="O39" t="s">
+        <v>40</v>
+      </c>
+      <c r="P39" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q39" s="43">
+        <v>46275</v>
+      </c>
+      <c r="R39" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S39" s="23"/>
       <c r="T39" s="23"/>
-      <c r="U39" s="7"/>
-      <c r="V39" s="28"/>
+      <c r="U39" s="43">
+        <v>46287</v>
+      </c>
+      <c r="V39" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="40" spans="1:22">
-      <c r="A40" s="10"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
-      <c r="K40" s="26"/>
-      <c r="L40" s="26"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="11"/>
-      <c r="O40" s="11"/>
-      <c r="P40" s="11"/>
-      <c r="Q40" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="R40" s="19" t="str">
+      <c r="A40" t="s">
+        <v>249</v>
+      </c>
+      <c r="B40" t="s">
+        <v>262</v>
+      </c>
+      <c r="C40" s="43">
+        <v>46273</v>
+      </c>
+      <c r="D40" s="43">
+        <v>46273</v>
+      </c>
+      <c r="E40" s="43">
+        <v>46274</v>
+      </c>
+      <c r="F40" t="s">
+        <v>266</v>
+      </c>
+      <c r="G40" t="s">
+        <v>114</v>
+      </c>
+      <c r="H40" t="s">
+        <v>54</v>
+      </c>
+      <c r="I40" t="s">
+        <v>290</v>
+      </c>
+      <c r="J40" t="s">
+        <v>143</v>
+      </c>
+      <c r="K40" t="s">
+        <v>329</v>
+      </c>
+      <c r="L40" t="s">
+        <v>325</v>
+      </c>
+      <c r="M40" t="s">
+        <v>41</v>
+      </c>
+      <c r="N40" t="s">
+        <v>40</v>
+      </c>
+      <c r="O40" t="s">
+        <v>40</v>
+      </c>
+      <c r="P40" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q40" s="43">
+        <v>46275</v>
+      </c>
+      <c r="R40" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S40" s="23"/>
       <c r="T40" s="23"/>
-      <c r="U40" s="7"/>
-      <c r="V40" s="28"/>
+      <c r="U40" s="43">
+        <v>46287</v>
+      </c>
+      <c r="V40" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="41" spans="1:22">
-      <c r="A41" s="10"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="11"/>
-      <c r="P41" s="11"/>
-      <c r="Q41" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="R41" s="19" t="str">
+      <c r="A41" t="s">
+        <v>250</v>
+      </c>
+      <c r="B41" t="s">
+        <v>262</v>
+      </c>
+      <c r="C41" s="43">
+        <v>46273</v>
+      </c>
+      <c r="D41" s="43">
+        <v>46273</v>
+      </c>
+      <c r="E41" s="43">
+        <v>46274</v>
+      </c>
+      <c r="F41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G41" t="s">
+        <v>114</v>
+      </c>
+      <c r="H41" t="s">
+        <v>54</v>
+      </c>
+      <c r="I41" t="s">
+        <v>291</v>
+      </c>
+      <c r="J41" t="s">
+        <v>143</v>
+      </c>
+      <c r="K41" t="s">
+        <v>330</v>
+      </c>
+      <c r="L41" t="s">
+        <v>325</v>
+      </c>
+      <c r="M41" t="s">
+        <v>41</v>
+      </c>
+      <c r="N41" t="s">
+        <v>40</v>
+      </c>
+      <c r="O41" t="s">
+        <v>40</v>
+      </c>
+      <c r="P41" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q41" s="43">
+        <v>46275</v>
+      </c>
+      <c r="R41" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S41" s="23"/>
       <c r="T41" s="23"/>
-      <c r="U41" s="7"/>
-      <c r="V41" s="28"/>
+      <c r="U41" s="43">
+        <v>46287</v>
+      </c>
+      <c r="V41" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="42" spans="1:22">
-      <c r="A42" s="10"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="26"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="11"/>
-      <c r="O42" s="11"/>
-      <c r="P42" s="11"/>
-      <c r="Q42" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="R42" s="19" t="str">
+      <c r="A42" t="s">
+        <v>251</v>
+      </c>
+      <c r="B42" t="s">
+        <v>262</v>
+      </c>
+      <c r="C42" s="43">
+        <v>46273</v>
+      </c>
+      <c r="D42" s="43">
+        <v>46273</v>
+      </c>
+      <c r="E42" s="43">
+        <v>46274</v>
+      </c>
+      <c r="F42" t="s">
+        <v>110</v>
+      </c>
+      <c r="G42" t="s">
+        <v>114</v>
+      </c>
+      <c r="H42" t="s">
+        <v>281</v>
+      </c>
+      <c r="I42" t="s">
+        <v>292</v>
+      </c>
+      <c r="J42" t="s">
+        <v>305</v>
+      </c>
+      <c r="K42" t="s">
+        <v>331</v>
+      </c>
+      <c r="L42" t="s">
+        <v>325</v>
+      </c>
+      <c r="M42" t="s">
+        <v>45</v>
+      </c>
+      <c r="N42" t="s">
+        <v>40</v>
+      </c>
+      <c r="O42" t="s">
+        <v>40</v>
+      </c>
+      <c r="P42" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>46275</v>
+      </c>
+      <c r="R42" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S42" s="23"/>
       <c r="T42" s="23"/>
-      <c r="U42" s="7"/>
-      <c r="V42" s="28"/>
+      <c r="U42" s="43">
+        <v>46287</v>
+      </c>
+      <c r="V42" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="43" spans="1:22">
-      <c r="A43" s="10"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
-      <c r="K43" s="26"/>
-      <c r="L43" s="26"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="11"/>
-      <c r="O43" s="11"/>
-      <c r="P43" s="11"/>
-      <c r="Q43" s="18" t="str">
-        <f t="shared" ref="Q43:Q74" si="2">IF(E43="","",E43+1)</f>
-        <v/>
-      </c>
-      <c r="R43" s="19" t="str">
-        <f t="shared" ref="R43:R74" ca="1" si="3">IF(E43="","",TODAY()-E43)</f>
-        <v/>
+      <c r="A43" t="s">
+        <v>252</v>
+      </c>
+      <c r="B43" t="s">
+        <v>262</v>
+      </c>
+      <c r="C43" s="43">
+        <v>46273</v>
+      </c>
+      <c r="D43" s="43">
+        <v>46273</v>
+      </c>
+      <c r="E43" s="43">
+        <v>46274</v>
+      </c>
+      <c r="F43" t="s">
+        <v>112</v>
+      </c>
+      <c r="G43" t="s">
+        <v>123</v>
+      </c>
+      <c r="H43" t="s">
+        <v>282</v>
+      </c>
+      <c r="I43" t="s">
+        <v>293</v>
+      </c>
+      <c r="J43" t="s">
+        <v>306</v>
+      </c>
+      <c r="K43" t="s">
+        <v>332</v>
+      </c>
+      <c r="L43" t="s">
+        <v>325</v>
+      </c>
+      <c r="M43" t="s">
+        <v>41</v>
+      </c>
+      <c r="N43" t="s">
+        <v>40</v>
+      </c>
+      <c r="O43" t="s">
+        <v>40</v>
+      </c>
+      <c r="P43" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q43" s="43">
+        <v>46275</v>
+      </c>
+      <c r="R43" s="19">
+        <f t="shared" ref="R43:R74" ca="1" si="2">IF(E43="","",TODAY()-E43)</f>
+        <v>0</v>
       </c>
       <c r="S43" s="23"/>
       <c r="T43" s="23"/>
-      <c r="U43" s="7"/>
-      <c r="V43" s="28"/>
+      <c r="U43" s="43">
+        <v>46287</v>
+      </c>
+      <c r="V43" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="44" spans="1:22">
-      <c r="A44" s="10"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="23"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="26"/>
-      <c r="J44" s="26"/>
-      <c r="K44" s="26"/>
-      <c r="L44" s="26"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="11"/>
-      <c r="O44" s="11"/>
-      <c r="P44" s="11"/>
-      <c r="Q44" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="R44" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
+      <c r="A44" t="s">
+        <v>253</v>
+      </c>
+      <c r="B44" t="s">
+        <v>262</v>
+      </c>
+      <c r="C44" s="43">
+        <v>46273</v>
+      </c>
+      <c r="D44" s="43">
+        <v>46273</v>
+      </c>
+      <c r="E44" s="43">
+        <v>46274</v>
+      </c>
+      <c r="F44" t="s">
+        <v>268</v>
+      </c>
+      <c r="G44" t="s">
+        <v>123</v>
+      </c>
+      <c r="H44" t="s">
+        <v>283</v>
+      </c>
+      <c r="I44" t="s">
+        <v>294</v>
+      </c>
+      <c r="J44" t="s">
+        <v>307</v>
+      </c>
+      <c r="K44" t="s">
+        <v>333</v>
+      </c>
+      <c r="L44" t="s">
+        <v>325</v>
+      </c>
+      <c r="M44" t="s">
+        <v>45</v>
+      </c>
+      <c r="N44" t="s">
+        <v>40</v>
+      </c>
+      <c r="O44" t="s">
+        <v>40</v>
+      </c>
+      <c r="P44" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q44" s="43">
+        <v>46275</v>
+      </c>
+      <c r="R44" s="19">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="S44" s="23"/>
       <c r="T44" s="23"/>
-      <c r="U44" s="7"/>
-      <c r="V44" s="28"/>
+      <c r="U44" s="43">
+        <v>46287</v>
+      </c>
+      <c r="V44" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="45" spans="1:22">
-      <c r="A45" s="10"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="23"/>
-      <c r="H45" s="11"/>
-      <c r="I45" s="26"/>
-      <c r="J45" s="26"/>
-      <c r="K45" s="26"/>
-      <c r="L45" s="26"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="11"/>
-      <c r="O45" s="11"/>
-      <c r="P45" s="11"/>
-      <c r="Q45" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="R45" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
+      <c r="A45" t="s">
+        <v>254</v>
+      </c>
+      <c r="B45" t="s">
+        <v>262</v>
+      </c>
+      <c r="C45" s="43">
+        <v>46273</v>
+      </c>
+      <c r="D45" s="43">
+        <v>46273</v>
+      </c>
+      <c r="E45" s="43">
+        <v>46274</v>
+      </c>
+      <c r="F45" t="s">
+        <v>269</v>
+      </c>
+      <c r="G45" t="s">
+        <v>277</v>
+      </c>
+      <c r="H45" t="s">
+        <v>284</v>
+      </c>
+      <c r="I45" t="s">
+        <v>295</v>
+      </c>
+      <c r="J45" t="s">
+        <v>308</v>
+      </c>
+      <c r="K45" t="s">
+        <v>334</v>
+      </c>
+      <c r="L45" t="s">
+        <v>325</v>
+      </c>
+      <c r="M45" t="s">
+        <v>45</v>
+      </c>
+      <c r="N45" t="s">
+        <v>40</v>
+      </c>
+      <c r="O45" t="s">
+        <v>40</v>
+      </c>
+      <c r="P45" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q45" s="43">
+        <v>46275</v>
+      </c>
+      <c r="R45" s="19">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="S45" s="23"/>
       <c r="T45" s="23"/>
-      <c r="U45" s="7"/>
-      <c r="V45" s="28"/>
+      <c r="U45" s="43">
+        <v>46287</v>
+      </c>
+      <c r="V45" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="46" spans="1:22">
-      <c r="A46" s="10"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="23"/>
-      <c r="G46" s="23"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="26"/>
-      <c r="J46" s="26"/>
-      <c r="K46" s="26"/>
-      <c r="L46" s="26"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="11"/>
-      <c r="O46" s="11"/>
-      <c r="P46" s="11"/>
-      <c r="Q46" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="R46" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
+      <c r="A46" t="s">
+        <v>255</v>
+      </c>
+      <c r="B46" t="s">
+        <v>262</v>
+      </c>
+      <c r="C46" s="43">
+        <v>46273</v>
+      </c>
+      <c r="D46" s="43">
+        <v>46273</v>
+      </c>
+      <c r="E46" s="43">
+        <v>46274</v>
+      </c>
+      <c r="F46" t="s">
+        <v>270</v>
+      </c>
+      <c r="G46" t="s">
+        <v>114</v>
+      </c>
+      <c r="H46" t="s">
+        <v>285</v>
+      </c>
+      <c r="I46" t="s">
+        <v>296</v>
+      </c>
+      <c r="J46" t="s">
+        <v>309</v>
+      </c>
+      <c r="K46" t="s">
+        <v>335</v>
+      </c>
+      <c r="L46" t="s">
+        <v>325</v>
+      </c>
+      <c r="M46" t="s">
+        <v>45</v>
+      </c>
+      <c r="N46" t="s">
+        <v>40</v>
+      </c>
+      <c r="O46" t="s">
+        <v>40</v>
+      </c>
+      <c r="P46" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q46" s="43">
+        <v>46275</v>
+      </c>
+      <c r="R46" s="19">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="S46" s="23"/>
       <c r="T46" s="23"/>
-      <c r="U46" s="7"/>
-      <c r="V46" s="28"/>
+      <c r="U46" s="43">
+        <v>46279</v>
+      </c>
+      <c r="V46" t="s">
+        <v>355</v>
+      </c>
     </row>
     <row r="47" spans="1:22">
-      <c r="A47" s="10"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="23"/>
-      <c r="G47" s="23"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="26"/>
-      <c r="J47" s="26"/>
-      <c r="K47" s="26"/>
-      <c r="L47" s="26"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="11"/>
-      <c r="O47" s="11"/>
-      <c r="P47" s="11"/>
-      <c r="Q47" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="R47" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
+      <c r="A47" t="s">
+        <v>256</v>
+      </c>
+      <c r="B47" t="s">
+        <v>262</v>
+      </c>
+      <c r="C47" s="43">
+        <v>46273</v>
+      </c>
+      <c r="D47" s="43">
+        <v>46273</v>
+      </c>
+      <c r="E47" s="43">
+        <v>46274</v>
+      </c>
+      <c r="F47" t="s">
+        <v>98</v>
+      </c>
+      <c r="G47" t="s">
+        <v>114</v>
+      </c>
+      <c r="H47" t="s">
+        <v>54</v>
+      </c>
+      <c r="I47" t="s">
+        <v>297</v>
+      </c>
+      <c r="J47" t="s">
+        <v>143</v>
+      </c>
+      <c r="K47" t="s">
+        <v>336</v>
+      </c>
+      <c r="L47" t="s">
+        <v>325</v>
+      </c>
+      <c r="M47" t="s">
+        <v>41</v>
+      </c>
+      <c r="N47" t="s">
+        <v>40</v>
+      </c>
+      <c r="O47" t="s">
+        <v>40</v>
+      </c>
+      <c r="P47" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q47" s="43">
+        <v>46275</v>
+      </c>
+      <c r="R47" s="19">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="S47" s="23"/>
       <c r="T47" s="23"/>
-      <c r="U47" s="7"/>
-      <c r="V47" s="28"/>
+      <c r="U47" t="s">
+        <v>342</v>
+      </c>
+      <c r="V47" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="48" spans="1:22">
-      <c r="A48" s="10"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="23"/>
-      <c r="G48" s="23"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="26"/>
-      <c r="J48" s="26"/>
-      <c r="K48" s="26"/>
-      <c r="L48" s="26"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="11"/>
-      <c r="O48" s="11"/>
-      <c r="P48" s="11"/>
-      <c r="Q48" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="A48" t="s">
+        <v>257</v>
+      </c>
+      <c r="B48" t="s">
+        <v>262</v>
+      </c>
+      <c r="C48" s="43">
+        <v>46273</v>
+      </c>
+      <c r="D48" s="43">
+        <v>46273</v>
+      </c>
+      <c r="F48" t="s">
+        <v>112</v>
+      </c>
+      <c r="G48" t="s">
+        <v>278</v>
+      </c>
+      <c r="H48" t="s">
+        <v>62</v>
+      </c>
+      <c r="I48" t="s">
+        <v>298</v>
+      </c>
+      <c r="J48" t="s">
+        <v>310</v>
+      </c>
+      <c r="K48" t="s">
+        <v>337</v>
+      </c>
+      <c r="L48" t="s">
+        <v>325</v>
+      </c>
+      <c r="M48" t="s">
+        <v>45</v>
+      </c>
+      <c r="N48" t="s">
+        <v>40</v>
+      </c>
+      <c r="O48" t="s">
+        <v>44</v>
+      </c>
+      <c r="P48" t="s">
+        <v>57</v>
       </c>
       <c r="R48" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S48" s="23"/>
       <c r="T48" s="23"/>
-      <c r="U48" s="7"/>
-      <c r="V48" s="28"/>
+      <c r="U48" s="43">
+        <v>46287</v>
+      </c>
+      <c r="V48" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="49" spans="1:22">
-      <c r="A49" s="10"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="23"/>
-      <c r="H49" s="11"/>
-      <c r="I49" s="26"/>
-      <c r="J49" s="26"/>
-      <c r="K49" s="26"/>
-      <c r="L49" s="26"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="11"/>
-      <c r="O49" s="11"/>
-      <c r="P49" s="11"/>
-      <c r="Q49" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="R49" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
+      <c r="A49" t="s">
+        <v>258</v>
+      </c>
+      <c r="B49" t="s">
+        <v>262</v>
+      </c>
+      <c r="C49" s="43">
+        <v>46273</v>
+      </c>
+      <c r="D49" s="43">
+        <v>46273</v>
+      </c>
+      <c r="E49" s="43">
+        <v>46274</v>
+      </c>
+      <c r="F49" t="s">
+        <v>112</v>
+      </c>
+      <c r="G49" t="s">
+        <v>279</v>
+      </c>
+      <c r="H49" t="s">
+        <v>286</v>
+      </c>
+      <c r="I49" t="s">
+        <v>299</v>
+      </c>
+      <c r="J49" t="s">
+        <v>311</v>
+      </c>
+      <c r="K49" t="s">
+        <v>338</v>
+      </c>
+      <c r="L49" t="s">
+        <v>325</v>
+      </c>
+      <c r="M49" t="s">
+        <v>45</v>
+      </c>
+      <c r="N49" t="s">
+        <v>40</v>
+      </c>
+      <c r="O49" t="s">
+        <v>40</v>
+      </c>
+      <c r="P49" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q49" s="43">
+        <v>46275</v>
+      </c>
+      <c r="R49" s="19">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="S49" s="23"/>
       <c r="T49" s="23"/>
-      <c r="U49" s="7"/>
-      <c r="V49" s="28"/>
+      <c r="U49" s="43">
+        <v>46279</v>
+      </c>
+      <c r="V49" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="50" spans="1:22">
-      <c r="A50" s="10"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="23"/>
-      <c r="G50" s="23"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="26"/>
-      <c r="J50" s="26"/>
-      <c r="K50" s="26"/>
-      <c r="L50" s="26"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="11"/>
-      <c r="O50" s="11"/>
-      <c r="P50" s="11"/>
-      <c r="Q50" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="R50" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
+      <c r="A50" t="s">
+        <v>259</v>
+      </c>
+      <c r="B50" t="s">
+        <v>262</v>
+      </c>
+      <c r="C50" s="43">
+        <v>46273</v>
+      </c>
+      <c r="D50" s="43">
+        <v>46273</v>
+      </c>
+      <c r="E50" s="43">
+        <v>46274</v>
+      </c>
+      <c r="F50" t="s">
+        <v>271</v>
+      </c>
+      <c r="G50" t="s">
+        <v>280</v>
+      </c>
+      <c r="H50" t="s">
+        <v>138</v>
+      </c>
+      <c r="I50" t="s">
+        <v>300</v>
+      </c>
+      <c r="J50" t="s">
+        <v>306</v>
+      </c>
+      <c r="K50" t="s">
+        <v>339</v>
+      </c>
+      <c r="L50" t="s">
+        <v>325</v>
+      </c>
+      <c r="M50" t="s">
+        <v>41</v>
+      </c>
+      <c r="N50" t="s">
+        <v>40</v>
+      </c>
+      <c r="O50" t="s">
+        <v>40</v>
+      </c>
+      <c r="P50" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q50" s="43">
+        <v>46275</v>
+      </c>
+      <c r="R50" s="19">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="S50" s="23"/>
       <c r="T50" s="23"/>
-      <c r="U50" s="7"/>
-      <c r="V50" s="28"/>
+      <c r="U50" s="43">
+        <v>46287</v>
+      </c>
+      <c r="V50" t="s">
+        <v>359</v>
+      </c>
     </row>
     <row r="51" spans="1:22">
-      <c r="A51" s="10"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="23"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="26"/>
-      <c r="J51" s="26"/>
-      <c r="K51" s="26"/>
-      <c r="L51" s="26"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="11"/>
-      <c r="O51" s="11"/>
-      <c r="P51" s="11"/>
-      <c r="Q51" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="R51" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
+      <c r="A51" t="s">
+        <v>260</v>
+      </c>
+      <c r="B51" t="s">
+        <v>262</v>
+      </c>
+      <c r="C51" s="43">
+        <v>46273</v>
+      </c>
+      <c r="D51" s="43">
+        <v>46273</v>
+      </c>
+      <c r="E51" s="43">
+        <v>46274</v>
+      </c>
+      <c r="F51" t="s">
+        <v>272</v>
+      </c>
+      <c r="G51" t="s">
+        <v>114</v>
+      </c>
+      <c r="H51" t="s">
+        <v>287</v>
+      </c>
+      <c r="I51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J51" t="s">
+        <v>312</v>
+      </c>
+      <c r="K51" t="s">
+        <v>340</v>
+      </c>
+      <c r="L51" t="s">
+        <v>325</v>
+      </c>
+      <c r="M51" t="s">
+        <v>45</v>
+      </c>
+      <c r="N51" t="s">
+        <v>40</v>
+      </c>
+      <c r="O51" t="s">
+        <v>40</v>
+      </c>
+      <c r="P51" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q51" s="43">
+        <v>46275</v>
+      </c>
+      <c r="R51" s="19">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="S51" s="23"/>
       <c r="T51" s="23"/>
-      <c r="U51" s="7"/>
-      <c r="V51" s="28"/>
+      <c r="U51" s="43">
+        <v>46287</v>
+      </c>
+      <c r="V51" t="s">
+        <v>360</v>
+      </c>
     </row>
     <row r="52" spans="1:22">
-      <c r="A52" s="10"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="11"/>
-      <c r="I52" s="26"/>
-      <c r="J52" s="26"/>
-      <c r="K52" s="26"/>
-      <c r="L52" s="26"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="11"/>
-      <c r="O52" s="11"/>
-      <c r="P52" s="11"/>
-      <c r="Q52" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="R52" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
+      <c r="A52" t="s">
+        <v>261</v>
+      </c>
+      <c r="B52" t="s">
+        <v>262</v>
+      </c>
+      <c r="C52" s="43">
+        <v>46273</v>
+      </c>
+      <c r="D52" s="43">
+        <v>46273</v>
+      </c>
+      <c r="E52" s="43">
+        <v>46274</v>
+      </c>
+      <c r="F52" t="s">
+        <v>273</v>
+      </c>
+      <c r="G52" t="s">
+        <v>114</v>
+      </c>
+      <c r="H52" t="s">
+        <v>138</v>
+      </c>
+      <c r="I52" t="s">
+        <v>302</v>
+      </c>
+      <c r="J52" t="s">
+        <v>306</v>
+      </c>
+      <c r="K52" t="s">
+        <v>341</v>
+      </c>
+      <c r="L52" t="s">
+        <v>325</v>
+      </c>
+      <c r="M52" t="s">
+        <v>41</v>
+      </c>
+      <c r="N52" t="s">
+        <v>40</v>
+      </c>
+      <c r="O52" t="s">
+        <v>40</v>
+      </c>
+      <c r="P52" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q52" s="43">
+        <v>46275</v>
+      </c>
+      <c r="R52" s="19">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="S52" s="23"/>
       <c r="T52" s="23"/>
-      <c r="U52" s="7"/>
-      <c r="V52" s="28"/>
+      <c r="U52" s="43">
+        <v>46287</v>
+      </c>
+      <c r="V52" t="s">
+        <v>361</v>
+      </c>
     </row>
     <row r="53" spans="1:22">
       <c r="A53" s="10"/>
@@ -3789,11 +4809,11 @@
       <c r="O53" s="11"/>
       <c r="P53" s="11"/>
       <c r="Q53" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="Q43:Q74" si="3">IF(E53="","",E53+1)</f>
         <v/>
       </c>
       <c r="R53" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S53" s="23"/>
@@ -3819,11 +4839,11 @@
       <c r="O54" s="11"/>
       <c r="P54" s="11"/>
       <c r="Q54" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R54" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S54" s="23"/>
@@ -3849,11 +4869,11 @@
       <c r="O55" s="11"/>
       <c r="P55" s="11"/>
       <c r="Q55" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R55" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S55" s="23"/>
@@ -3879,11 +4899,11 @@
       <c r="O56" s="11"/>
       <c r="P56" s="11"/>
       <c r="Q56" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R56" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S56" s="23"/>
@@ -3909,11 +4929,11 @@
       <c r="O57" s="11"/>
       <c r="P57" s="11"/>
       <c r="Q57" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R57" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S57" s="23"/>
@@ -3939,11 +4959,11 @@
       <c r="O58" s="11"/>
       <c r="P58" s="11"/>
       <c r="Q58" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R58" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S58" s="23"/>
@@ -3969,11 +4989,11 @@
       <c r="O59" s="11"/>
       <c r="P59" s="11"/>
       <c r="Q59" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R59" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S59" s="23"/>
@@ -3999,11 +5019,11 @@
       <c r="O60" s="11"/>
       <c r="P60" s="11"/>
       <c r="Q60" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R60" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S60" s="23"/>
@@ -4029,11 +5049,11 @@
       <c r="O61" s="11"/>
       <c r="P61" s="11"/>
       <c r="Q61" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R61" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S61" s="23"/>
@@ -4059,11 +5079,11 @@
       <c r="O62" s="11"/>
       <c r="P62" s="11"/>
       <c r="Q62" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R62" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S62" s="23"/>
@@ -4089,11 +5109,11 @@
       <c r="O63" s="11"/>
       <c r="P63" s="11"/>
       <c r="Q63" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R63" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S63" s="23"/>
@@ -4119,11 +5139,11 @@
       <c r="O64" s="11"/>
       <c r="P64" s="11"/>
       <c r="Q64" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R64" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S64" s="23"/>
@@ -4149,11 +5169,11 @@
       <c r="O65" s="11"/>
       <c r="P65" s="11"/>
       <c r="Q65" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R65" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S65" s="23"/>
@@ -4179,11 +5199,11 @@
       <c r="O66" s="11"/>
       <c r="P66" s="11"/>
       <c r="Q66" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R66" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S66" s="23"/>
@@ -4209,11 +5229,11 @@
       <c r="O67" s="11"/>
       <c r="P67" s="11"/>
       <c r="Q67" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R67" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S67" s="23"/>
@@ -4239,11 +5259,11 @@
       <c r="O68" s="11"/>
       <c r="P68" s="11"/>
       <c r="Q68" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R68" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S68" s="23"/>
@@ -4269,11 +5289,11 @@
       <c r="O69" s="11"/>
       <c r="P69" s="11"/>
       <c r="Q69" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R69" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S69" s="23"/>
@@ -4299,11 +5319,11 @@
       <c r="O70" s="11"/>
       <c r="P70" s="11"/>
       <c r="Q70" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R70" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S70" s="23"/>
@@ -4329,11 +5349,11 @@
       <c r="O71" s="11"/>
       <c r="P71" s="11"/>
       <c r="Q71" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R71" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S71" s="23"/>
@@ -4359,11 +5379,11 @@
       <c r="O72" s="11"/>
       <c r="P72" s="11"/>
       <c r="Q72" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R72" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S72" s="23"/>
@@ -4389,11 +5409,11 @@
       <c r="O73" s="11"/>
       <c r="P73" s="11"/>
       <c r="Q73" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R73" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S73" s="23"/>
@@ -4419,11 +5439,11 @@
       <c r="O74" s="11"/>
       <c r="P74" s="11"/>
       <c r="Q74" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R74" s="19" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="S74" s="23"/>
@@ -8599,16 +9619,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="32" t="s">
@@ -8727,16 +9747,16 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="15">
-      <c r="A18" s="50" t="s">
+      <c r="A18" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="50"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
     </row>
     <row r="19" spans="1:8" ht="29.25">
       <c r="A19" s="33" t="s">

--- a/dados/Registro_Alteracoes_Amazon_Ads_Winnet.xlsx
+++ b/dados/Registro_Alteracoes_Amazon_Ads_Winnet.xlsx
@@ -15,12 +15,12 @@
     <sheet name="Registro_Alteracoes" sheetId="1" r:id="rId1"/>
     <sheet name="Listas" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="405">
   <si>
     <t>REGISTRO DE ALTERAÇÕES — AMAZON ADS | WINNET METAIS</t>
   </si>
@@ -1116,6 +1116,135 @@
   </si>
   <si>
     <t>A auto PXP ganhou 1 compra entre 07/09 e 09/09 (+R$ 151,10) e o Extintor ganhou outra (+R$ 302,20). Export vitalício não separa data — pode ser venda nova ou maturação de atribuição. Resolver em 14/09 contra o Registro_Vendas. NÃO INFERIDO</t>
+  </si>
+  <si>
+    <t>Sem atividade desde 17/08. O ASIN B0H5Z1XK3V não aparece no Business Report da Era (zero sessão)</t>
+  </si>
+  <si>
+    <t>Superada pela O4-R03 no mesmo dia</t>
+  </si>
+  <si>
+    <t>Reativada, mas zero impressão de 18/08 a 07/09 (o 30d registra 172 impressões e 1 clique, só entre 11 e 17/08). Conferido no console em 09/09: o ANÚNCIO dentro da campanha está suspenso por política</t>
+  </si>
+  <si>
+    <t>Export de 08/09: ajuste de topo 0,75 vigente. Era: 1 clique e 1 venda de R$ 203,54. ACOS 30d de 1,4%. Termos em rank 1 com share 100%</t>
+  </si>
+  <si>
+    <t>Todos os termos servidos via substitutes terminam em 25/08 ou antes; na Era só houve entrega pela loose-match</t>
+  </si>
+  <si>
+    <t>Nenhum dos 18 termos negativados reaparece na Era</t>
+  </si>
+  <si>
+    <t>Sem atividade após 25/08. O SKU teve 13 sessões e zero unidade na Era; Relâmpago de −10% em curso</t>
+  </si>
+  <si>
+    <t>Era: 4 cliques, R$ 2,51, zero venda. Vitalício: 18 cliques e zero venda em 32 alvos</t>
+  </si>
+  <si>
+    <t>Era: 1 clique, R$ 0,99, zero venda. Vitalício: 8 cliques e zero venda em 83 alvos</t>
+  </si>
+  <si>
+    <t>Não vigorou em 25/08 — a campanha foi encontrada ATIVA em 31/08 e pausada no ato</t>
+  </si>
+  <si>
+    <t>Sem atividade após 25/08</t>
+  </si>
+  <si>
+    <t>Sem atividade após 25/08. O SKU teve 19 sessões e zero unidade na Era</t>
+  </si>
+  <si>
+    <t>Era: 2 cliques, R$ 2,02, zero venda</t>
+  </si>
+  <si>
+    <t>Gasto da Era: R$ 137,16 em 13 dias = R$ 10,55/dia, contra orçamento de R$ 90/dia (12%)</t>
+  </si>
+  <si>
+    <t>Impressões de 361 para 2.391 em 30d. Era: ~2.500 impressões, 1 clique, zero venda, CTR 0,13%</t>
+  </si>
+  <si>
+    <t>A 6B vendeu (R$ 265,80, 1ª venda da manual). L3070-B e Cinzeiros com zero clique na Era; Bituqueiras com 1</t>
+  </si>
+  <si>
+    <t>Pré-Era: 6 cliques em 15 dias, zero venda. Era: 11 cliques em 13 dias e 1 venda de R$ 265,80. CPC de 1,33 para 1,60. Controles fixos com 0 a 1 clique na Era</t>
+  </si>
+  <si>
+    <t>O lance padrão do grupo NÃO É USADO. Evidência: o export de segmentação de 25/08 e o console de 08/09 trazem os mesmos lances por segmentação (0,45 / 0,45 / 0,54 / 0,54). Se as segmentações seguissem o padrão, leriam 0,40 antes e 0,48 depois — nunca leram nenhum dos dois</t>
+  </si>
+  <si>
+    <t>Sem venda de SP-T na Era</t>
+  </si>
+  <si>
+    <t>Última atividade em 31/08; ausente da Era a partir daí</t>
+  </si>
+  <si>
+    <t>Janela pós começa em 08/09. Até 09/09: PG2460 vendeu em 07/09 (R$ 223,88) e PXP vendeu 2 vezes em 08/09 (R$ 302,20 e R$ 151,10), todas com Melhor Oferta de −10%</t>
+  </si>
+  <si>
+    <t>Dias de execução dentro da semana de 07 a 13/09</t>
+  </si>
+  <si>
+    <t>MANTIDA — a inelegibilidade persiste. Reativar somente com o anúncio liberado. Pausa por inelegibilidade, não conta como falha de desempenho (Playbook §30)</t>
+  </si>
+  <si>
+    <t>ENCERRADA (superada)</t>
+  </si>
+  <si>
+    <t>SEM EFEITO — a premissa da reativação (ASIN requalificado) era VERDADEIRA: o listing está ativo e o mesmo SKU segue anunciado pela Manual Bituqueiras (14 impressões, 20/08–04/09). O que não voltou foi o anúncio DENTRO desta campanha. Campanha pausada em O5-012</t>
+  </si>
+  <si>
+    <t>POSITIVO — o conserto vigorou. O volume dos termos exatos é baixo (métrica bruta, não inferir teto de mercado). A campanha ganhou uma 2ª venda vitalícia em 08/09 (PXP ×2, R$ 302,20)</t>
+  </si>
+  <si>
+    <t>EFETIVA NA SEGMENTAÇÃO — a substitutes parou de fato. Mas o CTR da campanha seguiu em ~0,06%, agora pela loose-match: o problema migrou de segmentação, não foi resolvido. Tratado em O5-010</t>
+  </si>
+  <si>
+    <t>EFETIVA</t>
+  </si>
+  <si>
+    <t>MANTIDA — retorno condicionado ao lote de correção de página</t>
+  </si>
+  <si>
+    <t>NEGATIVO — o radar não gerou amostra em 8 dias úteis após o +20%. Contrato de saída acionado; campanha pausada em O5-004</t>
+  </si>
+  <si>
+    <t>NEGATIVO — sem amostra. Contrato de saída acionado; campanha pausada em O5-005. A família PG vendeu por outro caminho: PG2460 pela Geral com Melhor Oferta em 07/09</t>
+  </si>
+  <si>
+    <t>SUPERADA por EC-002. Precedente que tornou obrigatória a conferência de estado pós-execução</t>
+  </si>
+  <si>
+    <t>MANTIDA</t>
+  </si>
+  <si>
+    <t>NEGATIVO — sem amostra; contrato acionado, campanha pausada em O5-006. ⚠️ CONTRAPESO VITALÍCIO: esta campanha TEM venda vitalícia de R$ 610,62 (pedido de 08/07, 3 un). A pausa se sustenta por redundância, não por ausência de histórico. CORRIGIR O TEXTO DO MOTIVO: PXM é suporte de extintor 6 kg, não porta-guarda-chuva</t>
+  </si>
+  <si>
+    <t>CONFIRMADA — o orçamento não é a restrição. Mantido em O5-003. Regra consolidada: ACOS abaixo do Objetivo não aciona a régua de orçamento quando a campanha consome fração do próprio teto</t>
+  </si>
+  <si>
+    <t>PARCIAL — a entrega destravou, a conversão não. O radar cumpriu seu objetivo declarado (gerar amostra de entrega) e revelou que o gargalo é CTR. Prorrogado como vigia por 1 Era em O5-007, com gatilho na O6</t>
+  </si>
+  <si>
+    <t>CONFIRMADA — ajustes derivados em O5-009 (L3070-B para dinâmico) e O5-015 (as três fixas mantidas por share 100%)</t>
+  </si>
+  <si>
+    <t>POSITIVO PRELIMINAR (n = 1 venda) — mantido em O5-008 e estendido à L3070-B. Veredito consolidado na O6. Ressalva: o custo real do termo vencedor é R$ 11,71 e não R$ 5,19, porque a perna L2025-B levou R$ 6,52 sem venda</t>
+  </si>
+  <si>
+    <t>INERTE — sem efeito operacional, confirmado por evidência e não por inferência. A escala real da Geral é por segmentação, tratada em O5-001 e O5-002. Fecha a pendência dos lances por segmentação</t>
+  </si>
+  <si>
+    <t>SEM EFEITO ISOLÁVEL (esperado) — a inclusão corrigiu uma lacuna de configuração, não uma alavanca de venda</t>
+  </si>
+  <si>
+    <t>EFETIVA — conserto da O4-006</t>
+  </si>
+  <si>
+    <t>NÃO AVALIÁVEL até 14/09. ACHADO JÁ CONFIRMADO: nos 3 pedidos o Ads registrou o valor COM desconto — a Melhor Oferta é atribuída ao PREÇO DA OFERTA. A atribuição a preço de tabela vale para a promoção de quantidade, que é outro mecanismo</t>
+  </si>
+  <si>
+    <t>NÃO AVALIÁVEL até 14/09</t>
   </si>
 </sst>
 </file>
@@ -1350,7 +1479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1415,9 +1544,6 @@
     <xf numFmtId="1" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1471,11 +1597,9 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1497,12 +1621,153 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9A3412"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFED7AA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF991B1B"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF374151"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF3F4F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF166534"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF3730A3"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE0E7FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1E40AF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9A3412"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFED7AA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF991B1B"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF374151"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF3F4F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF166534"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF3730A3"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE0E7FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1E40AF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1835,82 +2100,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="45"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="44"/>
     </row>
     <row r="2" spans="1:22" ht="30" customHeight="1">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="46"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
+      <c r="V2" s="45"/>
     </row>
     <row r="3" spans="1:22" ht="27.95" customHeight="1">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="46"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="46"/>
+      <c r="T3" s="46"/>
+      <c r="U3" s="46"/>
+      <c r="V3" s="46"/>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1" t="s">
@@ -1931,23 +2196,23 @@
       <c r="F5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="48" t="s">
+      <c r="H5" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="48"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
+      <c r="Q5" s="47"/>
+      <c r="R5" s="47"/>
+      <c r="S5" s="47"/>
+      <c r="T5" s="47"/>
+      <c r="U5" s="47"/>
+      <c r="V5" s="47"/>
     </row>
     <row r="6" spans="1:22" ht="26.1" customHeight="1">
       <c r="A6" s="2">
@@ -1968,53 +2233,53 @@
       </c>
       <c r="E6" s="3">
         <f>COUNTIF(P11:P210,"EXECUTADA - EM MATURAÇÃO")</f>
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F6" s="4">
         <f>COUNTIF(P11:P210,"EXECUTADA - AVALIADA")</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="48"/>
-      <c r="O6" s="48"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="48"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="48"/>
-      <c r="U6" s="48"/>
-      <c r="V6" s="48"/>
+        <v>21</v>
+      </c>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="47"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="47"/>
+      <c r="T6" s="47"/>
+      <c r="U6" s="47"/>
+      <c r="V6" s="47"/>
     </row>
     <row r="8" spans="1:22" ht="21.95" customHeight="1">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="49"/>
-      <c r="M8" s="49"/>
-      <c r="N8" s="49"/>
-      <c r="O8" s="49"/>
-      <c r="P8" s="49"/>
-      <c r="Q8" s="49"/>
-      <c r="R8" s="49"/>
-      <c r="S8" s="49"/>
-      <c r="T8" s="49"/>
-      <c r="U8" s="49"/>
-      <c r="V8" s="49"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="48"/>
+      <c r="R8" s="48"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="48"/>
+      <c r="V8" s="48"/>
     </row>
     <row r="10" spans="1:22" ht="38.1" customHeight="1">
       <c r="A10" s="5" t="s">
@@ -2085,38 +2350,38 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="85.5">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41">
+      <c r="C11" s="40"/>
+      <c r="D11" s="40">
         <v>46251</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="40">
         <v>46251</v>
       </c>
-      <c r="F11" s="40" t="s">
+      <c r="F11" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="G11" s="40" t="s">
+      <c r="G11" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="H11" s="40" t="s">
+      <c r="H11" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="I11" s="40" t="s">
+      <c r="I11" s="39" t="s">
         <v>141</v>
       </c>
-      <c r="J11" s="40" t="s">
+      <c r="J11" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="K11" s="25" t="s">
+      <c r="K11" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="L11" s="25" t="s">
+      <c r="L11" s="24" t="s">
         <v>166</v>
       </c>
       <c r="M11" s="9" t="s">
@@ -2129,56 +2394,60 @@
         <v>40</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Q11" s="16">
-        <f t="shared" ref="Q11:Q42" si="0">IF(E11="","",E11+1)</f>
+        <f t="shared" ref="Q11:Q33" si="0">IF(E11="","",E11+1)</f>
         <v>46252</v>
       </c>
       <c r="R11" s="17">
         <f t="shared" ref="R11:R42" ca="1" si="1">IF(E11="","",TODAY()-E11)</f>
         <v>23</v>
       </c>
-      <c r="S11" s="22"/>
-      <c r="T11" s="22"/>
+      <c r="S11" t="s">
+        <v>362</v>
+      </c>
+      <c r="T11" t="s">
+        <v>384</v>
+      </c>
       <c r="U11" s="6"/>
-      <c r="V11" s="39" t="s">
+      <c r="V11" s="38" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="28.5">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41">
+      <c r="C12" s="40"/>
+      <c r="D12" s="40">
         <v>46251</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="40">
         <v>46251</v>
       </c>
-      <c r="F12" s="40" t="s">
+      <c r="F12" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="40" t="s">
+      <c r="G12" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="H12" s="40" t="s">
+      <c r="H12" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="I12" s="40" t="s">
+      <c r="I12" s="39" t="s">
         <v>142</v>
       </c>
-      <c r="J12" s="40" t="s">
+      <c r="J12" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="K12" s="26" t="s">
+      <c r="K12" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="L12" s="26" t="s">
+      <c r="L12" s="25" t="s">
         <v>168</v>
       </c>
       <c r="M12" s="11" t="s">
@@ -2190,8 +2459,8 @@
       <c r="O12" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P12" s="11" t="s">
-        <v>47</v>
+      <c r="P12" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q12" s="18">
         <f t="shared" si="0"/>
@@ -2201,44 +2470,48 @@
         <f t="shared" ca="1" si="1"/>
         <v>23</v>
       </c>
-      <c r="S12" s="23"/>
-      <c r="T12" s="23"/>
+      <c r="S12" t="s">
+        <v>363</v>
+      </c>
+      <c r="T12" t="s">
+        <v>385</v>
+      </c>
       <c r="U12" s="7"/>
-      <c r="V12" s="28" t="s">
+      <c r="V12" s="27" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="57">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="41">
+      <c r="C13" s="40"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="40">
         <v>46259</v>
       </c>
-      <c r="F13" s="40" t="s">
+      <c r="F13" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="G13" s="40" t="s">
+      <c r="G13" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="H13" s="40" t="s">
+      <c r="H13" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="I13" s="40" t="s">
+      <c r="I13" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="J13" s="40" t="s">
+      <c r="J13" s="39" t="s">
         <v>142</v>
       </c>
-      <c r="K13" s="26" t="s">
+      <c r="K13" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="L13" s="26" t="s">
+      <c r="L13" s="25" t="s">
         <v>170</v>
       </c>
       <c r="M13" s="11" t="s">
@@ -2250,8 +2523,8 @@
       <c r="O13" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P13" s="11" t="s">
-        <v>47</v>
+      <c r="P13" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q13" s="18">
         <f t="shared" si="0"/>
@@ -2261,48 +2534,52 @@
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
-      <c r="S13" s="23"/>
-      <c r="T13" s="42"/>
+      <c r="S13" t="s">
+        <v>364</v>
+      </c>
+      <c r="T13" t="s">
+        <v>386</v>
+      </c>
       <c r="U13" s="7">
         <v>46273</v>
       </c>
-      <c r="V13" s="28" t="s">
+      <c r="V13" s="27" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="42.75">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41">
+      <c r="C14" s="40"/>
+      <c r="D14" s="40">
         <v>46251</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="40">
         <v>46259</v>
       </c>
-      <c r="F14" s="40" t="s">
+      <c r="F14" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="G14" s="40" t="s">
+      <c r="G14" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="H14" s="40" t="s">
+      <c r="H14" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="I14" s="40" t="s">
+      <c r="I14" s="39" t="s">
         <v>144</v>
       </c>
-      <c r="J14" s="40" t="s">
+      <c r="J14" s="39" t="s">
         <v>155</v>
       </c>
-      <c r="K14" s="26" t="s">
+      <c r="K14" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="L14" s="26" t="s">
+      <c r="L14" s="25" t="s">
         <v>172</v>
       </c>
       <c r="M14" s="11" t="s">
@@ -2314,8 +2591,8 @@
       <c r="O14" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P14" s="11" t="s">
-        <v>47</v>
+      <c r="P14" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q14" s="18">
         <f t="shared" si="0"/>
@@ -2325,50 +2602,54 @@
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
+      <c r="S14" t="s">
+        <v>365</v>
+      </c>
+      <c r="T14" t="s">
+        <v>387</v>
+      </c>
       <c r="U14" s="7">
         <v>46273</v>
       </c>
-      <c r="V14" s="28" t="s">
+      <c r="V14" s="27" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="57">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="41">
+      <c r="C15" s="40">
         <v>46259</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="40">
         <v>46259</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="40">
         <v>46259</v>
       </c>
-      <c r="F15" s="40" t="s">
+      <c r="F15" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="40" t="s">
+      <c r="G15" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="H15" s="40" t="s">
+      <c r="H15" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="I15" s="40" t="s">
+      <c r="I15" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="J15" s="40" t="s">
+      <c r="J15" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="K15" s="26" t="s">
+      <c r="K15" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="L15" s="26" t="s">
+      <c r="L15" s="25" t="s">
         <v>174</v>
       </c>
       <c r="M15" s="11" t="s">
@@ -2380,8 +2661,8 @@
       <c r="O15" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P15" s="11" t="s">
-        <v>47</v>
+      <c r="P15" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q15" s="18">
         <f t="shared" si="0"/>
@@ -2391,50 +2672,54 @@
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
-      <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="S15" t="s">
+        <v>366</v>
+      </c>
+      <c r="T15" t="s">
+        <v>388</v>
+      </c>
       <c r="U15" s="7">
         <v>46273</v>
       </c>
-      <c r="V15" s="28" t="s">
+      <c r="V15" s="27" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="57">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="40">
         <v>46259</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="40">
         <v>46259</v>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="40">
         <v>46259</v>
       </c>
-      <c r="F16" s="40" t="s">
+      <c r="F16" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="40" t="s">
+      <c r="G16" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="H16" s="40" t="s">
+      <c r="H16" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="I16" s="40" t="s">
+      <c r="I16" s="39" t="s">
         <v>146</v>
       </c>
-      <c r="J16" s="40" t="s">
+      <c r="J16" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="K16" s="26" t="s">
+      <c r="K16" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="L16" s="26" t="s">
+      <c r="L16" s="25" t="s">
         <v>176</v>
       </c>
       <c r="M16" s="11" t="s">
@@ -2446,8 +2731,8 @@
       <c r="O16" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P16" s="11" t="s">
-        <v>47</v>
+      <c r="P16" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q16" s="18">
         <f t="shared" si="0"/>
@@ -2457,50 +2742,54 @@
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
-      <c r="S16" s="23"/>
-      <c r="T16" s="23"/>
+      <c r="S16" t="s">
+        <v>367</v>
+      </c>
+      <c r="T16" t="s">
+        <v>389</v>
+      </c>
       <c r="U16" s="7">
         <v>46273</v>
       </c>
-      <c r="V16" s="28" t="s">
+      <c r="V16" s="27" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="85.5">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C17" s="41">
+      <c r="C17" s="40">
         <v>46259</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="40">
         <v>46259</v>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="40">
         <v>46259</v>
       </c>
-      <c r="F17" s="40" t="s">
+      <c r="F17" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="40" t="s">
+      <c r="G17" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="H17" s="40" t="s">
+      <c r="H17" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="I17" s="40" t="s">
+      <c r="I17" s="39" t="s">
         <v>147</v>
       </c>
-      <c r="J17" s="40" t="s">
+      <c r="J17" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="K17" s="26" t="s">
+      <c r="K17" s="25" t="s">
         <v>177</v>
       </c>
-      <c r="L17" s="26" t="s">
+      <c r="L17" s="25" t="s">
         <v>178</v>
       </c>
       <c r="M17" s="11" t="s">
@@ -2512,8 +2801,8 @@
       <c r="O17" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P17" s="11" t="s">
-        <v>47</v>
+      <c r="P17" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q17" s="18">
         <f t="shared" si="0"/>
@@ -2523,48 +2812,52 @@
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
-      <c r="S17" s="23"/>
-      <c r="T17" s="23"/>
+      <c r="S17" t="s">
+        <v>368</v>
+      </c>
+      <c r="T17" t="s">
+        <v>390</v>
+      </c>
       <c r="U17" s="7"/>
-      <c r="V17" s="28" t="s">
+      <c r="V17" s="27" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="42.75">
-      <c r="A18" s="40" t="s">
+      <c r="A18" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="40">
         <v>46259</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="40">
         <v>46259</v>
       </c>
-      <c r="E18" s="41">
+      <c r="E18" s="40">
         <v>46259</v>
       </c>
-      <c r="F18" s="40" t="s">
+      <c r="F18" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="G18" s="40" t="s">
+      <c r="G18" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="H18" s="40" t="s">
+      <c r="H18" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="I18" s="40" t="s">
+      <c r="I18" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="J18" s="40" t="s">
+      <c r="J18" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="K18" s="26" t="s">
+      <c r="K18" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="L18" s="26" t="s">
+      <c r="L18" s="25" t="s">
         <v>180</v>
       </c>
       <c r="M18" s="11" t="s">
@@ -2576,8 +2869,8 @@
       <c r="O18" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P18" s="11" t="s">
-        <v>47</v>
+      <c r="P18" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q18" s="18">
         <f t="shared" si="0"/>
@@ -2587,50 +2880,54 @@
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
-      <c r="S18" s="23"/>
-      <c r="T18" s="23"/>
+      <c r="S18" t="s">
+        <v>369</v>
+      </c>
+      <c r="T18" t="s">
+        <v>391</v>
+      </c>
       <c r="U18" s="7">
         <v>46273</v>
       </c>
-      <c r="V18" s="28" t="s">
+      <c r="V18" s="27" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="42.75">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C19" s="41">
+      <c r="C19" s="40">
         <v>46259</v>
       </c>
-      <c r="D19" s="41">
+      <c r="D19" s="40">
         <v>46259</v>
       </c>
-      <c r="E19" s="41">
+      <c r="E19" s="40">
         <v>46259</v>
       </c>
-      <c r="F19" s="40" t="s">
+      <c r="F19" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="G19" s="40" t="s">
+      <c r="G19" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="H19" s="40" t="s">
+      <c r="H19" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="I19" s="40" t="s">
+      <c r="I19" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="J19" s="40" t="s">
+      <c r="J19" s="39" t="s">
         <v>158</v>
       </c>
-      <c r="K19" s="26" t="s">
+      <c r="K19" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="L19" s="26" t="s">
+      <c r="L19" s="25" t="s">
         <v>180</v>
       </c>
       <c r="M19" s="11" t="s">
@@ -2642,8 +2939,8 @@
       <c r="O19" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P19" s="11" t="s">
-        <v>47</v>
+      <c r="P19" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q19" s="18">
         <f t="shared" si="0"/>
@@ -2653,50 +2950,54 @@
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
-      <c r="S19" s="23"/>
-      <c r="T19" s="23"/>
+      <c r="S19" t="s">
+        <v>370</v>
+      </c>
+      <c r="T19" t="s">
+        <v>392</v>
+      </c>
       <c r="U19" s="7">
         <v>46273</v>
       </c>
-      <c r="V19" s="28" t="s">
+      <c r="V19" s="27" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="42.75">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C20" s="41">
+      <c r="C20" s="40">
         <v>46259</v>
       </c>
-      <c r="D20" s="41">
+      <c r="D20" s="40">
         <v>46259</v>
       </c>
-      <c r="E20" s="41">
+      <c r="E20" s="40">
         <v>46259</v>
       </c>
-      <c r="F20" s="40" t="s">
+      <c r="F20" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="G20" s="40" t="s">
+      <c r="G20" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="H20" s="40" t="s">
+      <c r="H20" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="I20" s="40" t="s">
+      <c r="I20" s="39" t="s">
         <v>142</v>
       </c>
-      <c r="J20" s="40" t="s">
+      <c r="J20" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="K20" s="26" t="s">
+      <c r="K20" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="L20" s="26" t="s">
+      <c r="L20" s="25" t="s">
         <v>183</v>
       </c>
       <c r="M20" s="11" t="s">
@@ -2708,8 +3009,8 @@
       <c r="O20" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P20" s="11" t="s">
-        <v>47</v>
+      <c r="P20" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q20" s="18">
         <f t="shared" si="0"/>
@@ -2719,48 +3020,52 @@
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
-      <c r="S20" s="23"/>
-      <c r="T20" s="23"/>
+      <c r="S20" t="s">
+        <v>371</v>
+      </c>
+      <c r="T20" t="s">
+        <v>393</v>
+      </c>
       <c r="U20" s="7"/>
-      <c r="V20" s="28" t="s">
+      <c r="V20" s="27" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="42.75">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C21" s="41">
+      <c r="C21" s="40">
         <v>46259</v>
       </c>
-      <c r="D21" s="41">
+      <c r="D21" s="40">
         <v>46259</v>
       </c>
-      <c r="E21" s="41">
+      <c r="E21" s="40">
         <v>46259</v>
       </c>
-      <c r="F21" s="40" t="s">
+      <c r="F21" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="G21" s="40" t="s">
+      <c r="G21" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="H21" s="40" t="s">
+      <c r="H21" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="I21" s="40" t="s">
+      <c r="I21" s="39" t="s">
         <v>142</v>
       </c>
-      <c r="J21" s="40" t="s">
+      <c r="J21" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="K21" s="26" t="s">
+      <c r="K21" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="L21" s="26" t="s">
+      <c r="L21" s="25" t="s">
         <v>185</v>
       </c>
       <c r="M21" s="11" t="s">
@@ -2772,8 +3077,8 @@
       <c r="O21" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P21" s="11" t="s">
-        <v>47</v>
+      <c r="P21" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q21" s="18">
         <f t="shared" si="0"/>
@@ -2783,46 +3088,50 @@
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
-      <c r="S21" s="23"/>
-      <c r="T21" s="23"/>
+      <c r="S21" t="s">
+        <v>372</v>
+      </c>
+      <c r="T21" t="s">
+        <v>389</v>
+      </c>
       <c r="U21" s="7"/>
-      <c r="V21" s="28"/>
+      <c r="V21" s="27"/>
     </row>
     <row r="22" spans="1:22" ht="42.75">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="B22" s="40" t="s">
+      <c r="B22" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="41">
+      <c r="C22" s="40">
         <v>46259</v>
       </c>
-      <c r="D22" s="41">
+      <c r="D22" s="40">
         <v>46259</v>
       </c>
-      <c r="E22" s="41">
+      <c r="E22" s="40">
         <v>46259</v>
       </c>
-      <c r="F22" s="40" t="s">
+      <c r="F22" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="G22" s="40" t="s">
+      <c r="G22" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="H22" s="40" t="s">
+      <c r="H22" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="I22" s="40" t="s">
+      <c r="I22" s="39" t="s">
         <v>142</v>
       </c>
-      <c r="J22" s="40" t="s">
+      <c r="J22" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="K22" s="26" t="s">
+      <c r="K22" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="L22" s="26" t="s">
+      <c r="L22" s="25" t="s">
         <v>187</v>
       </c>
       <c r="M22" s="11" t="s">
@@ -2834,8 +3143,8 @@
       <c r="O22" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P22" s="11" t="s">
-        <v>47</v>
+      <c r="P22" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q22" s="18">
         <f t="shared" si="0"/>
@@ -2845,46 +3154,50 @@
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
-      <c r="S22" s="23"/>
-      <c r="T22" s="23"/>
+      <c r="S22" t="s">
+        <v>373</v>
+      </c>
+      <c r="T22" t="s">
+        <v>394</v>
+      </c>
       <c r="U22" s="7"/>
-      <c r="V22" s="28"/>
+      <c r="V22" s="27"/>
     </row>
     <row r="23" spans="1:22" ht="42.75">
-      <c r="A23" s="40" t="s">
+      <c r="A23" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="40" t="s">
+      <c r="B23" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="41">
+      <c r="C23" s="40">
         <v>46259</v>
       </c>
-      <c r="D23" s="41">
+      <c r="D23" s="40">
         <v>46259</v>
       </c>
-      <c r="E23" s="41">
+      <c r="E23" s="40">
         <v>46259</v>
       </c>
-      <c r="F23" s="40" t="s">
+      <c r="F23" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="G23" s="40" t="s">
+      <c r="G23" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="H23" s="40" t="s">
+      <c r="H23" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="I23" s="40" t="s">
+      <c r="I23" s="39" t="s">
         <v>142</v>
       </c>
-      <c r="J23" s="40" t="s">
+      <c r="J23" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="K23" s="26" t="s">
+      <c r="K23" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="L23" s="26" t="s">
+      <c r="L23" s="25" t="s">
         <v>185</v>
       </c>
       <c r="M23" s="11" t="s">
@@ -2896,8 +3209,8 @@
       <c r="O23" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P23" s="11" t="s">
-        <v>47</v>
+      <c r="P23" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q23" s="18">
         <f t="shared" si="0"/>
@@ -2907,46 +3220,50 @@
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
-      <c r="S23" s="23"/>
-      <c r="T23" s="23"/>
+      <c r="S23" t="s">
+        <v>372</v>
+      </c>
+      <c r="T23" t="s">
+        <v>389</v>
+      </c>
       <c r="U23" s="7"/>
-      <c r="V23" s="28"/>
+      <c r="V23" s="27"/>
     </row>
     <row r="24" spans="1:22" ht="42.75">
-      <c r="A24" s="40" t="s">
+      <c r="A24" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="41">
+      <c r="C24" s="40">
         <v>46259</v>
       </c>
-      <c r="D24" s="41">
+      <c r="D24" s="40">
         <v>46259</v>
       </c>
-      <c r="E24" s="41">
+      <c r="E24" s="40">
         <v>46259</v>
       </c>
-      <c r="F24" s="40" t="s">
+      <c r="F24" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="G24" s="40" t="s">
+      <c r="G24" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="H24" s="40" t="s">
+      <c r="H24" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="I24" s="40" t="s">
+      <c r="I24" s="39" t="s">
         <v>150</v>
       </c>
-      <c r="J24" s="40" t="s">
+      <c r="J24" s="39" t="s">
         <v>159</v>
       </c>
-      <c r="K24" s="26" t="s">
+      <c r="K24" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="L24" s="26" t="s">
+      <c r="L24" s="25" t="s">
         <v>190</v>
       </c>
       <c r="M24" s="11" t="s">
@@ -2958,8 +3275,8 @@
       <c r="O24" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P24" s="11" t="s">
-        <v>47</v>
+      <c r="P24" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q24" s="18">
         <f t="shared" si="0"/>
@@ -2969,50 +3286,54 @@
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
-      <c r="S24" s="23"/>
-      <c r="T24" s="23"/>
+      <c r="S24" t="s">
+        <v>374</v>
+      </c>
+      <c r="T24" t="s">
+        <v>395</v>
+      </c>
       <c r="U24" s="7">
         <v>46273</v>
       </c>
-      <c r="V24" s="28" t="s">
+      <c r="V24" s="27" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="57">
-      <c r="A25" s="40" t="s">
+      <c r="A25" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="41">
+      <c r="C25" s="40">
         <v>46259</v>
       </c>
-      <c r="D25" s="41">
+      <c r="D25" s="40">
         <v>46259</v>
       </c>
-      <c r="E25" s="41">
+      <c r="E25" s="40">
         <v>46259</v>
       </c>
-      <c r="F25" s="40" t="s">
+      <c r="F25" s="39" t="s">
         <v>109</v>
       </c>
-      <c r="G25" s="40" t="s">
+      <c r="G25" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="H25" s="40" t="s">
+      <c r="H25" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="I25" s="40" t="s">
+      <c r="I25" s="39" t="s">
         <v>151</v>
       </c>
-      <c r="J25" s="40" t="s">
+      <c r="J25" s="39" t="s">
         <v>160</v>
       </c>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="L25" s="26" t="s">
+      <c r="L25" s="25" t="s">
         <v>192</v>
       </c>
       <c r="M25" s="11" t="s">
@@ -3024,8 +3345,8 @@
       <c r="O25" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P25" s="11" t="s">
-        <v>47</v>
+      <c r="P25" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q25" s="18">
         <f t="shared" si="0"/>
@@ -3035,46 +3356,50 @@
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
-      <c r="S25" s="23"/>
-      <c r="T25" s="23"/>
+      <c r="S25" t="s">
+        <v>375</v>
+      </c>
+      <c r="T25" t="s">
+        <v>396</v>
+      </c>
       <c r="U25" s="7"/>
-      <c r="V25" s="28"/>
+      <c r="V25" s="27"/>
     </row>
     <row r="26" spans="1:22" ht="57">
-      <c r="A26" s="40" t="s">
+      <c r="A26" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C26" s="41">
+      <c r="C26" s="40">
         <v>46259</v>
       </c>
-      <c r="D26" s="41">
+      <c r="D26" s="40">
         <v>46259</v>
       </c>
-      <c r="E26" s="41">
+      <c r="E26" s="40">
         <v>46259</v>
       </c>
-      <c r="F26" s="40" t="s">
+      <c r="F26" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="G26" s="40" t="s">
+      <c r="G26" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="H26" s="40" t="s">
+      <c r="H26" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="I26" s="40" t="s">
+      <c r="I26" s="39" t="s">
         <v>152</v>
       </c>
-      <c r="J26" s="40" t="s">
+      <c r="J26" s="39" t="s">
         <v>161</v>
       </c>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="L26" s="26" t="s">
+      <c r="L26" s="25" t="s">
         <v>194</v>
       </c>
       <c r="M26" s="11" t="s">
@@ -3086,8 +3411,8 @@
       <c r="O26" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P26" s="11" t="s">
-        <v>47</v>
+      <c r="P26" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q26" s="18">
         <f t="shared" si="0"/>
@@ -3097,48 +3422,52 @@
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
-      <c r="S26" s="23"/>
-      <c r="T26" s="23"/>
+      <c r="S26" t="s">
+        <v>376</v>
+      </c>
+      <c r="T26" t="s">
+        <v>397</v>
+      </c>
       <c r="U26" s="7">
         <v>46273</v>
       </c>
-      <c r="V26" s="28"/>
+      <c r="V26" s="27"/>
     </row>
     <row r="27" spans="1:22" ht="57">
-      <c r="A27" s="40" t="s">
+      <c r="A27" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C27" s="41">
+      <c r="C27" s="40">
         <v>46259</v>
       </c>
-      <c r="D27" s="41">
+      <c r="D27" s="40">
         <v>46259</v>
       </c>
-      <c r="E27" s="41">
+      <c r="E27" s="40">
         <v>46259</v>
       </c>
-      <c r="F27" s="40" t="s">
+      <c r="F27" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="G27" s="40" t="s">
+      <c r="G27" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="H27" s="40" t="s">
+      <c r="H27" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="I27" s="40" t="s">
+      <c r="I27" s="39" t="s">
         <v>146</v>
       </c>
-      <c r="J27" s="40" t="s">
+      <c r="J27" s="39" t="s">
         <v>162</v>
       </c>
-      <c r="K27" s="26" t="s">
+      <c r="K27" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="L27" s="26" t="s">
+      <c r="L27" s="25" t="s">
         <v>196</v>
       </c>
       <c r="M27" s="11" t="s">
@@ -3150,8 +3479,8 @@
       <c r="O27" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P27" s="11" t="s">
-        <v>47</v>
+      <c r="P27" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q27" s="18">
         <f t="shared" si="0"/>
@@ -3161,50 +3490,54 @@
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
-      <c r="S27" s="23"/>
-      <c r="T27" s="23"/>
+      <c r="S27" t="s">
+        <v>377</v>
+      </c>
+      <c r="T27" t="s">
+        <v>398</v>
+      </c>
       <c r="U27" s="7">
         <v>46273</v>
       </c>
-      <c r="V27" s="28" t="s">
+      <c r="V27" s="27" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="71.25">
-      <c r="A28" s="40" t="s">
+      <c r="A28" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="40" t="s">
+      <c r="B28" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C28" s="41">
+      <c r="C28" s="40">
         <v>46259</v>
       </c>
-      <c r="D28" s="41">
+      <c r="D28" s="40">
         <v>46259</v>
       </c>
-      <c r="E28" s="41">
+      <c r="E28" s="40">
         <v>46259</v>
       </c>
-      <c r="F28" s="40" t="s">
+      <c r="F28" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="G28" s="40" t="s">
+      <c r="G28" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="H28" s="40" t="s">
+      <c r="H28" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="I28" s="40" t="s">
+      <c r="I28" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="J28" s="40" t="s">
+      <c r="J28" s="39" t="s">
         <v>163</v>
       </c>
-      <c r="K28" s="26" t="s">
+      <c r="K28" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="L28" s="26" t="s">
+      <c r="L28" s="25" t="s">
         <v>198</v>
       </c>
       <c r="M28" s="11" t="s">
@@ -3216,8 +3549,8 @@
       <c r="O28" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P28" s="11" t="s">
-        <v>47</v>
+      <c r="P28" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q28" s="18">
         <f t="shared" si="0"/>
@@ -3227,50 +3560,54 @@
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
-      <c r="S28" s="23"/>
-      <c r="T28" s="23"/>
+      <c r="S28" t="s">
+        <v>378</v>
+      </c>
+      <c r="T28" t="s">
+        <v>399</v>
+      </c>
       <c r="U28" s="7">
         <v>46273</v>
       </c>
-      <c r="V28" s="28" t="s">
+      <c r="V28" s="27" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="85.5">
-      <c r="A29" s="40" t="s">
+      <c r="A29" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="B29" s="40" t="s">
+      <c r="B29" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="41">
+      <c r="C29" s="40">
         <v>46259</v>
       </c>
-      <c r="D29" s="41">
+      <c r="D29" s="40">
         <v>46259</v>
       </c>
-      <c r="E29" s="41">
+      <c r="E29" s="40">
         <v>46259</v>
       </c>
-      <c r="F29" s="40" t="s">
+      <c r="F29" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="G29" s="40" t="s">
+      <c r="G29" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="40" t="s">
+      <c r="H29" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="I29" s="40" t="s">
+      <c r="I29" s="39" t="s">
         <v>154</v>
       </c>
-      <c r="J29" s="40" t="s">
+      <c r="J29" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="K29" s="26" t="s">
+      <c r="K29" s="25" t="s">
         <v>199</v>
       </c>
-      <c r="L29" s="26" t="s">
+      <c r="L29" s="25" t="s">
         <v>200</v>
       </c>
       <c r="M29" s="11" t="s">
@@ -3282,8 +3619,8 @@
       <c r="O29" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P29" s="11" t="s">
-        <v>47</v>
+      <c r="P29" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q29" s="18">
         <f t="shared" si="0"/>
@@ -3293,12 +3630,16 @@
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
-      <c r="S29" s="23"/>
-      <c r="T29" s="23"/>
+      <c r="S29" t="s">
+        <v>379</v>
+      </c>
+      <c r="T29" t="s">
+        <v>400</v>
+      </c>
       <c r="U29" s="7">
         <v>46273</v>
       </c>
-      <c r="V29" s="28" t="s">
+      <c r="V29" s="27" t="s">
         <v>213</v>
       </c>
     </row>
@@ -3309,13 +3650,13 @@
       <c r="B30" t="s">
         <v>215</v>
       </c>
-      <c r="C30" s="43">
+      <c r="C30" s="41">
         <v>46262</v>
       </c>
-      <c r="D30" s="43">
+      <c r="D30" s="41">
         <v>46262</v>
       </c>
-      <c r="E30" s="43">
+      <c r="E30" s="41">
         <v>46262</v>
       </c>
       <c r="F30" t="s">
@@ -3348,8 +3689,8 @@
       <c r="O30" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P30" s="11" t="s">
-        <v>47</v>
+      <c r="P30" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q30" s="18">
         <f t="shared" si="0"/>
@@ -3359,9 +3700,13 @@
         <f t="shared" ca="1" si="1"/>
         <v>12</v>
       </c>
-      <c r="S30" s="23"/>
-      <c r="T30" s="23"/>
-      <c r="U30" s="43">
+      <c r="S30" t="s">
+        <v>380</v>
+      </c>
+      <c r="T30" t="s">
+        <v>401</v>
+      </c>
+      <c r="U30" s="41">
         <v>46273</v>
       </c>
       <c r="V30" t="s">
@@ -3375,19 +3720,19 @@
       <c r="B31" t="s">
         <v>215</v>
       </c>
-      <c r="C31" s="43">
+      <c r="C31" s="41">
         <v>46265</v>
       </c>
-      <c r="D31" s="43">
+      <c r="D31" s="41">
         <v>46265</v>
       </c>
-      <c r="E31" s="43">
+      <c r="E31" s="41">
         <v>46265</v>
       </c>
       <c r="F31" t="s">
         <v>104</v>
       </c>
-      <c r="G31" s="23" t="s">
+      <c r="G31" s="22" t="s">
         <v>114</v>
       </c>
       <c r="H31" s="11" t="s">
@@ -3414,8 +3759,8 @@
       <c r="O31" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P31" s="11" t="s">
-        <v>47</v>
+      <c r="P31" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="Q31" s="18">
         <f t="shared" si="0"/>
@@ -3425,9 +3770,13 @@
         <f t="shared" ca="1" si="1"/>
         <v>9</v>
       </c>
-      <c r="S31" s="23"/>
-      <c r="T31" s="23"/>
-      <c r="U31" s="43">
+      <c r="S31" t="s">
+        <v>381</v>
+      </c>
+      <c r="T31" t="s">
+        <v>402</v>
+      </c>
+      <c r="U31" s="41">
         <v>46273</v>
       </c>
       <c r="V31" t="s">
@@ -3450,25 +3799,25 @@
       <c r="E32" s="12">
         <v>46267</v>
       </c>
-      <c r="F32" s="23" t="s">
+      <c r="F32" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="G32" s="44" t="s">
+      <c r="G32" s="42" t="s">
         <v>233</v>
       </c>
       <c r="H32" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="I32" s="26" t="s">
+      <c r="I32" s="25" t="s">
         <v>235</v>
       </c>
-      <c r="J32" s="26" t="s">
+      <c r="J32" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="K32" s="26" t="s">
+      <c r="K32" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="L32" s="26" t="s">
+      <c r="L32" s="25" t="s">
         <v>238</v>
       </c>
       <c r="M32" s="11" t="s">
@@ -3491,12 +3840,16 @@
         <f t="shared" ca="1" si="1"/>
         <v>7</v>
       </c>
-      <c r="S32" s="23"/>
-      <c r="T32" s="23"/>
+      <c r="S32" t="s">
+        <v>382</v>
+      </c>
+      <c r="T32" t="s">
+        <v>403</v>
+      </c>
       <c r="U32" s="7">
         <v>46279</v>
       </c>
-      <c r="V32" s="28"/>
+      <c r="V32" s="27"/>
     </row>
     <row r="33" spans="1:22" ht="57">
       <c r="A33" t="s">
@@ -3514,25 +3867,25 @@
       <c r="E33" s="12">
         <v>46267</v>
       </c>
-      <c r="F33" s="23" t="s">
+      <c r="F33" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="G33" s="23" t="s">
+      <c r="G33" s="22" t="s">
         <v>239</v>
       </c>
       <c r="H33" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="I33" s="26" t="s">
+      <c r="I33" s="25" t="s">
         <v>235</v>
       </c>
-      <c r="J33" s="26" t="s">
+      <c r="J33" s="25" t="s">
         <v>241</v>
       </c>
-      <c r="K33" s="26" t="s">
+      <c r="K33" s="25" t="s">
         <v>242</v>
       </c>
-      <c r="L33" s="26" t="s">
+      <c r="L33" s="25" t="s">
         <v>238</v>
       </c>
       <c r="M33" s="11" t="s">
@@ -3555,12 +3908,16 @@
         <f t="shared" ca="1" si="1"/>
         <v>7</v>
       </c>
-      <c r="S33" s="23"/>
-      <c r="T33" s="23"/>
+      <c r="S33" t="s">
+        <v>383</v>
+      </c>
+      <c r="T33" t="s">
+        <v>404</v>
+      </c>
       <c r="U33" s="7">
         <v>46279</v>
       </c>
-      <c r="V33" s="28"/>
+      <c r="V33" s="27"/>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
@@ -3569,13 +3926,13 @@
       <c r="B34" t="s">
         <v>215</v>
       </c>
-      <c r="C34" s="43">
+      <c r="C34" s="41">
         <v>46269</v>
       </c>
-      <c r="D34" s="43">
+      <c r="D34" s="41">
         <v>46269</v>
       </c>
-      <c r="E34" s="43">
+      <c r="E34" s="41">
         <v>46269</v>
       </c>
       <c r="F34" t="s">
@@ -3611,16 +3968,16 @@
       <c r="P34" t="s">
         <v>47</v>
       </c>
-      <c r="Q34" s="43">
+      <c r="Q34" s="41">
         <v>46270</v>
       </c>
       <c r="R34" s="19">
         <f t="shared" ca="1" si="1"/>
         <v>5</v>
       </c>
-      <c r="S34" s="23"/>
-      <c r="T34" s="23"/>
-      <c r="U34" s="43">
+      <c r="S34" s="22"/>
+      <c r="T34" s="22"/>
+      <c r="U34" s="41">
         <v>46283</v>
       </c>
       <c r="V34" t="s">
@@ -3634,13 +3991,13 @@
       <c r="B35" t="s">
         <v>215</v>
       </c>
-      <c r="C35" s="43">
+      <c r="C35" s="41">
         <v>46269</v>
       </c>
-      <c r="D35" s="43">
+      <c r="D35" s="41">
         <v>46269</v>
       </c>
-      <c r="E35" s="43">
+      <c r="E35" s="41">
         <v>46269</v>
       </c>
       <c r="F35" t="s">
@@ -3676,16 +4033,16 @@
       <c r="P35" t="s">
         <v>47</v>
       </c>
-      <c r="Q35" s="43">
+      <c r="Q35" s="41">
         <v>46270</v>
       </c>
       <c r="R35" s="19">
         <f t="shared" ca="1" si="1"/>
         <v>5</v>
       </c>
-      <c r="S35" s="23"/>
-      <c r="T35" s="23"/>
-      <c r="U35" s="43">
+      <c r="S35" s="22"/>
+      <c r="T35" s="22"/>
+      <c r="U35" s="41">
         <v>46283</v>
       </c>
       <c r="V35" t="s">
@@ -3699,13 +4056,13 @@
       <c r="B36" t="s">
         <v>262</v>
       </c>
-      <c r="C36" s="43">
+      <c r="C36" s="41">
         <v>46273</v>
       </c>
-      <c r="D36" s="43">
+      <c r="D36" s="41">
         <v>46273</v>
       </c>
-      <c r="E36" s="43">
+      <c r="E36" s="41">
         <v>46274</v>
       </c>
       <c r="F36" t="s">
@@ -3717,7 +4074,7 @@
       <c r="H36" t="s">
         <v>42</v>
       </c>
-      <c r="I36" s="52">
+      <c r="I36" s="43">
         <v>0.54</v>
       </c>
       <c r="J36" t="s">
@@ -3741,16 +4098,16 @@
       <c r="P36" t="s">
         <v>47</v>
       </c>
-      <c r="Q36" s="43">
+      <c r="Q36" s="41">
         <v>46275</v>
       </c>
       <c r="R36" s="19">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="S36" s="23"/>
-      <c r="T36" s="23"/>
-      <c r="U36" s="43">
+      <c r="S36" s="22"/>
+      <c r="T36" s="22"/>
+      <c r="U36" s="41">
         <v>46287</v>
       </c>
       <c r="V36" t="s">
@@ -3764,13 +4121,13 @@
       <c r="B37" t="s">
         <v>262</v>
       </c>
-      <c r="C37" s="43">
+      <c r="C37" s="41">
         <v>46273</v>
       </c>
-      <c r="D37" s="43">
+      <c r="D37" s="41">
         <v>46273</v>
       </c>
-      <c r="E37" s="43">
+      <c r="E37" s="41">
         <v>46274</v>
       </c>
       <c r="F37" t="s">
@@ -3782,7 +4139,7 @@
       <c r="H37" t="s">
         <v>38</v>
       </c>
-      <c r="I37" s="52">
+      <c r="I37" s="43">
         <v>0.45</v>
       </c>
       <c r="J37" t="s">
@@ -3806,16 +4163,16 @@
       <c r="P37" t="s">
         <v>47</v>
       </c>
-      <c r="Q37" s="43">
+      <c r="Q37" s="41">
         <v>46275</v>
       </c>
       <c r="R37" s="19">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="S37" s="23"/>
-      <c r="T37" s="23"/>
-      <c r="U37" s="43">
+      <c r="S37" s="22"/>
+      <c r="T37" s="22"/>
+      <c r="U37" s="41">
         <v>46287</v>
       </c>
       <c r="V37" t="s">
@@ -3829,13 +4186,13 @@
       <c r="B38" t="s">
         <v>262</v>
       </c>
-      <c r="C38" s="43">
+      <c r="C38" s="41">
         <v>46273</v>
       </c>
-      <c r="D38" s="43">
+      <c r="D38" s="41">
         <v>46273</v>
       </c>
-      <c r="E38" s="43">
+      <c r="E38" s="41">
         <v>46274</v>
       </c>
       <c r="F38" t="s">
@@ -3871,16 +4228,16 @@
       <c r="P38" t="s">
         <v>47</v>
       </c>
-      <c r="Q38" s="43">
+      <c r="Q38" s="41">
         <v>46275</v>
       </c>
       <c r="R38" s="19">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="S38" s="23"/>
-      <c r="T38" s="23"/>
-      <c r="U38" s="43">
+      <c r="S38" s="22"/>
+      <c r="T38" s="22"/>
+      <c r="U38" s="41">
         <v>46287</v>
       </c>
       <c r="V38" t="s">
@@ -3894,13 +4251,13 @@
       <c r="B39" t="s">
         <v>262</v>
       </c>
-      <c r="C39" s="43">
+      <c r="C39" s="41">
         <v>46273</v>
       </c>
-      <c r="D39" s="43">
+      <c r="D39" s="41">
         <v>46273</v>
       </c>
-      <c r="E39" s="43">
+      <c r="E39" s="41">
         <v>46274</v>
       </c>
       <c r="F39" t="s">
@@ -3936,16 +4293,16 @@
       <c r="P39" t="s">
         <v>47</v>
       </c>
-      <c r="Q39" s="43">
+      <c r="Q39" s="41">
         <v>46275</v>
       </c>
       <c r="R39" s="19">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="S39" s="23"/>
-      <c r="T39" s="23"/>
-      <c r="U39" s="43">
+      <c r="S39" s="22"/>
+      <c r="T39" s="22"/>
+      <c r="U39" s="41">
         <v>46287</v>
       </c>
       <c r="V39" t="s">
@@ -3959,13 +4316,13 @@
       <c r="B40" t="s">
         <v>262</v>
       </c>
-      <c r="C40" s="43">
+      <c r="C40" s="41">
         <v>46273</v>
       </c>
-      <c r="D40" s="43">
+      <c r="D40" s="41">
         <v>46273</v>
       </c>
-      <c r="E40" s="43">
+      <c r="E40" s="41">
         <v>46274</v>
       </c>
       <c r="F40" t="s">
@@ -4001,16 +4358,16 @@
       <c r="P40" t="s">
         <v>47</v>
       </c>
-      <c r="Q40" s="43">
+      <c r="Q40" s="41">
         <v>46275</v>
       </c>
       <c r="R40" s="19">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="S40" s="23"/>
-      <c r="T40" s="23"/>
-      <c r="U40" s="43">
+      <c r="S40" s="22"/>
+      <c r="T40" s="22"/>
+      <c r="U40" s="41">
         <v>46287</v>
       </c>
       <c r="V40" t="s">
@@ -4024,13 +4381,13 @@
       <c r="B41" t="s">
         <v>262</v>
       </c>
-      <c r="C41" s="43">
+      <c r="C41" s="41">
         <v>46273</v>
       </c>
-      <c r="D41" s="43">
+      <c r="D41" s="41">
         <v>46273</v>
       </c>
-      <c r="E41" s="43">
+      <c r="E41" s="41">
         <v>46274</v>
       </c>
       <c r="F41" t="s">
@@ -4066,16 +4423,16 @@
       <c r="P41" t="s">
         <v>47</v>
       </c>
-      <c r="Q41" s="43">
+      <c r="Q41" s="41">
         <v>46275</v>
       </c>
       <c r="R41" s="19">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="S41" s="23"/>
-      <c r="T41" s="23"/>
-      <c r="U41" s="43">
+      <c r="S41" s="22"/>
+      <c r="T41" s="22"/>
+      <c r="U41" s="41">
         <v>46287</v>
       </c>
       <c r="V41" t="s">
@@ -4089,13 +4446,13 @@
       <c r="B42" t="s">
         <v>262</v>
       </c>
-      <c r="C42" s="43">
+      <c r="C42" s="41">
         <v>46273</v>
       </c>
-      <c r="D42" s="43">
+      <c r="D42" s="41">
         <v>46273</v>
       </c>
-      <c r="E42" s="43">
+      <c r="E42" s="41">
         <v>46274</v>
       </c>
       <c r="F42" t="s">
@@ -4131,16 +4488,16 @@
       <c r="P42" t="s">
         <v>47</v>
       </c>
-      <c r="Q42" s="43">
+      <c r="Q42" s="41">
         <v>46275</v>
       </c>
       <c r="R42" s="19">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="S42" s="23"/>
-      <c r="T42" s="23"/>
-      <c r="U42" s="43">
+      <c r="S42" s="22"/>
+      <c r="T42" s="22"/>
+      <c r="U42" s="41">
         <v>46287</v>
       </c>
       <c r="V42" t="s">
@@ -4154,13 +4511,13 @@
       <c r="B43" t="s">
         <v>262</v>
       </c>
-      <c r="C43" s="43">
+      <c r="C43" s="41">
         <v>46273</v>
       </c>
-      <c r="D43" s="43">
+      <c r="D43" s="41">
         <v>46273</v>
       </c>
-      <c r="E43" s="43">
+      <c r="E43" s="41">
         <v>46274</v>
       </c>
       <c r="F43" t="s">
@@ -4196,16 +4553,16 @@
       <c r="P43" t="s">
         <v>47</v>
       </c>
-      <c r="Q43" s="43">
+      <c r="Q43" s="41">
         <v>46275</v>
       </c>
       <c r="R43" s="19">
         <f t="shared" ref="R43:R74" ca="1" si="2">IF(E43="","",TODAY()-E43)</f>
         <v>0</v>
       </c>
-      <c r="S43" s="23"/>
-      <c r="T43" s="23"/>
-      <c r="U43" s="43">
+      <c r="S43" s="22"/>
+      <c r="T43" s="22"/>
+      <c r="U43" s="41">
         <v>46287</v>
       </c>
       <c r="V43" t="s">
@@ -4219,13 +4576,13 @@
       <c r="B44" t="s">
         <v>262</v>
       </c>
-      <c r="C44" s="43">
+      <c r="C44" s="41">
         <v>46273</v>
       </c>
-      <c r="D44" s="43">
+      <c r="D44" s="41">
         <v>46273</v>
       </c>
-      <c r="E44" s="43">
+      <c r="E44" s="41">
         <v>46274</v>
       </c>
       <c r="F44" t="s">
@@ -4261,16 +4618,16 @@
       <c r="P44" t="s">
         <v>47</v>
       </c>
-      <c r="Q44" s="43">
+      <c r="Q44" s="41">
         <v>46275</v>
       </c>
       <c r="R44" s="19">
         <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="S44" s="23"/>
-      <c r="T44" s="23"/>
-      <c r="U44" s="43">
+      <c r="S44" s="22"/>
+      <c r="T44" s="22"/>
+      <c r="U44" s="41">
         <v>46287</v>
       </c>
       <c r="V44" t="s">
@@ -4284,13 +4641,13 @@
       <c r="B45" t="s">
         <v>262</v>
       </c>
-      <c r="C45" s="43">
+      <c r="C45" s="41">
         <v>46273</v>
       </c>
-      <c r="D45" s="43">
+      <c r="D45" s="41">
         <v>46273</v>
       </c>
-      <c r="E45" s="43">
+      <c r="E45" s="41">
         <v>46274</v>
       </c>
       <c r="F45" t="s">
@@ -4326,16 +4683,16 @@
       <c r="P45" t="s">
         <v>47</v>
       </c>
-      <c r="Q45" s="43">
+      <c r="Q45" s="41">
         <v>46275</v>
       </c>
       <c r="R45" s="19">
         <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="S45" s="23"/>
-      <c r="T45" s="23"/>
-      <c r="U45" s="43">
+      <c r="S45" s="22"/>
+      <c r="T45" s="22"/>
+      <c r="U45" s="41">
         <v>46287</v>
       </c>
       <c r="V45" t="s">
@@ -4349,13 +4706,13 @@
       <c r="B46" t="s">
         <v>262</v>
       </c>
-      <c r="C46" s="43">
+      <c r="C46" s="41">
         <v>46273</v>
       </c>
-      <c r="D46" s="43">
+      <c r="D46" s="41">
         <v>46273</v>
       </c>
-      <c r="E46" s="43">
+      <c r="E46" s="41">
         <v>46274</v>
       </c>
       <c r="F46" t="s">
@@ -4391,16 +4748,16 @@
       <c r="P46" t="s">
         <v>47</v>
       </c>
-      <c r="Q46" s="43">
+      <c r="Q46" s="41">
         <v>46275</v>
       </c>
       <c r="R46" s="19">
         <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="S46" s="23"/>
-      <c r="T46" s="23"/>
-      <c r="U46" s="43">
+      <c r="S46" s="22"/>
+      <c r="T46" s="22"/>
+      <c r="U46" s="41">
         <v>46279</v>
       </c>
       <c r="V46" t="s">
@@ -4414,13 +4771,13 @@
       <c r="B47" t="s">
         <v>262</v>
       </c>
-      <c r="C47" s="43">
+      <c r="C47" s="41">
         <v>46273</v>
       </c>
-      <c r="D47" s="43">
+      <c r="D47" s="41">
         <v>46273</v>
       </c>
-      <c r="E47" s="43">
+      <c r="E47" s="41">
         <v>46274</v>
       </c>
       <c r="F47" t="s">
@@ -4456,15 +4813,15 @@
       <c r="P47" t="s">
         <v>47</v>
       </c>
-      <c r="Q47" s="43">
+      <c r="Q47" s="41">
         <v>46275</v>
       </c>
       <c r="R47" s="19">
         <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="S47" s="23"/>
-      <c r="T47" s="23"/>
+      <c r="S47" s="22"/>
+      <c r="T47" s="22"/>
       <c r="U47" t="s">
         <v>342</v>
       </c>
@@ -4479,10 +4836,10 @@
       <c r="B48" t="s">
         <v>262</v>
       </c>
-      <c r="C48" s="43">
+      <c r="C48" s="41">
         <v>46273</v>
       </c>
-      <c r="D48" s="43">
+      <c r="D48" s="41">
         <v>46273</v>
       </c>
       <c r="F48" t="s">
@@ -4522,9 +4879,9 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S48" s="23"/>
-      <c r="T48" s="23"/>
-      <c r="U48" s="43">
+      <c r="S48" s="22"/>
+      <c r="T48" s="22"/>
+      <c r="U48" s="41">
         <v>46287</v>
       </c>
       <c r="V48" t="s">
@@ -4538,13 +4895,13 @@
       <c r="B49" t="s">
         <v>262</v>
       </c>
-      <c r="C49" s="43">
+      <c r="C49" s="41">
         <v>46273</v>
       </c>
-      <c r="D49" s="43">
+      <c r="D49" s="41">
         <v>46273</v>
       </c>
-      <c r="E49" s="43">
+      <c r="E49" s="41">
         <v>46274</v>
       </c>
       <c r="F49" t="s">
@@ -4580,16 +4937,16 @@
       <c r="P49" t="s">
         <v>47</v>
       </c>
-      <c r="Q49" s="43">
+      <c r="Q49" s="41">
         <v>46275</v>
       </c>
       <c r="R49" s="19">
         <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="S49" s="23"/>
-      <c r="T49" s="23"/>
-      <c r="U49" s="43">
+      <c r="S49" s="22"/>
+      <c r="T49" s="22"/>
+      <c r="U49" s="41">
         <v>46279</v>
       </c>
       <c r="V49" t="s">
@@ -4603,13 +4960,13 @@
       <c r="B50" t="s">
         <v>262</v>
       </c>
-      <c r="C50" s="43">
+      <c r="C50" s="41">
         <v>46273</v>
       </c>
-      <c r="D50" s="43">
+      <c r="D50" s="41">
         <v>46273</v>
       </c>
-      <c r="E50" s="43">
+      <c r="E50" s="41">
         <v>46274</v>
       </c>
       <c r="F50" t="s">
@@ -4645,16 +5002,16 @@
       <c r="P50" t="s">
         <v>47</v>
       </c>
-      <c r="Q50" s="43">
+      <c r="Q50" s="41">
         <v>46275</v>
       </c>
       <c r="R50" s="19">
         <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="S50" s="23"/>
-      <c r="T50" s="23"/>
-      <c r="U50" s="43">
+      <c r="S50" s="22"/>
+      <c r="T50" s="22"/>
+      <c r="U50" s="41">
         <v>46287</v>
       </c>
       <c r="V50" t="s">
@@ -4668,13 +5025,13 @@
       <c r="B51" t="s">
         <v>262</v>
       </c>
-      <c r="C51" s="43">
+      <c r="C51" s="41">
         <v>46273</v>
       </c>
-      <c r="D51" s="43">
+      <c r="D51" s="41">
         <v>46273</v>
       </c>
-      <c r="E51" s="43">
+      <c r="E51" s="41">
         <v>46274</v>
       </c>
       <c r="F51" t="s">
@@ -4710,16 +5067,16 @@
       <c r="P51" t="s">
         <v>47</v>
       </c>
-      <c r="Q51" s="43">
+      <c r="Q51" s="41">
         <v>46275</v>
       </c>
       <c r="R51" s="19">
         <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="S51" s="23"/>
-      <c r="T51" s="23"/>
-      <c r="U51" s="43">
+      <c r="S51" s="22"/>
+      <c r="T51" s="22"/>
+      <c r="U51" s="41">
         <v>46287</v>
       </c>
       <c r="V51" t="s">
@@ -4733,13 +5090,13 @@
       <c r="B52" t="s">
         <v>262</v>
       </c>
-      <c r="C52" s="43">
+      <c r="C52" s="41">
         <v>46273</v>
       </c>
-      <c r="D52" s="43">
+      <c r="D52" s="41">
         <v>46273</v>
       </c>
-      <c r="E52" s="43">
+      <c r="E52" s="41">
         <v>46274</v>
       </c>
       <c r="F52" t="s">
@@ -4775,16 +5132,16 @@
       <c r="P52" t="s">
         <v>47</v>
       </c>
-      <c r="Q52" s="43">
+      <c r="Q52" s="41">
         <v>46275</v>
       </c>
       <c r="R52" s="19">
         <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="S52" s="23"/>
-      <c r="T52" s="23"/>
-      <c r="U52" s="43">
+      <c r="S52" s="22"/>
+      <c r="T52" s="22"/>
+      <c r="U52" s="41">
         <v>46287</v>
       </c>
       <c r="V52" t="s">
@@ -4797,29 +5154,29 @@
       <c r="C53" s="12"/>
       <c r="D53" s="12"/>
       <c r="E53" s="12"/>
-      <c r="F53" s="23"/>
-      <c r="G53" s="23"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
       <c r="H53" s="11"/>
-      <c r="I53" s="26"/>
-      <c r="J53" s="26"/>
-      <c r="K53" s="26"/>
-      <c r="L53" s="26"/>
+      <c r="I53" s="25"/>
+      <c r="J53" s="25"/>
+      <c r="K53" s="25"/>
+      <c r="L53" s="25"/>
       <c r="M53" s="11"/>
       <c r="N53" s="11"/>
       <c r="O53" s="11"/>
       <c r="P53" s="11"/>
       <c r="Q53" s="18" t="str">
-        <f t="shared" ref="Q43:Q74" si="3">IF(E53="","",E53+1)</f>
+        <f t="shared" ref="Q53:Q74" si="3">IF(E53="","",E53+1)</f>
         <v/>
       </c>
       <c r="R53" s="19" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S53" s="23"/>
-      <c r="T53" s="23"/>
+      <c r="S53" s="22"/>
+      <c r="T53" s="22"/>
       <c r="U53" s="7"/>
-      <c r="V53" s="28"/>
+      <c r="V53" s="27"/>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" s="10"/>
@@ -4827,13 +5184,13 @@
       <c r="C54" s="12"/>
       <c r="D54" s="12"/>
       <c r="E54" s="12"/>
-      <c r="F54" s="23"/>
-      <c r="G54" s="23"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="22"/>
       <c r="H54" s="11"/>
-      <c r="I54" s="26"/>
-      <c r="J54" s="26"/>
-      <c r="K54" s="26"/>
-      <c r="L54" s="26"/>
+      <c r="I54" s="25"/>
+      <c r="J54" s="25"/>
+      <c r="K54" s="25"/>
+      <c r="L54" s="25"/>
       <c r="M54" s="11"/>
       <c r="N54" s="11"/>
       <c r="O54" s="11"/>
@@ -4846,10 +5203,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S54" s="23"/>
-      <c r="T54" s="23"/>
+      <c r="S54" s="22"/>
+      <c r="T54" s="22"/>
       <c r="U54" s="7"/>
-      <c r="V54" s="28"/>
+      <c r="V54" s="27"/>
     </row>
     <row r="55" spans="1:22">
       <c r="A55" s="10"/>
@@ -4857,13 +5214,13 @@
       <c r="C55" s="12"/>
       <c r="D55" s="12"/>
       <c r="E55" s="12"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="23"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
       <c r="H55" s="11"/>
-      <c r="I55" s="26"/>
-      <c r="J55" s="26"/>
-      <c r="K55" s="26"/>
-      <c r="L55" s="26"/>
+      <c r="I55" s="25"/>
+      <c r="J55" s="25"/>
+      <c r="K55" s="25"/>
+      <c r="L55" s="25"/>
       <c r="M55" s="11"/>
       <c r="N55" s="11"/>
       <c r="O55" s="11"/>
@@ -4876,10 +5233,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S55" s="23"/>
-      <c r="T55" s="23"/>
+      <c r="S55" s="22"/>
+      <c r="T55" s="22"/>
       <c r="U55" s="7"/>
-      <c r="V55" s="28"/>
+      <c r="V55" s="27"/>
     </row>
     <row r="56" spans="1:22">
       <c r="A56" s="10"/>
@@ -4887,13 +5244,13 @@
       <c r="C56" s="12"/>
       <c r="D56" s="12"/>
       <c r="E56" s="12"/>
-      <c r="F56" s="23"/>
-      <c r="G56" s="23"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="22"/>
       <c r="H56" s="11"/>
-      <c r="I56" s="26"/>
-      <c r="J56" s="26"/>
-      <c r="K56" s="26"/>
-      <c r="L56" s="26"/>
+      <c r="I56" s="25"/>
+      <c r="J56" s="25"/>
+      <c r="K56" s="25"/>
+      <c r="L56" s="25"/>
       <c r="M56" s="11"/>
       <c r="N56" s="11"/>
       <c r="O56" s="11"/>
@@ -4906,10 +5263,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S56" s="23"/>
-      <c r="T56" s="23"/>
+      <c r="S56" s="22"/>
+      <c r="T56" s="22"/>
       <c r="U56" s="7"/>
-      <c r="V56" s="28"/>
+      <c r="V56" s="27"/>
     </row>
     <row r="57" spans="1:22">
       <c r="A57" s="10"/>
@@ -4917,13 +5274,13 @@
       <c r="C57" s="12"/>
       <c r="D57" s="12"/>
       <c r="E57" s="12"/>
-      <c r="F57" s="23"/>
-      <c r="G57" s="23"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
       <c r="H57" s="11"/>
-      <c r="I57" s="26"/>
-      <c r="J57" s="26"/>
-      <c r="K57" s="26"/>
-      <c r="L57" s="26"/>
+      <c r="I57" s="25"/>
+      <c r="J57" s="25"/>
+      <c r="K57" s="25"/>
+      <c r="L57" s="25"/>
       <c r="M57" s="11"/>
       <c r="N57" s="11"/>
       <c r="O57" s="11"/>
@@ -4936,10 +5293,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S57" s="23"/>
-      <c r="T57" s="23"/>
+      <c r="S57" s="22"/>
+      <c r="T57" s="22"/>
       <c r="U57" s="7"/>
-      <c r="V57" s="28"/>
+      <c r="V57" s="27"/>
     </row>
     <row r="58" spans="1:22">
       <c r="A58" s="10"/>
@@ -4947,13 +5304,13 @@
       <c r="C58" s="12"/>
       <c r="D58" s="12"/>
       <c r="E58" s="12"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="23"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
       <c r="H58" s="11"/>
-      <c r="I58" s="26"/>
-      <c r="J58" s="26"/>
-      <c r="K58" s="26"/>
-      <c r="L58" s="26"/>
+      <c r="I58" s="25"/>
+      <c r="J58" s="25"/>
+      <c r="K58" s="25"/>
+      <c r="L58" s="25"/>
       <c r="M58" s="11"/>
       <c r="N58" s="11"/>
       <c r="O58" s="11"/>
@@ -4966,10 +5323,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S58" s="23"/>
-      <c r="T58" s="23"/>
+      <c r="S58" s="22"/>
+      <c r="T58" s="22"/>
       <c r="U58" s="7"/>
-      <c r="V58" s="28"/>
+      <c r="V58" s="27"/>
     </row>
     <row r="59" spans="1:22">
       <c r="A59" s="10"/>
@@ -4977,13 +5334,13 @@
       <c r="C59" s="12"/>
       <c r="D59" s="12"/>
       <c r="E59" s="12"/>
-      <c r="F59" s="23"/>
-      <c r="G59" s="23"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="22"/>
       <c r="H59" s="11"/>
-      <c r="I59" s="26"/>
-      <c r="J59" s="26"/>
-      <c r="K59" s="26"/>
-      <c r="L59" s="26"/>
+      <c r="I59" s="25"/>
+      <c r="J59" s="25"/>
+      <c r="K59" s="25"/>
+      <c r="L59" s="25"/>
       <c r="M59" s="11"/>
       <c r="N59" s="11"/>
       <c r="O59" s="11"/>
@@ -4996,10 +5353,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S59" s="23"/>
-      <c r="T59" s="23"/>
+      <c r="S59" s="22"/>
+      <c r="T59" s="22"/>
       <c r="U59" s="7"/>
-      <c r="V59" s="28"/>
+      <c r="V59" s="27"/>
     </row>
     <row r="60" spans="1:22">
       <c r="A60" s="10"/>
@@ -5007,13 +5364,13 @@
       <c r="C60" s="12"/>
       <c r="D60" s="12"/>
       <c r="E60" s="12"/>
-      <c r="F60" s="23"/>
-      <c r="G60" s="23"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="22"/>
       <c r="H60" s="11"/>
-      <c r="I60" s="26"/>
-      <c r="J60" s="26"/>
-      <c r="K60" s="26"/>
-      <c r="L60" s="26"/>
+      <c r="I60" s="25"/>
+      <c r="J60" s="25"/>
+      <c r="K60" s="25"/>
+      <c r="L60" s="25"/>
       <c r="M60" s="11"/>
       <c r="N60" s="11"/>
       <c r="O60" s="11"/>
@@ -5026,10 +5383,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S60" s="23"/>
-      <c r="T60" s="23"/>
+      <c r="S60" s="22"/>
+      <c r="T60" s="22"/>
       <c r="U60" s="7"/>
-      <c r="V60" s="28"/>
+      <c r="V60" s="27"/>
     </row>
     <row r="61" spans="1:22">
       <c r="A61" s="10"/>
@@ -5037,13 +5394,13 @@
       <c r="C61" s="12"/>
       <c r="D61" s="12"/>
       <c r="E61" s="12"/>
-      <c r="F61" s="23"/>
-      <c r="G61" s="23"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
       <c r="H61" s="11"/>
-      <c r="I61" s="26"/>
-      <c r="J61" s="26"/>
-      <c r="K61" s="26"/>
-      <c r="L61" s="26"/>
+      <c r="I61" s="25"/>
+      <c r="J61" s="25"/>
+      <c r="K61" s="25"/>
+      <c r="L61" s="25"/>
       <c r="M61" s="11"/>
       <c r="N61" s="11"/>
       <c r="O61" s="11"/>
@@ -5056,10 +5413,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S61" s="23"/>
-      <c r="T61" s="23"/>
+      <c r="S61" s="22"/>
+      <c r="T61" s="22"/>
       <c r="U61" s="7"/>
-      <c r="V61" s="28"/>
+      <c r="V61" s="27"/>
     </row>
     <row r="62" spans="1:22">
       <c r="A62" s="10"/>
@@ -5067,13 +5424,13 @@
       <c r="C62" s="12"/>
       <c r="D62" s="12"/>
       <c r="E62" s="12"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="23"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
       <c r="H62" s="11"/>
-      <c r="I62" s="26"/>
-      <c r="J62" s="26"/>
-      <c r="K62" s="26"/>
-      <c r="L62" s="26"/>
+      <c r="I62" s="25"/>
+      <c r="J62" s="25"/>
+      <c r="K62" s="25"/>
+      <c r="L62" s="25"/>
       <c r="M62" s="11"/>
       <c r="N62" s="11"/>
       <c r="O62" s="11"/>
@@ -5086,10 +5443,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S62" s="23"/>
-      <c r="T62" s="23"/>
+      <c r="S62" s="22"/>
+      <c r="T62" s="22"/>
       <c r="U62" s="7"/>
-      <c r="V62" s="28"/>
+      <c r="V62" s="27"/>
     </row>
     <row r="63" spans="1:22">
       <c r="A63" s="10"/>
@@ -5097,13 +5454,13 @@
       <c r="C63" s="12"/>
       <c r="D63" s="12"/>
       <c r="E63" s="12"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="23"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
       <c r="H63" s="11"/>
-      <c r="I63" s="26"/>
-      <c r="J63" s="26"/>
-      <c r="K63" s="26"/>
-      <c r="L63" s="26"/>
+      <c r="I63" s="25"/>
+      <c r="J63" s="25"/>
+      <c r="K63" s="25"/>
+      <c r="L63" s="25"/>
       <c r="M63" s="11"/>
       <c r="N63" s="11"/>
       <c r="O63" s="11"/>
@@ -5116,10 +5473,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S63" s="23"/>
-      <c r="T63" s="23"/>
+      <c r="S63" s="22"/>
+      <c r="T63" s="22"/>
       <c r="U63" s="7"/>
-      <c r="V63" s="28"/>
+      <c r="V63" s="27"/>
     </row>
     <row r="64" spans="1:22">
       <c r="A64" s="10"/>
@@ -5127,13 +5484,13 @@
       <c r="C64" s="12"/>
       <c r="D64" s="12"/>
       <c r="E64" s="12"/>
-      <c r="F64" s="23"/>
-      <c r="G64" s="23"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="22"/>
       <c r="H64" s="11"/>
-      <c r="I64" s="26"/>
-      <c r="J64" s="26"/>
-      <c r="K64" s="26"/>
-      <c r="L64" s="26"/>
+      <c r="I64" s="25"/>
+      <c r="J64" s="25"/>
+      <c r="K64" s="25"/>
+      <c r="L64" s="25"/>
       <c r="M64" s="11"/>
       <c r="N64" s="11"/>
       <c r="O64" s="11"/>
@@ -5146,10 +5503,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S64" s="23"/>
-      <c r="T64" s="23"/>
+      <c r="S64" s="22"/>
+      <c r="T64" s="22"/>
       <c r="U64" s="7"/>
-      <c r="V64" s="28"/>
+      <c r="V64" s="27"/>
     </row>
     <row r="65" spans="1:22">
       <c r="A65" s="10"/>
@@ -5157,13 +5514,13 @@
       <c r="C65" s="12"/>
       <c r="D65" s="12"/>
       <c r="E65" s="12"/>
-      <c r="F65" s="23"/>
-      <c r="G65" s="23"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
       <c r="H65" s="11"/>
-      <c r="I65" s="26"/>
-      <c r="J65" s="26"/>
-      <c r="K65" s="26"/>
-      <c r="L65" s="26"/>
+      <c r="I65" s="25"/>
+      <c r="J65" s="25"/>
+      <c r="K65" s="25"/>
+      <c r="L65" s="25"/>
       <c r="M65" s="11"/>
       <c r="N65" s="11"/>
       <c r="O65" s="11"/>
@@ -5176,10 +5533,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S65" s="23"/>
-      <c r="T65" s="23"/>
+      <c r="S65" s="22"/>
+      <c r="T65" s="22"/>
       <c r="U65" s="7"/>
-      <c r="V65" s="28"/>
+      <c r="V65" s="27"/>
     </row>
     <row r="66" spans="1:22">
       <c r="A66" s="10"/>
@@ -5187,13 +5544,13 @@
       <c r="C66" s="12"/>
       <c r="D66" s="12"/>
       <c r="E66" s="12"/>
-      <c r="F66" s="23"/>
-      <c r="G66" s="23"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="22"/>
       <c r="H66" s="11"/>
-      <c r="I66" s="26"/>
-      <c r="J66" s="26"/>
-      <c r="K66" s="26"/>
-      <c r="L66" s="26"/>
+      <c r="I66" s="25"/>
+      <c r="J66" s="25"/>
+      <c r="K66" s="25"/>
+      <c r="L66" s="25"/>
       <c r="M66" s="11"/>
       <c r="N66" s="11"/>
       <c r="O66" s="11"/>
@@ -5206,10 +5563,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S66" s="23"/>
-      <c r="T66" s="23"/>
+      <c r="S66" s="22"/>
+      <c r="T66" s="22"/>
       <c r="U66" s="7"/>
-      <c r="V66" s="28"/>
+      <c r="V66" s="27"/>
     </row>
     <row r="67" spans="1:22">
       <c r="A67" s="10"/>
@@ -5217,13 +5574,13 @@
       <c r="C67" s="12"/>
       <c r="D67" s="12"/>
       <c r="E67" s="12"/>
-      <c r="F67" s="23"/>
-      <c r="G67" s="23"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
       <c r="H67" s="11"/>
-      <c r="I67" s="26"/>
-      <c r="J67" s="26"/>
-      <c r="K67" s="26"/>
-      <c r="L67" s="26"/>
+      <c r="I67" s="25"/>
+      <c r="J67" s="25"/>
+      <c r="K67" s="25"/>
+      <c r="L67" s="25"/>
       <c r="M67" s="11"/>
       <c r="N67" s="11"/>
       <c r="O67" s="11"/>
@@ -5236,10 +5593,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S67" s="23"/>
-      <c r="T67" s="23"/>
+      <c r="S67" s="22"/>
+      <c r="T67" s="22"/>
       <c r="U67" s="7"/>
-      <c r="V67" s="28"/>
+      <c r="V67" s="27"/>
     </row>
     <row r="68" spans="1:22">
       <c r="A68" s="10"/>
@@ -5247,13 +5604,13 @@
       <c r="C68" s="12"/>
       <c r="D68" s="12"/>
       <c r="E68" s="12"/>
-      <c r="F68" s="23"/>
-      <c r="G68" s="23"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
       <c r="H68" s="11"/>
-      <c r="I68" s="26"/>
-      <c r="J68" s="26"/>
-      <c r="K68" s="26"/>
-      <c r="L68" s="26"/>
+      <c r="I68" s="25"/>
+      <c r="J68" s="25"/>
+      <c r="K68" s="25"/>
+      <c r="L68" s="25"/>
       <c r="M68" s="11"/>
       <c r="N68" s="11"/>
       <c r="O68" s="11"/>
@@ -5266,10 +5623,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S68" s="23"/>
-      <c r="T68" s="23"/>
+      <c r="S68" s="22"/>
+      <c r="T68" s="22"/>
       <c r="U68" s="7"/>
-      <c r="V68" s="28"/>
+      <c r="V68" s="27"/>
     </row>
     <row r="69" spans="1:22">
       <c r="A69" s="10"/>
@@ -5277,13 +5634,13 @@
       <c r="C69" s="12"/>
       <c r="D69" s="12"/>
       <c r="E69" s="12"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="23"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
       <c r="H69" s="11"/>
-      <c r="I69" s="26"/>
-      <c r="J69" s="26"/>
-      <c r="K69" s="26"/>
-      <c r="L69" s="26"/>
+      <c r="I69" s="25"/>
+      <c r="J69" s="25"/>
+      <c r="K69" s="25"/>
+      <c r="L69" s="25"/>
       <c r="M69" s="11"/>
       <c r="N69" s="11"/>
       <c r="O69" s="11"/>
@@ -5296,10 +5653,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S69" s="23"/>
-      <c r="T69" s="23"/>
+      <c r="S69" s="22"/>
+      <c r="T69" s="22"/>
       <c r="U69" s="7"/>
-      <c r="V69" s="28"/>
+      <c r="V69" s="27"/>
     </row>
     <row r="70" spans="1:22">
       <c r="A70" s="10"/>
@@ -5307,13 +5664,13 @@
       <c r="C70" s="12"/>
       <c r="D70" s="12"/>
       <c r="E70" s="12"/>
-      <c r="F70" s="23"/>
-      <c r="G70" s="23"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
       <c r="H70" s="11"/>
-      <c r="I70" s="26"/>
-      <c r="J70" s="26"/>
-      <c r="K70" s="26"/>
-      <c r="L70" s="26"/>
+      <c r="I70" s="25"/>
+      <c r="J70" s="25"/>
+      <c r="K70" s="25"/>
+      <c r="L70" s="25"/>
       <c r="M70" s="11"/>
       <c r="N70" s="11"/>
       <c r="O70" s="11"/>
@@ -5326,10 +5683,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S70" s="23"/>
-      <c r="T70" s="23"/>
+      <c r="S70" s="22"/>
+      <c r="T70" s="22"/>
       <c r="U70" s="7"/>
-      <c r="V70" s="28"/>
+      <c r="V70" s="27"/>
     </row>
     <row r="71" spans="1:22">
       <c r="A71" s="10"/>
@@ -5337,13 +5694,13 @@
       <c r="C71" s="12"/>
       <c r="D71" s="12"/>
       <c r="E71" s="12"/>
-      <c r="F71" s="23"/>
-      <c r="G71" s="23"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
       <c r="H71" s="11"/>
-      <c r="I71" s="26"/>
-      <c r="J71" s="26"/>
-      <c r="K71" s="26"/>
-      <c r="L71" s="26"/>
+      <c r="I71" s="25"/>
+      <c r="J71" s="25"/>
+      <c r="K71" s="25"/>
+      <c r="L71" s="25"/>
       <c r="M71" s="11"/>
       <c r="N71" s="11"/>
       <c r="O71" s="11"/>
@@ -5356,10 +5713,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S71" s="23"/>
-      <c r="T71" s="23"/>
+      <c r="S71" s="22"/>
+      <c r="T71" s="22"/>
       <c r="U71" s="7"/>
-      <c r="V71" s="28"/>
+      <c r="V71" s="27"/>
     </row>
     <row r="72" spans="1:22">
       <c r="A72" s="10"/>
@@ -5367,13 +5724,13 @@
       <c r="C72" s="12"/>
       <c r="D72" s="12"/>
       <c r="E72" s="12"/>
-      <c r="F72" s="23"/>
-      <c r="G72" s="23"/>
+      <c r="F72" s="22"/>
+      <c r="G72" s="22"/>
       <c r="H72" s="11"/>
-      <c r="I72" s="26"/>
-      <c r="J72" s="26"/>
-      <c r="K72" s="26"/>
-      <c r="L72" s="26"/>
+      <c r="I72" s="25"/>
+      <c r="J72" s="25"/>
+      <c r="K72" s="25"/>
+      <c r="L72" s="25"/>
       <c r="M72" s="11"/>
       <c r="N72" s="11"/>
       <c r="O72" s="11"/>
@@ -5386,10 +5743,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S72" s="23"/>
-      <c r="T72" s="23"/>
+      <c r="S72" s="22"/>
+      <c r="T72" s="22"/>
       <c r="U72" s="7"/>
-      <c r="V72" s="28"/>
+      <c r="V72" s="27"/>
     </row>
     <row r="73" spans="1:22">
       <c r="A73" s="10"/>
@@ -5397,13 +5754,13 @@
       <c r="C73" s="12"/>
       <c r="D73" s="12"/>
       <c r="E73" s="12"/>
-      <c r="F73" s="23"/>
-      <c r="G73" s="23"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
       <c r="H73" s="11"/>
-      <c r="I73" s="26"/>
-      <c r="J73" s="26"/>
-      <c r="K73" s="26"/>
-      <c r="L73" s="26"/>
+      <c r="I73" s="25"/>
+      <c r="J73" s="25"/>
+      <c r="K73" s="25"/>
+      <c r="L73" s="25"/>
       <c r="M73" s="11"/>
       <c r="N73" s="11"/>
       <c r="O73" s="11"/>
@@ -5416,10 +5773,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S73" s="23"/>
-      <c r="T73" s="23"/>
+      <c r="S73" s="22"/>
+      <c r="T73" s="22"/>
       <c r="U73" s="7"/>
-      <c r="V73" s="28"/>
+      <c r="V73" s="27"/>
     </row>
     <row r="74" spans="1:22">
       <c r="A74" s="10"/>
@@ -5427,13 +5784,13 @@
       <c r="C74" s="12"/>
       <c r="D74" s="12"/>
       <c r="E74" s="12"/>
-      <c r="F74" s="23"/>
-      <c r="G74" s="23"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
       <c r="H74" s="11"/>
-      <c r="I74" s="26"/>
-      <c r="J74" s="26"/>
-      <c r="K74" s="26"/>
-      <c r="L74" s="26"/>
+      <c r="I74" s="25"/>
+      <c r="J74" s="25"/>
+      <c r="K74" s="25"/>
+      <c r="L74" s="25"/>
       <c r="M74" s="11"/>
       <c r="N74" s="11"/>
       <c r="O74" s="11"/>
@@ -5446,10 +5803,10 @@
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="S74" s="23"/>
-      <c r="T74" s="23"/>
+      <c r="S74" s="22"/>
+      <c r="T74" s="22"/>
       <c r="U74" s="7"/>
-      <c r="V74" s="28"/>
+      <c r="V74" s="27"/>
     </row>
     <row r="75" spans="1:22">
       <c r="A75" s="10"/>
@@ -5457,13 +5814,13 @@
       <c r="C75" s="12"/>
       <c r="D75" s="12"/>
       <c r="E75" s="12"/>
-      <c r="F75" s="23"/>
-      <c r="G75" s="23"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
       <c r="H75" s="11"/>
-      <c r="I75" s="26"/>
-      <c r="J75" s="26"/>
-      <c r="K75" s="26"/>
-      <c r="L75" s="26"/>
+      <c r="I75" s="25"/>
+      <c r="J75" s="25"/>
+      <c r="K75" s="25"/>
+      <c r="L75" s="25"/>
       <c r="M75" s="11"/>
       <c r="N75" s="11"/>
       <c r="O75" s="11"/>
@@ -5476,10 +5833,10 @@
         <f t="shared" ref="R75:R106" ca="1" si="5">IF(E75="","",TODAY()-E75)</f>
         <v/>
       </c>
-      <c r="S75" s="23"/>
-      <c r="T75" s="23"/>
+      <c r="S75" s="22"/>
+      <c r="T75" s="22"/>
       <c r="U75" s="7"/>
-      <c r="V75" s="28"/>
+      <c r="V75" s="27"/>
     </row>
     <row r="76" spans="1:22">
       <c r="A76" s="10"/>
@@ -5487,13 +5844,13 @@
       <c r="C76" s="12"/>
       <c r="D76" s="12"/>
       <c r="E76" s="12"/>
-      <c r="F76" s="23"/>
-      <c r="G76" s="23"/>
+      <c r="F76" s="22"/>
+      <c r="G76" s="22"/>
       <c r="H76" s="11"/>
-      <c r="I76" s="26"/>
-      <c r="J76" s="26"/>
-      <c r="K76" s="26"/>
-      <c r="L76" s="26"/>
+      <c r="I76" s="25"/>
+      <c r="J76" s="25"/>
+      <c r="K76" s="25"/>
+      <c r="L76" s="25"/>
       <c r="M76" s="11"/>
       <c r="N76" s="11"/>
       <c r="O76" s="11"/>
@@ -5506,10 +5863,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S76" s="23"/>
-      <c r="T76" s="23"/>
+      <c r="S76" s="22"/>
+      <c r="T76" s="22"/>
       <c r="U76" s="7"/>
-      <c r="V76" s="28"/>
+      <c r="V76" s="27"/>
     </row>
     <row r="77" spans="1:22">
       <c r="A77" s="10"/>
@@ -5517,13 +5874,13 @@
       <c r="C77" s="12"/>
       <c r="D77" s="12"/>
       <c r="E77" s="12"/>
-      <c r="F77" s="23"/>
-      <c r="G77" s="23"/>
+      <c r="F77" s="22"/>
+      <c r="G77" s="22"/>
       <c r="H77" s="11"/>
-      <c r="I77" s="26"/>
-      <c r="J77" s="26"/>
-      <c r="K77" s="26"/>
-      <c r="L77" s="26"/>
+      <c r="I77" s="25"/>
+      <c r="J77" s="25"/>
+      <c r="K77" s="25"/>
+      <c r="L77" s="25"/>
       <c r="M77" s="11"/>
       <c r="N77" s="11"/>
       <c r="O77" s="11"/>
@@ -5536,10 +5893,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S77" s="23"/>
-      <c r="T77" s="23"/>
+      <c r="S77" s="22"/>
+      <c r="T77" s="22"/>
       <c r="U77" s="7"/>
-      <c r="V77" s="28"/>
+      <c r="V77" s="27"/>
     </row>
     <row r="78" spans="1:22">
       <c r="A78" s="10"/>
@@ -5547,13 +5904,13 @@
       <c r="C78" s="12"/>
       <c r="D78" s="12"/>
       <c r="E78" s="12"/>
-      <c r="F78" s="23"/>
-      <c r="G78" s="23"/>
+      <c r="F78" s="22"/>
+      <c r="G78" s="22"/>
       <c r="H78" s="11"/>
-      <c r="I78" s="26"/>
-      <c r="J78" s="26"/>
-      <c r="K78" s="26"/>
-      <c r="L78" s="26"/>
+      <c r="I78" s="25"/>
+      <c r="J78" s="25"/>
+      <c r="K78" s="25"/>
+      <c r="L78" s="25"/>
       <c r="M78" s="11"/>
       <c r="N78" s="11"/>
       <c r="O78" s="11"/>
@@ -5566,10 +5923,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S78" s="23"/>
-      <c r="T78" s="23"/>
+      <c r="S78" s="22"/>
+      <c r="T78" s="22"/>
       <c r="U78" s="7"/>
-      <c r="V78" s="28"/>
+      <c r="V78" s="27"/>
     </row>
     <row r="79" spans="1:22">
       <c r="A79" s="10"/>
@@ -5577,13 +5934,13 @@
       <c r="C79" s="12"/>
       <c r="D79" s="12"/>
       <c r="E79" s="12"/>
-      <c r="F79" s="23"/>
-      <c r="G79" s="23"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
       <c r="H79" s="11"/>
-      <c r="I79" s="26"/>
-      <c r="J79" s="26"/>
-      <c r="K79" s="26"/>
-      <c r="L79" s="26"/>
+      <c r="I79" s="25"/>
+      <c r="J79" s="25"/>
+      <c r="K79" s="25"/>
+      <c r="L79" s="25"/>
       <c r="M79" s="11"/>
       <c r="N79" s="11"/>
       <c r="O79" s="11"/>
@@ -5596,10 +5953,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S79" s="23"/>
-      <c r="T79" s="23"/>
+      <c r="S79" s="22"/>
+      <c r="T79" s="22"/>
       <c r="U79" s="7"/>
-      <c r="V79" s="28"/>
+      <c r="V79" s="27"/>
     </row>
     <row r="80" spans="1:22">
       <c r="A80" s="10"/>
@@ -5607,13 +5964,13 @@
       <c r="C80" s="12"/>
       <c r="D80" s="12"/>
       <c r="E80" s="12"/>
-      <c r="F80" s="23"/>
-      <c r="G80" s="23"/>
+      <c r="F80" s="22"/>
+      <c r="G80" s="22"/>
       <c r="H80" s="11"/>
-      <c r="I80" s="26"/>
-      <c r="J80" s="26"/>
-      <c r="K80" s="26"/>
-      <c r="L80" s="26"/>
+      <c r="I80" s="25"/>
+      <c r="J80" s="25"/>
+      <c r="K80" s="25"/>
+      <c r="L80" s="25"/>
       <c r="M80" s="11"/>
       <c r="N80" s="11"/>
       <c r="O80" s="11"/>
@@ -5626,10 +5983,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S80" s="23"/>
-      <c r="T80" s="23"/>
+      <c r="S80" s="22"/>
+      <c r="T80" s="22"/>
       <c r="U80" s="7"/>
-      <c r="V80" s="28"/>
+      <c r="V80" s="27"/>
     </row>
     <row r="81" spans="1:22">
       <c r="A81" s="10"/>
@@ -5637,13 +5994,13 @@
       <c r="C81" s="12"/>
       <c r="D81" s="12"/>
       <c r="E81" s="12"/>
-      <c r="F81" s="23"/>
-      <c r="G81" s="23"/>
+      <c r="F81" s="22"/>
+      <c r="G81" s="22"/>
       <c r="H81" s="11"/>
-      <c r="I81" s="26"/>
-      <c r="J81" s="26"/>
-      <c r="K81" s="26"/>
-      <c r="L81" s="26"/>
+      <c r="I81" s="25"/>
+      <c r="J81" s="25"/>
+      <c r="K81" s="25"/>
+      <c r="L81" s="25"/>
       <c r="M81" s="11"/>
       <c r="N81" s="11"/>
       <c r="O81" s="11"/>
@@ -5656,10 +6013,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S81" s="23"/>
-      <c r="T81" s="23"/>
+      <c r="S81" s="22"/>
+      <c r="T81" s="22"/>
       <c r="U81" s="7"/>
-      <c r="V81" s="28"/>
+      <c r="V81" s="27"/>
     </row>
     <row r="82" spans="1:22">
       <c r="A82" s="10"/>
@@ -5667,13 +6024,13 @@
       <c r="C82" s="12"/>
       <c r="D82" s="12"/>
       <c r="E82" s="12"/>
-      <c r="F82" s="23"/>
-      <c r="G82" s="23"/>
+      <c r="F82" s="22"/>
+      <c r="G82" s="22"/>
       <c r="H82" s="11"/>
-      <c r="I82" s="26"/>
-      <c r="J82" s="26"/>
-      <c r="K82" s="26"/>
-      <c r="L82" s="26"/>
+      <c r="I82" s="25"/>
+      <c r="J82" s="25"/>
+      <c r="K82" s="25"/>
+      <c r="L82" s="25"/>
       <c r="M82" s="11"/>
       <c r="N82" s="11"/>
       <c r="O82" s="11"/>
@@ -5686,10 +6043,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S82" s="23"/>
-      <c r="T82" s="23"/>
+      <c r="S82" s="22"/>
+      <c r="T82" s="22"/>
       <c r="U82" s="7"/>
-      <c r="V82" s="28"/>
+      <c r="V82" s="27"/>
     </row>
     <row r="83" spans="1:22">
       <c r="A83" s="10"/>
@@ -5697,13 +6054,13 @@
       <c r="C83" s="12"/>
       <c r="D83" s="12"/>
       <c r="E83" s="12"/>
-      <c r="F83" s="23"/>
-      <c r="G83" s="23"/>
+      <c r="F83" s="22"/>
+      <c r="G83" s="22"/>
       <c r="H83" s="11"/>
-      <c r="I83" s="26"/>
-      <c r="J83" s="26"/>
-      <c r="K83" s="26"/>
-      <c r="L83" s="26"/>
+      <c r="I83" s="25"/>
+      <c r="J83" s="25"/>
+      <c r="K83" s="25"/>
+      <c r="L83" s="25"/>
       <c r="M83" s="11"/>
       <c r="N83" s="11"/>
       <c r="O83" s="11"/>
@@ -5716,10 +6073,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S83" s="23"/>
-      <c r="T83" s="23"/>
+      <c r="S83" s="22"/>
+      <c r="T83" s="22"/>
       <c r="U83" s="7"/>
-      <c r="V83" s="28"/>
+      <c r="V83" s="27"/>
     </row>
     <row r="84" spans="1:22">
       <c r="A84" s="10"/>
@@ -5727,13 +6084,13 @@
       <c r="C84" s="12"/>
       <c r="D84" s="12"/>
       <c r="E84" s="12"/>
-      <c r="F84" s="23"/>
-      <c r="G84" s="23"/>
+      <c r="F84" s="22"/>
+      <c r="G84" s="22"/>
       <c r="H84" s="11"/>
-      <c r="I84" s="26"/>
-      <c r="J84" s="26"/>
-      <c r="K84" s="26"/>
-      <c r="L84" s="26"/>
+      <c r="I84" s="25"/>
+      <c r="J84" s="25"/>
+      <c r="K84" s="25"/>
+      <c r="L84" s="25"/>
       <c r="M84" s="11"/>
       <c r="N84" s="11"/>
       <c r="O84" s="11"/>
@@ -5746,10 +6103,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S84" s="23"/>
-      <c r="T84" s="23"/>
+      <c r="S84" s="22"/>
+      <c r="T84" s="22"/>
       <c r="U84" s="7"/>
-      <c r="V84" s="28"/>
+      <c r="V84" s="27"/>
     </row>
     <row r="85" spans="1:22">
       <c r="A85" s="10"/>
@@ -5757,13 +6114,13 @@
       <c r="C85" s="12"/>
       <c r="D85" s="12"/>
       <c r="E85" s="12"/>
-      <c r="F85" s="23"/>
-      <c r="G85" s="23"/>
+      <c r="F85" s="22"/>
+      <c r="G85" s="22"/>
       <c r="H85" s="11"/>
-      <c r="I85" s="26"/>
-      <c r="J85" s="26"/>
-      <c r="K85" s="26"/>
-      <c r="L85" s="26"/>
+      <c r="I85" s="25"/>
+      <c r="J85" s="25"/>
+      <c r="K85" s="25"/>
+      <c r="L85" s="25"/>
       <c r="M85" s="11"/>
       <c r="N85" s="11"/>
       <c r="O85" s="11"/>
@@ -5776,10 +6133,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S85" s="23"/>
-      <c r="T85" s="23"/>
+      <c r="S85" s="22"/>
+      <c r="T85" s="22"/>
       <c r="U85" s="7"/>
-      <c r="V85" s="28"/>
+      <c r="V85" s="27"/>
     </row>
     <row r="86" spans="1:22">
       <c r="A86" s="10"/>
@@ -5787,13 +6144,13 @@
       <c r="C86" s="12"/>
       <c r="D86" s="12"/>
       <c r="E86" s="12"/>
-      <c r="F86" s="23"/>
-      <c r="G86" s="23"/>
+      <c r="F86" s="22"/>
+      <c r="G86" s="22"/>
       <c r="H86" s="11"/>
-      <c r="I86" s="26"/>
-      <c r="J86" s="26"/>
-      <c r="K86" s="26"/>
-      <c r="L86" s="26"/>
+      <c r="I86" s="25"/>
+      <c r="J86" s="25"/>
+      <c r="K86" s="25"/>
+      <c r="L86" s="25"/>
       <c r="M86" s="11"/>
       <c r="N86" s="11"/>
       <c r="O86" s="11"/>
@@ -5806,10 +6163,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S86" s="23"/>
-      <c r="T86" s="23"/>
+      <c r="S86" s="22"/>
+      <c r="T86" s="22"/>
       <c r="U86" s="7"/>
-      <c r="V86" s="28"/>
+      <c r="V86" s="27"/>
     </row>
     <row r="87" spans="1:22">
       <c r="A87" s="10"/>
@@ -5817,13 +6174,13 @@
       <c r="C87" s="12"/>
       <c r="D87" s="12"/>
       <c r="E87" s="12"/>
-      <c r="F87" s="23"/>
-      <c r="G87" s="23"/>
+      <c r="F87" s="22"/>
+      <c r="G87" s="22"/>
       <c r="H87" s="11"/>
-      <c r="I87" s="26"/>
-      <c r="J87" s="26"/>
-      <c r="K87" s="26"/>
-      <c r="L87" s="26"/>
+      <c r="I87" s="25"/>
+      <c r="J87" s="25"/>
+      <c r="K87" s="25"/>
+      <c r="L87" s="25"/>
       <c r="M87" s="11"/>
       <c r="N87" s="11"/>
       <c r="O87" s="11"/>
@@ -5836,10 +6193,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S87" s="23"/>
-      <c r="T87" s="23"/>
+      <c r="S87" s="22"/>
+      <c r="T87" s="22"/>
       <c r="U87" s="7"/>
-      <c r="V87" s="28"/>
+      <c r="V87" s="27"/>
     </row>
     <row r="88" spans="1:22">
       <c r="A88" s="10"/>
@@ -5847,13 +6204,13 @@
       <c r="C88" s="12"/>
       <c r="D88" s="12"/>
       <c r="E88" s="12"/>
-      <c r="F88" s="23"/>
-      <c r="G88" s="23"/>
+      <c r="F88" s="22"/>
+      <c r="G88" s="22"/>
       <c r="H88" s="11"/>
-      <c r="I88" s="26"/>
-      <c r="J88" s="26"/>
-      <c r="K88" s="26"/>
-      <c r="L88" s="26"/>
+      <c r="I88" s="25"/>
+      <c r="J88" s="25"/>
+      <c r="K88" s="25"/>
+      <c r="L88" s="25"/>
       <c r="M88" s="11"/>
       <c r="N88" s="11"/>
       <c r="O88" s="11"/>
@@ -5866,10 +6223,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S88" s="23"/>
-      <c r="T88" s="23"/>
+      <c r="S88" s="22"/>
+      <c r="T88" s="22"/>
       <c r="U88" s="7"/>
-      <c r="V88" s="28"/>
+      <c r="V88" s="27"/>
     </row>
     <row r="89" spans="1:22">
       <c r="A89" s="10"/>
@@ -5877,13 +6234,13 @@
       <c r="C89" s="12"/>
       <c r="D89" s="12"/>
       <c r="E89" s="12"/>
-      <c r="F89" s="23"/>
-      <c r="G89" s="23"/>
+      <c r="F89" s="22"/>
+      <c r="G89" s="22"/>
       <c r="H89" s="11"/>
-      <c r="I89" s="26"/>
-      <c r="J89" s="26"/>
-      <c r="K89" s="26"/>
-      <c r="L89" s="26"/>
+      <c r="I89" s="25"/>
+      <c r="J89" s="25"/>
+      <c r="K89" s="25"/>
+      <c r="L89" s="25"/>
       <c r="M89" s="11"/>
       <c r="N89" s="11"/>
       <c r="O89" s="11"/>
@@ -5896,10 +6253,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S89" s="23"/>
-      <c r="T89" s="23"/>
+      <c r="S89" s="22"/>
+      <c r="T89" s="22"/>
       <c r="U89" s="7"/>
-      <c r="V89" s="28"/>
+      <c r="V89" s="27"/>
     </row>
     <row r="90" spans="1:22">
       <c r="A90" s="10"/>
@@ -5907,13 +6264,13 @@
       <c r="C90" s="12"/>
       <c r="D90" s="12"/>
       <c r="E90" s="12"/>
-      <c r="F90" s="23"/>
-      <c r="G90" s="23"/>
+      <c r="F90" s="22"/>
+      <c r="G90" s="22"/>
       <c r="H90" s="11"/>
-      <c r="I90" s="26"/>
-      <c r="J90" s="26"/>
-      <c r="K90" s="26"/>
-      <c r="L90" s="26"/>
+      <c r="I90" s="25"/>
+      <c r="J90" s="25"/>
+      <c r="K90" s="25"/>
+      <c r="L90" s="25"/>
       <c r="M90" s="11"/>
       <c r="N90" s="11"/>
       <c r="O90" s="11"/>
@@ -5926,10 +6283,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S90" s="23"/>
-      <c r="T90" s="23"/>
+      <c r="S90" s="22"/>
+      <c r="T90" s="22"/>
       <c r="U90" s="7"/>
-      <c r="V90" s="28"/>
+      <c r="V90" s="27"/>
     </row>
     <row r="91" spans="1:22">
       <c r="A91" s="10"/>
@@ -5937,13 +6294,13 @@
       <c r="C91" s="12"/>
       <c r="D91" s="12"/>
       <c r="E91" s="12"/>
-      <c r="F91" s="23"/>
-      <c r="G91" s="23"/>
+      <c r="F91" s="22"/>
+      <c r="G91" s="22"/>
       <c r="H91" s="11"/>
-      <c r="I91" s="26"/>
-      <c r="J91" s="26"/>
-      <c r="K91" s="26"/>
-      <c r="L91" s="26"/>
+      <c r="I91" s="25"/>
+      <c r="J91" s="25"/>
+      <c r="K91" s="25"/>
+      <c r="L91" s="25"/>
       <c r="M91" s="11"/>
       <c r="N91" s="11"/>
       <c r="O91" s="11"/>
@@ -5956,10 +6313,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S91" s="23"/>
-      <c r="T91" s="23"/>
+      <c r="S91" s="22"/>
+      <c r="T91" s="22"/>
       <c r="U91" s="7"/>
-      <c r="V91" s="28"/>
+      <c r="V91" s="27"/>
     </row>
     <row r="92" spans="1:22">
       <c r="A92" s="10"/>
@@ -5967,13 +6324,13 @@
       <c r="C92" s="12"/>
       <c r="D92" s="12"/>
       <c r="E92" s="12"/>
-      <c r="F92" s="23"/>
-      <c r="G92" s="23"/>
+      <c r="F92" s="22"/>
+      <c r="G92" s="22"/>
       <c r="H92" s="11"/>
-      <c r="I92" s="26"/>
-      <c r="J92" s="26"/>
-      <c r="K92" s="26"/>
-      <c r="L92" s="26"/>
+      <c r="I92" s="25"/>
+      <c r="J92" s="25"/>
+      <c r="K92" s="25"/>
+      <c r="L92" s="25"/>
       <c r="M92" s="11"/>
       <c r="N92" s="11"/>
       <c r="O92" s="11"/>
@@ -5986,10 +6343,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S92" s="23"/>
-      <c r="T92" s="23"/>
+      <c r="S92" s="22"/>
+      <c r="T92" s="22"/>
       <c r="U92" s="7"/>
-      <c r="V92" s="28"/>
+      <c r="V92" s="27"/>
     </row>
     <row r="93" spans="1:22">
       <c r="A93" s="10"/>
@@ -5997,13 +6354,13 @@
       <c r="C93" s="12"/>
       <c r="D93" s="12"/>
       <c r="E93" s="12"/>
-      <c r="F93" s="23"/>
-      <c r="G93" s="23"/>
+      <c r="F93" s="22"/>
+      <c r="G93" s="22"/>
       <c r="H93" s="11"/>
-      <c r="I93" s="26"/>
-      <c r="J93" s="26"/>
-      <c r="K93" s="26"/>
-      <c r="L93" s="26"/>
+      <c r="I93" s="25"/>
+      <c r="J93" s="25"/>
+      <c r="K93" s="25"/>
+      <c r="L93" s="25"/>
       <c r="M93" s="11"/>
       <c r="N93" s="11"/>
       <c r="O93" s="11"/>
@@ -6016,10 +6373,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S93" s="23"/>
-      <c r="T93" s="23"/>
+      <c r="S93" s="22"/>
+      <c r="T93" s="22"/>
       <c r="U93" s="7"/>
-      <c r="V93" s="28"/>
+      <c r="V93" s="27"/>
     </row>
     <row r="94" spans="1:22">
       <c r="A94" s="10"/>
@@ -6027,13 +6384,13 @@
       <c r="C94" s="12"/>
       <c r="D94" s="12"/>
       <c r="E94" s="12"/>
-      <c r="F94" s="23"/>
-      <c r="G94" s="23"/>
+      <c r="F94" s="22"/>
+      <c r="G94" s="22"/>
       <c r="H94" s="11"/>
-      <c r="I94" s="26"/>
-      <c r="J94" s="26"/>
-      <c r="K94" s="26"/>
-      <c r="L94" s="26"/>
+      <c r="I94" s="25"/>
+      <c r="J94" s="25"/>
+      <c r="K94" s="25"/>
+      <c r="L94" s="25"/>
       <c r="M94" s="11"/>
       <c r="N94" s="11"/>
       <c r="O94" s="11"/>
@@ -6046,10 +6403,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S94" s="23"/>
-      <c r="T94" s="23"/>
+      <c r="S94" s="22"/>
+      <c r="T94" s="22"/>
       <c r="U94" s="7"/>
-      <c r="V94" s="28"/>
+      <c r="V94" s="27"/>
     </row>
     <row r="95" spans="1:22">
       <c r="A95" s="10"/>
@@ -6057,13 +6414,13 @@
       <c r="C95" s="12"/>
       <c r="D95" s="12"/>
       <c r="E95" s="12"/>
-      <c r="F95" s="23"/>
-      <c r="G95" s="23"/>
+      <c r="F95" s="22"/>
+      <c r="G95" s="22"/>
       <c r="H95" s="11"/>
-      <c r="I95" s="26"/>
-      <c r="J95" s="26"/>
-      <c r="K95" s="26"/>
-      <c r="L95" s="26"/>
+      <c r="I95" s="25"/>
+      <c r="J95" s="25"/>
+      <c r="K95" s="25"/>
+      <c r="L95" s="25"/>
       <c r="M95" s="11"/>
       <c r="N95" s="11"/>
       <c r="O95" s="11"/>
@@ -6076,10 +6433,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S95" s="23"/>
-      <c r="T95" s="23"/>
+      <c r="S95" s="22"/>
+      <c r="T95" s="22"/>
       <c r="U95" s="7"/>
-      <c r="V95" s="28"/>
+      <c r="V95" s="27"/>
     </row>
     <row r="96" spans="1:22">
       <c r="A96" s="10"/>
@@ -6087,13 +6444,13 @@
       <c r="C96" s="12"/>
       <c r="D96" s="12"/>
       <c r="E96" s="12"/>
-      <c r="F96" s="23"/>
-      <c r="G96" s="23"/>
+      <c r="F96" s="22"/>
+      <c r="G96" s="22"/>
       <c r="H96" s="11"/>
-      <c r="I96" s="26"/>
-      <c r="J96" s="26"/>
-      <c r="K96" s="26"/>
-      <c r="L96" s="26"/>
+      <c r="I96" s="25"/>
+      <c r="J96" s="25"/>
+      <c r="K96" s="25"/>
+      <c r="L96" s="25"/>
       <c r="M96" s="11"/>
       <c r="N96" s="11"/>
       <c r="O96" s="11"/>
@@ -6106,10 +6463,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S96" s="23"/>
-      <c r="T96" s="23"/>
+      <c r="S96" s="22"/>
+      <c r="T96" s="22"/>
       <c r="U96" s="7"/>
-      <c r="V96" s="28"/>
+      <c r="V96" s="27"/>
     </row>
     <row r="97" spans="1:22">
       <c r="A97" s="10"/>
@@ -6117,13 +6474,13 @@
       <c r="C97" s="12"/>
       <c r="D97" s="12"/>
       <c r="E97" s="12"/>
-      <c r="F97" s="23"/>
-      <c r="G97" s="23"/>
+      <c r="F97" s="22"/>
+      <c r="G97" s="22"/>
       <c r="H97" s="11"/>
-      <c r="I97" s="26"/>
-      <c r="J97" s="26"/>
-      <c r="K97" s="26"/>
-      <c r="L97" s="26"/>
+      <c r="I97" s="25"/>
+      <c r="J97" s="25"/>
+      <c r="K97" s="25"/>
+      <c r="L97" s="25"/>
       <c r="M97" s="11"/>
       <c r="N97" s="11"/>
       <c r="O97" s="11"/>
@@ -6136,10 +6493,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S97" s="23"/>
-      <c r="T97" s="23"/>
+      <c r="S97" s="22"/>
+      <c r="T97" s="22"/>
       <c r="U97" s="7"/>
-      <c r="V97" s="28"/>
+      <c r="V97" s="27"/>
     </row>
     <row r="98" spans="1:22">
       <c r="A98" s="10"/>
@@ -6147,13 +6504,13 @@
       <c r="C98" s="12"/>
       <c r="D98" s="12"/>
       <c r="E98" s="12"/>
-      <c r="F98" s="23"/>
-      <c r="G98" s="23"/>
+      <c r="F98" s="22"/>
+      <c r="G98" s="22"/>
       <c r="H98" s="11"/>
-      <c r="I98" s="26"/>
-      <c r="J98" s="26"/>
-      <c r="K98" s="26"/>
-      <c r="L98" s="26"/>
+      <c r="I98" s="25"/>
+      <c r="J98" s="25"/>
+      <c r="K98" s="25"/>
+      <c r="L98" s="25"/>
       <c r="M98" s="11"/>
       <c r="N98" s="11"/>
       <c r="O98" s="11"/>
@@ -6166,10 +6523,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S98" s="23"/>
-      <c r="T98" s="23"/>
+      <c r="S98" s="22"/>
+      <c r="T98" s="22"/>
       <c r="U98" s="7"/>
-      <c r="V98" s="28"/>
+      <c r="V98" s="27"/>
     </row>
     <row r="99" spans="1:22">
       <c r="A99" s="10"/>
@@ -6177,13 +6534,13 @@
       <c r="C99" s="12"/>
       <c r="D99" s="12"/>
       <c r="E99" s="12"/>
-      <c r="F99" s="23"/>
-      <c r="G99" s="23"/>
+      <c r="F99" s="22"/>
+      <c r="G99" s="22"/>
       <c r="H99" s="11"/>
-      <c r="I99" s="26"/>
-      <c r="J99" s="26"/>
-      <c r="K99" s="26"/>
-      <c r="L99" s="26"/>
+      <c r="I99" s="25"/>
+      <c r="J99" s="25"/>
+      <c r="K99" s="25"/>
+      <c r="L99" s="25"/>
       <c r="M99" s="11"/>
       <c r="N99" s="11"/>
       <c r="O99" s="11"/>
@@ -6196,10 +6553,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S99" s="23"/>
-      <c r="T99" s="23"/>
+      <c r="S99" s="22"/>
+      <c r="T99" s="22"/>
       <c r="U99" s="7"/>
-      <c r="V99" s="28"/>
+      <c r="V99" s="27"/>
     </row>
     <row r="100" spans="1:22">
       <c r="A100" s="10"/>
@@ -6207,13 +6564,13 @@
       <c r="C100" s="12"/>
       <c r="D100" s="12"/>
       <c r="E100" s="12"/>
-      <c r="F100" s="23"/>
-      <c r="G100" s="23"/>
+      <c r="F100" s="22"/>
+      <c r="G100" s="22"/>
       <c r="H100" s="11"/>
-      <c r="I100" s="26"/>
-      <c r="J100" s="26"/>
-      <c r="K100" s="26"/>
-      <c r="L100" s="26"/>
+      <c r="I100" s="25"/>
+      <c r="J100" s="25"/>
+      <c r="K100" s="25"/>
+      <c r="L100" s="25"/>
       <c r="M100" s="11"/>
       <c r="N100" s="11"/>
       <c r="O100" s="11"/>
@@ -6226,10 +6583,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S100" s="23"/>
-      <c r="T100" s="23"/>
+      <c r="S100" s="22"/>
+      <c r="T100" s="22"/>
       <c r="U100" s="7"/>
-      <c r="V100" s="28"/>
+      <c r="V100" s="27"/>
     </row>
     <row r="101" spans="1:22">
       <c r="A101" s="10"/>
@@ -6237,13 +6594,13 @@
       <c r="C101" s="12"/>
       <c r="D101" s="12"/>
       <c r="E101" s="12"/>
-      <c r="F101" s="23"/>
-      <c r="G101" s="23"/>
+      <c r="F101" s="22"/>
+      <c r="G101" s="22"/>
       <c r="H101" s="11"/>
-      <c r="I101" s="26"/>
-      <c r="J101" s="26"/>
-      <c r="K101" s="26"/>
-      <c r="L101" s="26"/>
+      <c r="I101" s="25"/>
+      <c r="J101" s="25"/>
+      <c r="K101" s="25"/>
+      <c r="L101" s="25"/>
       <c r="M101" s="11"/>
       <c r="N101" s="11"/>
       <c r="O101" s="11"/>
@@ -6256,10 +6613,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S101" s="23"/>
-      <c r="T101" s="23"/>
+      <c r="S101" s="22"/>
+      <c r="T101" s="22"/>
       <c r="U101" s="7"/>
-      <c r="V101" s="28"/>
+      <c r="V101" s="27"/>
     </row>
     <row r="102" spans="1:22">
       <c r="A102" s="10"/>
@@ -6267,13 +6624,13 @@
       <c r="C102" s="12"/>
       <c r="D102" s="12"/>
       <c r="E102" s="12"/>
-      <c r="F102" s="23"/>
-      <c r="G102" s="23"/>
+      <c r="F102" s="22"/>
+      <c r="G102" s="22"/>
       <c r="H102" s="11"/>
-      <c r="I102" s="26"/>
-      <c r="J102" s="26"/>
-      <c r="K102" s="26"/>
-      <c r="L102" s="26"/>
+      <c r="I102" s="25"/>
+      <c r="J102" s="25"/>
+      <c r="K102" s="25"/>
+      <c r="L102" s="25"/>
       <c r="M102" s="11"/>
       <c r="N102" s="11"/>
       <c r="O102" s="11"/>
@@ -6286,10 +6643,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S102" s="23"/>
-      <c r="T102" s="23"/>
+      <c r="S102" s="22"/>
+      <c r="T102" s="22"/>
       <c r="U102" s="7"/>
-      <c r="V102" s="28"/>
+      <c r="V102" s="27"/>
     </row>
     <row r="103" spans="1:22">
       <c r="A103" s="10"/>
@@ -6297,13 +6654,13 @@
       <c r="C103" s="12"/>
       <c r="D103" s="12"/>
       <c r="E103" s="12"/>
-      <c r="F103" s="23"/>
-      <c r="G103" s="23"/>
+      <c r="F103" s="22"/>
+      <c r="G103" s="22"/>
       <c r="H103" s="11"/>
-      <c r="I103" s="26"/>
-      <c r="J103" s="26"/>
-      <c r="K103" s="26"/>
-      <c r="L103" s="26"/>
+      <c r="I103" s="25"/>
+      <c r="J103" s="25"/>
+      <c r="K103" s="25"/>
+      <c r="L103" s="25"/>
       <c r="M103" s="11"/>
       <c r="N103" s="11"/>
       <c r="O103" s="11"/>
@@ -6316,10 +6673,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S103" s="23"/>
-      <c r="T103" s="23"/>
+      <c r="S103" s="22"/>
+      <c r="T103" s="22"/>
       <c r="U103" s="7"/>
-      <c r="V103" s="28"/>
+      <c r="V103" s="27"/>
     </row>
     <row r="104" spans="1:22">
       <c r="A104" s="10"/>
@@ -6327,13 +6684,13 @@
       <c r="C104" s="12"/>
       <c r="D104" s="12"/>
       <c r="E104" s="12"/>
-      <c r="F104" s="23"/>
-      <c r="G104" s="23"/>
+      <c r="F104" s="22"/>
+      <c r="G104" s="22"/>
       <c r="H104" s="11"/>
-      <c r="I104" s="26"/>
-      <c r="J104" s="26"/>
-      <c r="K104" s="26"/>
-      <c r="L104" s="26"/>
+      <c r="I104" s="25"/>
+      <c r="J104" s="25"/>
+      <c r="K104" s="25"/>
+      <c r="L104" s="25"/>
       <c r="M104" s="11"/>
       <c r="N104" s="11"/>
       <c r="O104" s="11"/>
@@ -6346,10 +6703,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S104" s="23"/>
-      <c r="T104" s="23"/>
+      <c r="S104" s="22"/>
+      <c r="T104" s="22"/>
       <c r="U104" s="7"/>
-      <c r="V104" s="28"/>
+      <c r="V104" s="27"/>
     </row>
     <row r="105" spans="1:22">
       <c r="A105" s="10"/>
@@ -6357,13 +6714,13 @@
       <c r="C105" s="12"/>
       <c r="D105" s="12"/>
       <c r="E105" s="12"/>
-      <c r="F105" s="23"/>
-      <c r="G105" s="23"/>
+      <c r="F105" s="22"/>
+      <c r="G105" s="22"/>
       <c r="H105" s="11"/>
-      <c r="I105" s="26"/>
-      <c r="J105" s="26"/>
-      <c r="K105" s="26"/>
-      <c r="L105" s="26"/>
+      <c r="I105" s="25"/>
+      <c r="J105" s="25"/>
+      <c r="K105" s="25"/>
+      <c r="L105" s="25"/>
       <c r="M105" s="11"/>
       <c r="N105" s="11"/>
       <c r="O105" s="11"/>
@@ -6376,10 +6733,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S105" s="23"/>
-      <c r="T105" s="23"/>
+      <c r="S105" s="22"/>
+      <c r="T105" s="22"/>
       <c r="U105" s="7"/>
-      <c r="V105" s="28"/>
+      <c r="V105" s="27"/>
     </row>
     <row r="106" spans="1:22">
       <c r="A106" s="10"/>
@@ -6387,13 +6744,13 @@
       <c r="C106" s="12"/>
       <c r="D106" s="12"/>
       <c r="E106" s="12"/>
-      <c r="F106" s="23"/>
-      <c r="G106" s="23"/>
+      <c r="F106" s="22"/>
+      <c r="G106" s="22"/>
       <c r="H106" s="11"/>
-      <c r="I106" s="26"/>
-      <c r="J106" s="26"/>
-      <c r="K106" s="26"/>
-      <c r="L106" s="26"/>
+      <c r="I106" s="25"/>
+      <c r="J106" s="25"/>
+      <c r="K106" s="25"/>
+      <c r="L106" s="25"/>
       <c r="M106" s="11"/>
       <c r="N106" s="11"/>
       <c r="O106" s="11"/>
@@ -6406,10 +6763,10 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="S106" s="23"/>
-      <c r="T106" s="23"/>
+      <c r="S106" s="22"/>
+      <c r="T106" s="22"/>
       <c r="U106" s="7"/>
-      <c r="V106" s="28"/>
+      <c r="V106" s="27"/>
     </row>
     <row r="107" spans="1:22">
       <c r="A107" s="10"/>
@@ -6417,13 +6774,13 @@
       <c r="C107" s="12"/>
       <c r="D107" s="12"/>
       <c r="E107" s="12"/>
-      <c r="F107" s="23"/>
-      <c r="G107" s="23"/>
+      <c r="F107" s="22"/>
+      <c r="G107" s="22"/>
       <c r="H107" s="11"/>
-      <c r="I107" s="26"/>
-      <c r="J107" s="26"/>
-      <c r="K107" s="26"/>
-      <c r="L107" s="26"/>
+      <c r="I107" s="25"/>
+      <c r="J107" s="25"/>
+      <c r="K107" s="25"/>
+      <c r="L107" s="25"/>
       <c r="M107" s="11"/>
       <c r="N107" s="11"/>
       <c r="O107" s="11"/>
@@ -6436,10 +6793,10 @@
         <f t="shared" ref="R107:R138" ca="1" si="7">IF(E107="","",TODAY()-E107)</f>
         <v/>
       </c>
-      <c r="S107" s="23"/>
-      <c r="T107" s="23"/>
+      <c r="S107" s="22"/>
+      <c r="T107" s="22"/>
       <c r="U107" s="7"/>
-      <c r="V107" s="28"/>
+      <c r="V107" s="27"/>
     </row>
     <row r="108" spans="1:22">
       <c r="A108" s="10"/>
@@ -6447,13 +6804,13 @@
       <c r="C108" s="12"/>
       <c r="D108" s="12"/>
       <c r="E108" s="12"/>
-      <c r="F108" s="23"/>
-      <c r="G108" s="23"/>
+      <c r="F108" s="22"/>
+      <c r="G108" s="22"/>
       <c r="H108" s="11"/>
-      <c r="I108" s="26"/>
-      <c r="J108" s="26"/>
-      <c r="K108" s="26"/>
-      <c r="L108" s="26"/>
+      <c r="I108" s="25"/>
+      <c r="J108" s="25"/>
+      <c r="K108" s="25"/>
+      <c r="L108" s="25"/>
       <c r="M108" s="11"/>
       <c r="N108" s="11"/>
       <c r="O108" s="11"/>
@@ -6466,10 +6823,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S108" s="23"/>
-      <c r="T108" s="23"/>
+      <c r="S108" s="22"/>
+      <c r="T108" s="22"/>
       <c r="U108" s="7"/>
-      <c r="V108" s="28"/>
+      <c r="V108" s="27"/>
     </row>
     <row r="109" spans="1:22">
       <c r="A109" s="10"/>
@@ -6477,13 +6834,13 @@
       <c r="C109" s="12"/>
       <c r="D109" s="12"/>
       <c r="E109" s="12"/>
-      <c r="F109" s="23"/>
-      <c r="G109" s="23"/>
+      <c r="F109" s="22"/>
+      <c r="G109" s="22"/>
       <c r="H109" s="11"/>
-      <c r="I109" s="26"/>
-      <c r="J109" s="26"/>
-      <c r="K109" s="26"/>
-      <c r="L109" s="26"/>
+      <c r="I109" s="25"/>
+      <c r="J109" s="25"/>
+      <c r="K109" s="25"/>
+      <c r="L109" s="25"/>
       <c r="M109" s="11"/>
       <c r="N109" s="11"/>
       <c r="O109" s="11"/>
@@ -6496,10 +6853,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S109" s="23"/>
-      <c r="T109" s="23"/>
+      <c r="S109" s="22"/>
+      <c r="T109" s="22"/>
       <c r="U109" s="7"/>
-      <c r="V109" s="28"/>
+      <c r="V109" s="27"/>
     </row>
     <row r="110" spans="1:22">
       <c r="A110" s="10"/>
@@ -6507,13 +6864,13 @@
       <c r="C110" s="12"/>
       <c r="D110" s="12"/>
       <c r="E110" s="12"/>
-      <c r="F110" s="23"/>
-      <c r="G110" s="23"/>
+      <c r="F110" s="22"/>
+      <c r="G110" s="22"/>
       <c r="H110" s="11"/>
-      <c r="I110" s="26"/>
-      <c r="J110" s="26"/>
-      <c r="K110" s="26"/>
-      <c r="L110" s="26"/>
+      <c r="I110" s="25"/>
+      <c r="J110" s="25"/>
+      <c r="K110" s="25"/>
+      <c r="L110" s="25"/>
       <c r="M110" s="11"/>
       <c r="N110" s="11"/>
       <c r="O110" s="11"/>
@@ -6526,10 +6883,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S110" s="23"/>
-      <c r="T110" s="23"/>
+      <c r="S110" s="22"/>
+      <c r="T110" s="22"/>
       <c r="U110" s="7"/>
-      <c r="V110" s="28"/>
+      <c r="V110" s="27"/>
     </row>
     <row r="111" spans="1:22">
       <c r="A111" s="10"/>
@@ -6537,13 +6894,13 @@
       <c r="C111" s="12"/>
       <c r="D111" s="12"/>
       <c r="E111" s="12"/>
-      <c r="F111" s="23"/>
-      <c r="G111" s="23"/>
+      <c r="F111" s="22"/>
+      <c r="G111" s="22"/>
       <c r="H111" s="11"/>
-      <c r="I111" s="26"/>
-      <c r="J111" s="26"/>
-      <c r="K111" s="26"/>
-      <c r="L111" s="26"/>
+      <c r="I111" s="25"/>
+      <c r="J111" s="25"/>
+      <c r="K111" s="25"/>
+      <c r="L111" s="25"/>
       <c r="M111" s="11"/>
       <c r="N111" s="11"/>
       <c r="O111" s="11"/>
@@ -6556,10 +6913,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S111" s="23"/>
-      <c r="T111" s="23"/>
+      <c r="S111" s="22"/>
+      <c r="T111" s="22"/>
       <c r="U111" s="7"/>
-      <c r="V111" s="28"/>
+      <c r="V111" s="27"/>
     </row>
     <row r="112" spans="1:22">
       <c r="A112" s="10"/>
@@ -6567,13 +6924,13 @@
       <c r="C112" s="12"/>
       <c r="D112" s="12"/>
       <c r="E112" s="12"/>
-      <c r="F112" s="23"/>
-      <c r="G112" s="23"/>
+      <c r="F112" s="22"/>
+      <c r="G112" s="22"/>
       <c r="H112" s="11"/>
-      <c r="I112" s="26"/>
-      <c r="J112" s="26"/>
-      <c r="K112" s="26"/>
-      <c r="L112" s="26"/>
+      <c r="I112" s="25"/>
+      <c r="J112" s="25"/>
+      <c r="K112" s="25"/>
+      <c r="L112" s="25"/>
       <c r="M112" s="11"/>
       <c r="N112" s="11"/>
       <c r="O112" s="11"/>
@@ -6586,10 +6943,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S112" s="23"/>
-      <c r="T112" s="23"/>
+      <c r="S112" s="22"/>
+      <c r="T112" s="22"/>
       <c r="U112" s="7"/>
-      <c r="V112" s="28"/>
+      <c r="V112" s="27"/>
     </row>
     <row r="113" spans="1:22">
       <c r="A113" s="10"/>
@@ -6597,13 +6954,13 @@
       <c r="C113" s="12"/>
       <c r="D113" s="12"/>
       <c r="E113" s="12"/>
-      <c r="F113" s="23"/>
-      <c r="G113" s="23"/>
+      <c r="F113" s="22"/>
+      <c r="G113" s="22"/>
       <c r="H113" s="11"/>
-      <c r="I113" s="26"/>
-      <c r="J113" s="26"/>
-      <c r="K113" s="26"/>
-      <c r="L113" s="26"/>
+      <c r="I113" s="25"/>
+      <c r="J113" s="25"/>
+      <c r="K113" s="25"/>
+      <c r="L113" s="25"/>
       <c r="M113" s="11"/>
       <c r="N113" s="11"/>
       <c r="O113" s="11"/>
@@ -6616,10 +6973,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S113" s="23"/>
-      <c r="T113" s="23"/>
+      <c r="S113" s="22"/>
+      <c r="T113" s="22"/>
       <c r="U113" s="7"/>
-      <c r="V113" s="28"/>
+      <c r="V113" s="27"/>
     </row>
     <row r="114" spans="1:22">
       <c r="A114" s="10"/>
@@ -6627,13 +6984,13 @@
       <c r="C114" s="12"/>
       <c r="D114" s="12"/>
       <c r="E114" s="12"/>
-      <c r="F114" s="23"/>
-      <c r="G114" s="23"/>
+      <c r="F114" s="22"/>
+      <c r="G114" s="22"/>
       <c r="H114" s="11"/>
-      <c r="I114" s="26"/>
-      <c r="J114" s="26"/>
-      <c r="K114" s="26"/>
-      <c r="L114" s="26"/>
+      <c r="I114" s="25"/>
+      <c r="J114" s="25"/>
+      <c r="K114" s="25"/>
+      <c r="L114" s="25"/>
       <c r="M114" s="11"/>
       <c r="N114" s="11"/>
       <c r="O114" s="11"/>
@@ -6646,10 +7003,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S114" s="23"/>
-      <c r="T114" s="23"/>
+      <c r="S114" s="22"/>
+      <c r="T114" s="22"/>
       <c r="U114" s="7"/>
-      <c r="V114" s="28"/>
+      <c r="V114" s="27"/>
     </row>
     <row r="115" spans="1:22">
       <c r="A115" s="10"/>
@@ -6657,13 +7014,13 @@
       <c r="C115" s="12"/>
       <c r="D115" s="12"/>
       <c r="E115" s="12"/>
-      <c r="F115" s="23"/>
-      <c r="G115" s="23"/>
+      <c r="F115" s="22"/>
+      <c r="G115" s="22"/>
       <c r="H115" s="11"/>
-      <c r="I115" s="26"/>
-      <c r="J115" s="26"/>
-      <c r="K115" s="26"/>
-      <c r="L115" s="26"/>
+      <c r="I115" s="25"/>
+      <c r="J115" s="25"/>
+      <c r="K115" s="25"/>
+      <c r="L115" s="25"/>
       <c r="M115" s="11"/>
       <c r="N115" s="11"/>
       <c r="O115" s="11"/>
@@ -6676,10 +7033,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S115" s="23"/>
-      <c r="T115" s="23"/>
+      <c r="S115" s="22"/>
+      <c r="T115" s="22"/>
       <c r="U115" s="7"/>
-      <c r="V115" s="28"/>
+      <c r="V115" s="27"/>
     </row>
     <row r="116" spans="1:22">
       <c r="A116" s="10"/>
@@ -6687,13 +7044,13 @@
       <c r="C116" s="12"/>
       <c r="D116" s="12"/>
       <c r="E116" s="12"/>
-      <c r="F116" s="23"/>
-      <c r="G116" s="23"/>
+      <c r="F116" s="22"/>
+      <c r="G116" s="22"/>
       <c r="H116" s="11"/>
-      <c r="I116" s="26"/>
-      <c r="J116" s="26"/>
-      <c r="K116" s="26"/>
-      <c r="L116" s="26"/>
+      <c r="I116" s="25"/>
+      <c r="J116" s="25"/>
+      <c r="K116" s="25"/>
+      <c r="L116" s="25"/>
       <c r="M116" s="11"/>
       <c r="N116" s="11"/>
       <c r="O116" s="11"/>
@@ -6706,10 +7063,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S116" s="23"/>
-      <c r="T116" s="23"/>
+      <c r="S116" s="22"/>
+      <c r="T116" s="22"/>
       <c r="U116" s="7"/>
-      <c r="V116" s="28"/>
+      <c r="V116" s="27"/>
     </row>
     <row r="117" spans="1:22">
       <c r="A117" s="10"/>
@@ -6717,13 +7074,13 @@
       <c r="C117" s="12"/>
       <c r="D117" s="12"/>
       <c r="E117" s="12"/>
-      <c r="F117" s="23"/>
-      <c r="G117" s="23"/>
+      <c r="F117" s="22"/>
+      <c r="G117" s="22"/>
       <c r="H117" s="11"/>
-      <c r="I117" s="26"/>
-      <c r="J117" s="26"/>
-      <c r="K117" s="26"/>
-      <c r="L117" s="26"/>
+      <c r="I117" s="25"/>
+      <c r="J117" s="25"/>
+      <c r="K117" s="25"/>
+      <c r="L117" s="25"/>
       <c r="M117" s="11"/>
       <c r="N117" s="11"/>
       <c r="O117" s="11"/>
@@ -6736,10 +7093,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S117" s="23"/>
-      <c r="T117" s="23"/>
+      <c r="S117" s="22"/>
+      <c r="T117" s="22"/>
       <c r="U117" s="7"/>
-      <c r="V117" s="28"/>
+      <c r="V117" s="27"/>
     </row>
     <row r="118" spans="1:22">
       <c r="A118" s="10"/>
@@ -6747,13 +7104,13 @@
       <c r="C118" s="12"/>
       <c r="D118" s="12"/>
       <c r="E118" s="12"/>
-      <c r="F118" s="23"/>
-      <c r="G118" s="23"/>
+      <c r="F118" s="22"/>
+      <c r="G118" s="22"/>
       <c r="H118" s="11"/>
-      <c r="I118" s="26"/>
-      <c r="J118" s="26"/>
-      <c r="K118" s="26"/>
-      <c r="L118" s="26"/>
+      <c r="I118" s="25"/>
+      <c r="J118" s="25"/>
+      <c r="K118" s="25"/>
+      <c r="L118" s="25"/>
       <c r="M118" s="11"/>
       <c r="N118" s="11"/>
       <c r="O118" s="11"/>
@@ -6766,10 +7123,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S118" s="23"/>
-      <c r="T118" s="23"/>
+      <c r="S118" s="22"/>
+      <c r="T118" s="22"/>
       <c r="U118" s="7"/>
-      <c r="V118" s="28"/>
+      <c r="V118" s="27"/>
     </row>
     <row r="119" spans="1:22">
       <c r="A119" s="10"/>
@@ -6777,13 +7134,13 @@
       <c r="C119" s="12"/>
       <c r="D119" s="12"/>
       <c r="E119" s="12"/>
-      <c r="F119" s="23"/>
-      <c r="G119" s="23"/>
+      <c r="F119" s="22"/>
+      <c r="G119" s="22"/>
       <c r="H119" s="11"/>
-      <c r="I119" s="26"/>
-      <c r="J119" s="26"/>
-      <c r="K119" s="26"/>
-      <c r="L119" s="26"/>
+      <c r="I119" s="25"/>
+      <c r="J119" s="25"/>
+      <c r="K119" s="25"/>
+      <c r="L119" s="25"/>
       <c r="M119" s="11"/>
       <c r="N119" s="11"/>
       <c r="O119" s="11"/>
@@ -6796,10 +7153,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S119" s="23"/>
-      <c r="T119" s="23"/>
+      <c r="S119" s="22"/>
+      <c r="T119" s="22"/>
       <c r="U119" s="7"/>
-      <c r="V119" s="28"/>
+      <c r="V119" s="27"/>
     </row>
     <row r="120" spans="1:22">
       <c r="A120" s="10"/>
@@ -6807,13 +7164,13 @@
       <c r="C120" s="12"/>
       <c r="D120" s="12"/>
       <c r="E120" s="12"/>
-      <c r="F120" s="23"/>
-      <c r="G120" s="23"/>
+      <c r="F120" s="22"/>
+      <c r="G120" s="22"/>
       <c r="H120" s="11"/>
-      <c r="I120" s="26"/>
-      <c r="J120" s="26"/>
-      <c r="K120" s="26"/>
-      <c r="L120" s="26"/>
+      <c r="I120" s="25"/>
+      <c r="J120" s="25"/>
+      <c r="K120" s="25"/>
+      <c r="L120" s="25"/>
       <c r="M120" s="11"/>
       <c r="N120" s="11"/>
       <c r="O120" s="11"/>
@@ -6826,10 +7183,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S120" s="23"/>
-      <c r="T120" s="23"/>
+      <c r="S120" s="22"/>
+      <c r="T120" s="22"/>
       <c r="U120" s="7"/>
-      <c r="V120" s="28"/>
+      <c r="V120" s="27"/>
     </row>
     <row r="121" spans="1:22">
       <c r="A121" s="10"/>
@@ -6837,13 +7194,13 @@
       <c r="C121" s="12"/>
       <c r="D121" s="12"/>
       <c r="E121" s="12"/>
-      <c r="F121" s="23"/>
-      <c r="G121" s="23"/>
+      <c r="F121" s="22"/>
+      <c r="G121" s="22"/>
       <c r="H121" s="11"/>
-      <c r="I121" s="26"/>
-      <c r="J121" s="26"/>
-      <c r="K121" s="26"/>
-      <c r="L121" s="26"/>
+      <c r="I121" s="25"/>
+      <c r="J121" s="25"/>
+      <c r="K121" s="25"/>
+      <c r="L121" s="25"/>
       <c r="M121" s="11"/>
       <c r="N121" s="11"/>
       <c r="O121" s="11"/>
@@ -6856,10 +7213,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S121" s="23"/>
-      <c r="T121" s="23"/>
+      <c r="S121" s="22"/>
+      <c r="T121" s="22"/>
       <c r="U121" s="7"/>
-      <c r="V121" s="28"/>
+      <c r="V121" s="27"/>
     </row>
     <row r="122" spans="1:22">
       <c r="A122" s="10"/>
@@ -6867,13 +7224,13 @@
       <c r="C122" s="12"/>
       <c r="D122" s="12"/>
       <c r="E122" s="12"/>
-      <c r="F122" s="23"/>
-      <c r="G122" s="23"/>
+      <c r="F122" s="22"/>
+      <c r="G122" s="22"/>
       <c r="H122" s="11"/>
-      <c r="I122" s="26"/>
-      <c r="J122" s="26"/>
-      <c r="K122" s="26"/>
-      <c r="L122" s="26"/>
+      <c r="I122" s="25"/>
+      <c r="J122" s="25"/>
+      <c r="K122" s="25"/>
+      <c r="L122" s="25"/>
       <c r="M122" s="11"/>
       <c r="N122" s="11"/>
       <c r="O122" s="11"/>
@@ -6886,10 +7243,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S122" s="23"/>
-      <c r="T122" s="23"/>
+      <c r="S122" s="22"/>
+      <c r="T122" s="22"/>
       <c r="U122" s="7"/>
-      <c r="V122" s="28"/>
+      <c r="V122" s="27"/>
     </row>
     <row r="123" spans="1:22">
       <c r="A123" s="10"/>
@@ -6897,13 +7254,13 @@
       <c r="C123" s="12"/>
       <c r="D123" s="12"/>
       <c r="E123" s="12"/>
-      <c r="F123" s="23"/>
-      <c r="G123" s="23"/>
+      <c r="F123" s="22"/>
+      <c r="G123" s="22"/>
       <c r="H123" s="11"/>
-      <c r="I123" s="26"/>
-      <c r="J123" s="26"/>
-      <c r="K123" s="26"/>
-      <c r="L123" s="26"/>
+      <c r="I123" s="25"/>
+      <c r="J123" s="25"/>
+      <c r="K123" s="25"/>
+      <c r="L123" s="25"/>
       <c r="M123" s="11"/>
       <c r="N123" s="11"/>
       <c r="O123" s="11"/>
@@ -6916,10 +7273,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S123" s="23"/>
-      <c r="T123" s="23"/>
+      <c r="S123" s="22"/>
+      <c r="T123" s="22"/>
       <c r="U123" s="7"/>
-      <c r="V123" s="28"/>
+      <c r="V123" s="27"/>
     </row>
     <row r="124" spans="1:22">
       <c r="A124" s="10"/>
@@ -6927,13 +7284,13 @@
       <c r="C124" s="12"/>
       <c r="D124" s="12"/>
       <c r="E124" s="12"/>
-      <c r="F124" s="23"/>
-      <c r="G124" s="23"/>
+      <c r="F124" s="22"/>
+      <c r="G124" s="22"/>
       <c r="H124" s="11"/>
-      <c r="I124" s="26"/>
-      <c r="J124" s="26"/>
-      <c r="K124" s="26"/>
-      <c r="L124" s="26"/>
+      <c r="I124" s="25"/>
+      <c r="J124" s="25"/>
+      <c r="K124" s="25"/>
+      <c r="L124" s="25"/>
       <c r="M124" s="11"/>
       <c r="N124" s="11"/>
       <c r="O124" s="11"/>
@@ -6946,10 +7303,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S124" s="23"/>
-      <c r="T124" s="23"/>
+      <c r="S124" s="22"/>
+      <c r="T124" s="22"/>
       <c r="U124" s="7"/>
-      <c r="V124" s="28"/>
+      <c r="V124" s="27"/>
     </row>
     <row r="125" spans="1:22">
       <c r="A125" s="10"/>
@@ -6957,13 +7314,13 @@
       <c r="C125" s="12"/>
       <c r="D125" s="12"/>
       <c r="E125" s="12"/>
-      <c r="F125" s="23"/>
-      <c r="G125" s="23"/>
+      <c r="F125" s="22"/>
+      <c r="G125" s="22"/>
       <c r="H125" s="11"/>
-      <c r="I125" s="26"/>
-      <c r="J125" s="26"/>
-      <c r="K125" s="26"/>
-      <c r="L125" s="26"/>
+      <c r="I125" s="25"/>
+      <c r="J125" s="25"/>
+      <c r="K125" s="25"/>
+      <c r="L125" s="25"/>
       <c r="M125" s="11"/>
       <c r="N125" s="11"/>
       <c r="O125" s="11"/>
@@ -6976,10 +7333,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S125" s="23"/>
-      <c r="T125" s="23"/>
+      <c r="S125" s="22"/>
+      <c r="T125" s="22"/>
       <c r="U125" s="7"/>
-      <c r="V125" s="28"/>
+      <c r="V125" s="27"/>
     </row>
     <row r="126" spans="1:22">
       <c r="A126" s="10"/>
@@ -6987,13 +7344,13 @@
       <c r="C126" s="12"/>
       <c r="D126" s="12"/>
       <c r="E126" s="12"/>
-      <c r="F126" s="23"/>
-      <c r="G126" s="23"/>
+      <c r="F126" s="22"/>
+      <c r="G126" s="22"/>
       <c r="H126" s="11"/>
-      <c r="I126" s="26"/>
-      <c r="J126" s="26"/>
-      <c r="K126" s="26"/>
-      <c r="L126" s="26"/>
+      <c r="I126" s="25"/>
+      <c r="J126" s="25"/>
+      <c r="K126" s="25"/>
+      <c r="L126" s="25"/>
       <c r="M126" s="11"/>
       <c r="N126" s="11"/>
       <c r="O126" s="11"/>
@@ -7006,10 +7363,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S126" s="23"/>
-      <c r="T126" s="23"/>
+      <c r="S126" s="22"/>
+      <c r="T126" s="22"/>
       <c r="U126" s="7"/>
-      <c r="V126" s="28"/>
+      <c r="V126" s="27"/>
     </row>
     <row r="127" spans="1:22">
       <c r="A127" s="10"/>
@@ -7017,13 +7374,13 @@
       <c r="C127" s="12"/>
       <c r="D127" s="12"/>
       <c r="E127" s="12"/>
-      <c r="F127" s="23"/>
-      <c r="G127" s="23"/>
+      <c r="F127" s="22"/>
+      <c r="G127" s="22"/>
       <c r="H127" s="11"/>
-      <c r="I127" s="26"/>
-      <c r="J127" s="26"/>
-      <c r="K127" s="26"/>
-      <c r="L127" s="26"/>
+      <c r="I127" s="25"/>
+      <c r="J127" s="25"/>
+      <c r="K127" s="25"/>
+      <c r="L127" s="25"/>
       <c r="M127" s="11"/>
       <c r="N127" s="11"/>
       <c r="O127" s="11"/>
@@ -7036,10 +7393,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S127" s="23"/>
-      <c r="T127" s="23"/>
+      <c r="S127" s="22"/>
+      <c r="T127" s="22"/>
       <c r="U127" s="7"/>
-      <c r="V127" s="28"/>
+      <c r="V127" s="27"/>
     </row>
     <row r="128" spans="1:22">
       <c r="A128" s="10"/>
@@ -7047,13 +7404,13 @@
       <c r="C128" s="12"/>
       <c r="D128" s="12"/>
       <c r="E128" s="12"/>
-      <c r="F128" s="23"/>
-      <c r="G128" s="23"/>
+      <c r="F128" s="22"/>
+      <c r="G128" s="22"/>
       <c r="H128" s="11"/>
-      <c r="I128" s="26"/>
-      <c r="J128" s="26"/>
-      <c r="K128" s="26"/>
-      <c r="L128" s="26"/>
+      <c r="I128" s="25"/>
+      <c r="J128" s="25"/>
+      <c r="K128" s="25"/>
+      <c r="L128" s="25"/>
       <c r="M128" s="11"/>
       <c r="N128" s="11"/>
       <c r="O128" s="11"/>
@@ -7066,10 +7423,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S128" s="23"/>
-      <c r="T128" s="23"/>
+      <c r="S128" s="22"/>
+      <c r="T128" s="22"/>
       <c r="U128" s="7"/>
-      <c r="V128" s="28"/>
+      <c r="V128" s="27"/>
     </row>
     <row r="129" spans="1:22">
       <c r="A129" s="10"/>
@@ -7077,13 +7434,13 @@
       <c r="C129" s="12"/>
       <c r="D129" s="12"/>
       <c r="E129" s="12"/>
-      <c r="F129" s="23"/>
-      <c r="G129" s="23"/>
+      <c r="F129" s="22"/>
+      <c r="G129" s="22"/>
       <c r="H129" s="11"/>
-      <c r="I129" s="26"/>
-      <c r="J129" s="26"/>
-      <c r="K129" s="26"/>
-      <c r="L129" s="26"/>
+      <c r="I129" s="25"/>
+      <c r="J129" s="25"/>
+      <c r="K129" s="25"/>
+      <c r="L129" s="25"/>
       <c r="M129" s="11"/>
       <c r="N129" s="11"/>
       <c r="O129" s="11"/>
@@ -7096,10 +7453,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S129" s="23"/>
-      <c r="T129" s="23"/>
+      <c r="S129" s="22"/>
+      <c r="T129" s="22"/>
       <c r="U129" s="7"/>
-      <c r="V129" s="28"/>
+      <c r="V129" s="27"/>
     </row>
     <row r="130" spans="1:22">
       <c r="A130" s="10"/>
@@ -7107,13 +7464,13 @@
       <c r="C130" s="12"/>
       <c r="D130" s="12"/>
       <c r="E130" s="12"/>
-      <c r="F130" s="23"/>
-      <c r="G130" s="23"/>
+      <c r="F130" s="22"/>
+      <c r="G130" s="22"/>
       <c r="H130" s="11"/>
-      <c r="I130" s="26"/>
-      <c r="J130" s="26"/>
-      <c r="K130" s="26"/>
-      <c r="L130" s="26"/>
+      <c r="I130" s="25"/>
+      <c r="J130" s="25"/>
+      <c r="K130" s="25"/>
+      <c r="L130" s="25"/>
       <c r="M130" s="11"/>
       <c r="N130" s="11"/>
       <c r="O130" s="11"/>
@@ -7126,10 +7483,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S130" s="23"/>
-      <c r="T130" s="23"/>
+      <c r="S130" s="22"/>
+      <c r="T130" s="22"/>
       <c r="U130" s="7"/>
-      <c r="V130" s="28"/>
+      <c r="V130" s="27"/>
     </row>
     <row r="131" spans="1:22">
       <c r="A131" s="10"/>
@@ -7137,13 +7494,13 @@
       <c r="C131" s="12"/>
       <c r="D131" s="12"/>
       <c r="E131" s="12"/>
-      <c r="F131" s="23"/>
-      <c r="G131" s="23"/>
+      <c r="F131" s="22"/>
+      <c r="G131" s="22"/>
       <c r="H131" s="11"/>
-      <c r="I131" s="26"/>
-      <c r="J131" s="26"/>
-      <c r="K131" s="26"/>
-      <c r="L131" s="26"/>
+      <c r="I131" s="25"/>
+      <c r="J131" s="25"/>
+      <c r="K131" s="25"/>
+      <c r="L131" s="25"/>
       <c r="M131" s="11"/>
       <c r="N131" s="11"/>
       <c r="O131" s="11"/>
@@ -7156,10 +7513,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S131" s="23"/>
-      <c r="T131" s="23"/>
+      <c r="S131" s="22"/>
+      <c r="T131" s="22"/>
       <c r="U131" s="7"/>
-      <c r="V131" s="28"/>
+      <c r="V131" s="27"/>
     </row>
     <row r="132" spans="1:22">
       <c r="A132" s="10"/>
@@ -7167,13 +7524,13 @@
       <c r="C132" s="12"/>
       <c r="D132" s="12"/>
       <c r="E132" s="12"/>
-      <c r="F132" s="23"/>
-      <c r="G132" s="23"/>
+      <c r="F132" s="22"/>
+      <c r="G132" s="22"/>
       <c r="H132" s="11"/>
-      <c r="I132" s="26"/>
-      <c r="J132" s="26"/>
-      <c r="K132" s="26"/>
-      <c r="L132" s="26"/>
+      <c r="I132" s="25"/>
+      <c r="J132" s="25"/>
+      <c r="K132" s="25"/>
+      <c r="L132" s="25"/>
       <c r="M132" s="11"/>
       <c r="N132" s="11"/>
       <c r="O132" s="11"/>
@@ -7186,10 +7543,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S132" s="23"/>
-      <c r="T132" s="23"/>
+      <c r="S132" s="22"/>
+      <c r="T132" s="22"/>
       <c r="U132" s="7"/>
-      <c r="V132" s="28"/>
+      <c r="V132" s="27"/>
     </row>
     <row r="133" spans="1:22">
       <c r="A133" s="10"/>
@@ -7197,13 +7554,13 @@
       <c r="C133" s="12"/>
       <c r="D133" s="12"/>
       <c r="E133" s="12"/>
-      <c r="F133" s="23"/>
-      <c r="G133" s="23"/>
+      <c r="F133" s="22"/>
+      <c r="G133" s="22"/>
       <c r="H133" s="11"/>
-      <c r="I133" s="26"/>
-      <c r="J133" s="26"/>
-      <c r="K133" s="26"/>
-      <c r="L133" s="26"/>
+      <c r="I133" s="25"/>
+      <c r="J133" s="25"/>
+      <c r="K133" s="25"/>
+      <c r="L133" s="25"/>
       <c r="M133" s="11"/>
       <c r="N133" s="11"/>
       <c r="O133" s="11"/>
@@ -7216,10 +7573,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S133" s="23"/>
-      <c r="T133" s="23"/>
+      <c r="S133" s="22"/>
+      <c r="T133" s="22"/>
       <c r="U133" s="7"/>
-      <c r="V133" s="28"/>
+      <c r="V133" s="27"/>
     </row>
     <row r="134" spans="1:22">
       <c r="A134" s="10"/>
@@ -7227,13 +7584,13 @@
       <c r="C134" s="12"/>
       <c r="D134" s="12"/>
       <c r="E134" s="12"/>
-      <c r="F134" s="23"/>
-      <c r="G134" s="23"/>
+      <c r="F134" s="22"/>
+      <c r="G134" s="22"/>
       <c r="H134" s="11"/>
-      <c r="I134" s="26"/>
-      <c r="J134" s="26"/>
-      <c r="K134" s="26"/>
-      <c r="L134" s="26"/>
+      <c r="I134" s="25"/>
+      <c r="J134" s="25"/>
+      <c r="K134" s="25"/>
+      <c r="L134" s="25"/>
       <c r="M134" s="11"/>
       <c r="N134" s="11"/>
       <c r="O134" s="11"/>
@@ -7246,10 +7603,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S134" s="23"/>
-      <c r="T134" s="23"/>
+      <c r="S134" s="22"/>
+      <c r="T134" s="22"/>
       <c r="U134" s="7"/>
-      <c r="V134" s="28"/>
+      <c r="V134" s="27"/>
     </row>
     <row r="135" spans="1:22">
       <c r="A135" s="10"/>
@@ -7257,13 +7614,13 @@
       <c r="C135" s="12"/>
       <c r="D135" s="12"/>
       <c r="E135" s="12"/>
-      <c r="F135" s="23"/>
-      <c r="G135" s="23"/>
+      <c r="F135" s="22"/>
+      <c r="G135" s="22"/>
       <c r="H135" s="11"/>
-      <c r="I135" s="26"/>
-      <c r="J135" s="26"/>
-      <c r="K135" s="26"/>
-      <c r="L135" s="26"/>
+      <c r="I135" s="25"/>
+      <c r="J135" s="25"/>
+      <c r="K135" s="25"/>
+      <c r="L135" s="25"/>
       <c r="M135" s="11"/>
       <c r="N135" s="11"/>
       <c r="O135" s="11"/>
@@ -7276,10 +7633,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S135" s="23"/>
-      <c r="T135" s="23"/>
+      <c r="S135" s="22"/>
+      <c r="T135" s="22"/>
       <c r="U135" s="7"/>
-      <c r="V135" s="28"/>
+      <c r="V135" s="27"/>
     </row>
     <row r="136" spans="1:22">
       <c r="A136" s="10"/>
@@ -7287,13 +7644,13 @@
       <c r="C136" s="12"/>
       <c r="D136" s="12"/>
       <c r="E136" s="12"/>
-      <c r="F136" s="23"/>
-      <c r="G136" s="23"/>
+      <c r="F136" s="22"/>
+      <c r="G136" s="22"/>
       <c r="H136" s="11"/>
-      <c r="I136" s="26"/>
-      <c r="J136" s="26"/>
-      <c r="K136" s="26"/>
-      <c r="L136" s="26"/>
+      <c r="I136" s="25"/>
+      <c r="J136" s="25"/>
+      <c r="K136" s="25"/>
+      <c r="L136" s="25"/>
       <c r="M136" s="11"/>
       <c r="N136" s="11"/>
       <c r="O136" s="11"/>
@@ -7306,10 +7663,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S136" s="23"/>
-      <c r="T136" s="23"/>
+      <c r="S136" s="22"/>
+      <c r="T136" s="22"/>
       <c r="U136" s="7"/>
-      <c r="V136" s="28"/>
+      <c r="V136" s="27"/>
     </row>
     <row r="137" spans="1:22">
       <c r="A137" s="10"/>
@@ -7317,13 +7674,13 @@
       <c r="C137" s="12"/>
       <c r="D137" s="12"/>
       <c r="E137" s="12"/>
-      <c r="F137" s="23"/>
-      <c r="G137" s="23"/>
+      <c r="F137" s="22"/>
+      <c r="G137" s="22"/>
       <c r="H137" s="11"/>
-      <c r="I137" s="26"/>
-      <c r="J137" s="26"/>
-      <c r="K137" s="26"/>
-      <c r="L137" s="26"/>
+      <c r="I137" s="25"/>
+      <c r="J137" s="25"/>
+      <c r="K137" s="25"/>
+      <c r="L137" s="25"/>
       <c r="M137" s="11"/>
       <c r="N137" s="11"/>
       <c r="O137" s="11"/>
@@ -7336,10 +7693,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S137" s="23"/>
-      <c r="T137" s="23"/>
+      <c r="S137" s="22"/>
+      <c r="T137" s="22"/>
       <c r="U137" s="7"/>
-      <c r="V137" s="28"/>
+      <c r="V137" s="27"/>
     </row>
     <row r="138" spans="1:22">
       <c r="A138" s="10"/>
@@ -7347,13 +7704,13 @@
       <c r="C138" s="12"/>
       <c r="D138" s="12"/>
       <c r="E138" s="12"/>
-      <c r="F138" s="23"/>
-      <c r="G138" s="23"/>
+      <c r="F138" s="22"/>
+      <c r="G138" s="22"/>
       <c r="H138" s="11"/>
-      <c r="I138" s="26"/>
-      <c r="J138" s="26"/>
-      <c r="K138" s="26"/>
-      <c r="L138" s="26"/>
+      <c r="I138" s="25"/>
+      <c r="J138" s="25"/>
+      <c r="K138" s="25"/>
+      <c r="L138" s="25"/>
       <c r="M138" s="11"/>
       <c r="N138" s="11"/>
       <c r="O138" s="11"/>
@@ -7366,10 +7723,10 @@
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="S138" s="23"/>
-      <c r="T138" s="23"/>
+      <c r="S138" s="22"/>
+      <c r="T138" s="22"/>
       <c r="U138" s="7"/>
-      <c r="V138" s="28"/>
+      <c r="V138" s="27"/>
     </row>
     <row r="139" spans="1:22">
       <c r="A139" s="10"/>
@@ -7377,13 +7734,13 @@
       <c r="C139" s="12"/>
       <c r="D139" s="12"/>
       <c r="E139" s="12"/>
-      <c r="F139" s="23"/>
-      <c r="G139" s="23"/>
+      <c r="F139" s="22"/>
+      <c r="G139" s="22"/>
       <c r="H139" s="11"/>
-      <c r="I139" s="26"/>
-      <c r="J139" s="26"/>
-      <c r="K139" s="26"/>
-      <c r="L139" s="26"/>
+      <c r="I139" s="25"/>
+      <c r="J139" s="25"/>
+      <c r="K139" s="25"/>
+      <c r="L139" s="25"/>
       <c r="M139" s="11"/>
       <c r="N139" s="11"/>
       <c r="O139" s="11"/>
@@ -7396,10 +7753,10 @@
         <f t="shared" ref="R139:R170" ca="1" si="9">IF(E139="","",TODAY()-E139)</f>
         <v/>
       </c>
-      <c r="S139" s="23"/>
-      <c r="T139" s="23"/>
+      <c r="S139" s="22"/>
+      <c r="T139" s="22"/>
       <c r="U139" s="7"/>
-      <c r="V139" s="28"/>
+      <c r="V139" s="27"/>
     </row>
     <row r="140" spans="1:22">
       <c r="A140" s="10"/>
@@ -7407,13 +7764,13 @@
       <c r="C140" s="12"/>
       <c r="D140" s="12"/>
       <c r="E140" s="12"/>
-      <c r="F140" s="23"/>
-      <c r="G140" s="23"/>
+      <c r="F140" s="22"/>
+      <c r="G140" s="22"/>
       <c r="H140" s="11"/>
-      <c r="I140" s="26"/>
-      <c r="J140" s="26"/>
-      <c r="K140" s="26"/>
-      <c r="L140" s="26"/>
+      <c r="I140" s="25"/>
+      <c r="J140" s="25"/>
+      <c r="K140" s="25"/>
+      <c r="L140" s="25"/>
       <c r="M140" s="11"/>
       <c r="N140" s="11"/>
       <c r="O140" s="11"/>
@@ -7426,10 +7783,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S140" s="23"/>
-      <c r="T140" s="23"/>
+      <c r="S140" s="22"/>
+      <c r="T140" s="22"/>
       <c r="U140" s="7"/>
-      <c r="V140" s="28"/>
+      <c r="V140" s="27"/>
     </row>
     <row r="141" spans="1:22">
       <c r="A141" s="10"/>
@@ -7437,13 +7794,13 @@
       <c r="C141" s="12"/>
       <c r="D141" s="12"/>
       <c r="E141" s="12"/>
-      <c r="F141" s="23"/>
-      <c r="G141" s="23"/>
+      <c r="F141" s="22"/>
+      <c r="G141" s="22"/>
       <c r="H141" s="11"/>
-      <c r="I141" s="26"/>
-      <c r="J141" s="26"/>
-      <c r="K141" s="26"/>
-      <c r="L141" s="26"/>
+      <c r="I141" s="25"/>
+      <c r="J141" s="25"/>
+      <c r="K141" s="25"/>
+      <c r="L141" s="25"/>
       <c r="M141" s="11"/>
       <c r="N141" s="11"/>
       <c r="O141" s="11"/>
@@ -7456,10 +7813,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S141" s="23"/>
-      <c r="T141" s="23"/>
+      <c r="S141" s="22"/>
+      <c r="T141" s="22"/>
       <c r="U141" s="7"/>
-      <c r="V141" s="28"/>
+      <c r="V141" s="27"/>
     </row>
     <row r="142" spans="1:22">
       <c r="A142" s="10"/>
@@ -7467,13 +7824,13 @@
       <c r="C142" s="12"/>
       <c r="D142" s="12"/>
       <c r="E142" s="12"/>
-      <c r="F142" s="23"/>
-      <c r="G142" s="23"/>
+      <c r="F142" s="22"/>
+      <c r="G142" s="22"/>
       <c r="H142" s="11"/>
-      <c r="I142" s="26"/>
-      <c r="J142" s="26"/>
-      <c r="K142" s="26"/>
-      <c r="L142" s="26"/>
+      <c r="I142" s="25"/>
+      <c r="J142" s="25"/>
+      <c r="K142" s="25"/>
+      <c r="L142" s="25"/>
       <c r="M142" s="11"/>
       <c r="N142" s="11"/>
       <c r="O142" s="11"/>
@@ -7486,10 +7843,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S142" s="23"/>
-      <c r="T142" s="23"/>
+      <c r="S142" s="22"/>
+      <c r="T142" s="22"/>
       <c r="U142" s="7"/>
-      <c r="V142" s="28"/>
+      <c r="V142" s="27"/>
     </row>
     <row r="143" spans="1:22">
       <c r="A143" s="10"/>
@@ -7497,13 +7854,13 @@
       <c r="C143" s="12"/>
       <c r="D143" s="12"/>
       <c r="E143" s="12"/>
-      <c r="F143" s="23"/>
-      <c r="G143" s="23"/>
+      <c r="F143" s="22"/>
+      <c r="G143" s="22"/>
       <c r="H143" s="11"/>
-      <c r="I143" s="26"/>
-      <c r="J143" s="26"/>
-      <c r="K143" s="26"/>
-      <c r="L143" s="26"/>
+      <c r="I143" s="25"/>
+      <c r="J143" s="25"/>
+      <c r="K143" s="25"/>
+      <c r="L143" s="25"/>
       <c r="M143" s="11"/>
       <c r="N143" s="11"/>
       <c r="O143" s="11"/>
@@ -7516,10 +7873,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S143" s="23"/>
-      <c r="T143" s="23"/>
+      <c r="S143" s="22"/>
+      <c r="T143" s="22"/>
       <c r="U143" s="7"/>
-      <c r="V143" s="28"/>
+      <c r="V143" s="27"/>
     </row>
     <row r="144" spans="1:22">
       <c r="A144" s="10"/>
@@ -7527,13 +7884,13 @@
       <c r="C144" s="12"/>
       <c r="D144" s="12"/>
       <c r="E144" s="12"/>
-      <c r="F144" s="23"/>
-      <c r="G144" s="23"/>
+      <c r="F144" s="22"/>
+      <c r="G144" s="22"/>
       <c r="H144" s="11"/>
-      <c r="I144" s="26"/>
-      <c r="J144" s="26"/>
-      <c r="K144" s="26"/>
-      <c r="L144" s="26"/>
+      <c r="I144" s="25"/>
+      <c r="J144" s="25"/>
+      <c r="K144" s="25"/>
+      <c r="L144" s="25"/>
       <c r="M144" s="11"/>
       <c r="N144" s="11"/>
       <c r="O144" s="11"/>
@@ -7546,10 +7903,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S144" s="23"/>
-      <c r="T144" s="23"/>
+      <c r="S144" s="22"/>
+      <c r="T144" s="22"/>
       <c r="U144" s="7"/>
-      <c r="V144" s="28"/>
+      <c r="V144" s="27"/>
     </row>
     <row r="145" spans="1:22">
       <c r="A145" s="10"/>
@@ -7557,13 +7914,13 @@
       <c r="C145" s="12"/>
       <c r="D145" s="12"/>
       <c r="E145" s="12"/>
-      <c r="F145" s="23"/>
-      <c r="G145" s="23"/>
+      <c r="F145" s="22"/>
+      <c r="G145" s="22"/>
       <c r="H145" s="11"/>
-      <c r="I145" s="26"/>
-      <c r="J145" s="26"/>
-      <c r="K145" s="26"/>
-      <c r="L145" s="26"/>
+      <c r="I145" s="25"/>
+      <c r="J145" s="25"/>
+      <c r="K145" s="25"/>
+      <c r="L145" s="25"/>
       <c r="M145" s="11"/>
       <c r="N145" s="11"/>
       <c r="O145" s="11"/>
@@ -7576,10 +7933,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S145" s="23"/>
-      <c r="T145" s="23"/>
+      <c r="S145" s="22"/>
+      <c r="T145" s="22"/>
       <c r="U145" s="7"/>
-      <c r="V145" s="28"/>
+      <c r="V145" s="27"/>
     </row>
     <row r="146" spans="1:22">
       <c r="A146" s="10"/>
@@ -7587,13 +7944,13 @@
       <c r="C146" s="12"/>
       <c r="D146" s="12"/>
       <c r="E146" s="12"/>
-      <c r="F146" s="23"/>
-      <c r="G146" s="23"/>
+      <c r="F146" s="22"/>
+      <c r="G146" s="22"/>
       <c r="H146" s="11"/>
-      <c r="I146" s="26"/>
-      <c r="J146" s="26"/>
-      <c r="K146" s="26"/>
-      <c r="L146" s="26"/>
+      <c r="I146" s="25"/>
+      <c r="J146" s="25"/>
+      <c r="K146" s="25"/>
+      <c r="L146" s="25"/>
       <c r="M146" s="11"/>
       <c r="N146" s="11"/>
       <c r="O146" s="11"/>
@@ -7606,10 +7963,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S146" s="23"/>
-      <c r="T146" s="23"/>
+      <c r="S146" s="22"/>
+      <c r="T146" s="22"/>
       <c r="U146" s="7"/>
-      <c r="V146" s="28"/>
+      <c r="V146" s="27"/>
     </row>
     <row r="147" spans="1:22">
       <c r="A147" s="10"/>
@@ -7617,13 +7974,13 @@
       <c r="C147" s="12"/>
       <c r="D147" s="12"/>
       <c r="E147" s="12"/>
-      <c r="F147" s="23"/>
-      <c r="G147" s="23"/>
+      <c r="F147" s="22"/>
+      <c r="G147" s="22"/>
       <c r="H147" s="11"/>
-      <c r="I147" s="26"/>
-      <c r="J147" s="26"/>
-      <c r="K147" s="26"/>
-      <c r="L147" s="26"/>
+      <c r="I147" s="25"/>
+      <c r="J147" s="25"/>
+      <c r="K147" s="25"/>
+      <c r="L147" s="25"/>
       <c r="M147" s="11"/>
       <c r="N147" s="11"/>
       <c r="O147" s="11"/>
@@ -7636,10 +7993,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S147" s="23"/>
-      <c r="T147" s="23"/>
+      <c r="S147" s="22"/>
+      <c r="T147" s="22"/>
       <c r="U147" s="7"/>
-      <c r="V147" s="28"/>
+      <c r="V147" s="27"/>
     </row>
     <row r="148" spans="1:22">
       <c r="A148" s="10"/>
@@ -7647,13 +8004,13 @@
       <c r="C148" s="12"/>
       <c r="D148" s="12"/>
       <c r="E148" s="12"/>
-      <c r="F148" s="23"/>
-      <c r="G148" s="23"/>
+      <c r="F148" s="22"/>
+      <c r="G148" s="22"/>
       <c r="H148" s="11"/>
-      <c r="I148" s="26"/>
-      <c r="J148" s="26"/>
-      <c r="K148" s="26"/>
-      <c r="L148" s="26"/>
+      <c r="I148" s="25"/>
+      <c r="J148" s="25"/>
+      <c r="K148" s="25"/>
+      <c r="L148" s="25"/>
       <c r="M148" s="11"/>
       <c r="N148" s="11"/>
       <c r="O148" s="11"/>
@@ -7666,10 +8023,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S148" s="23"/>
-      <c r="T148" s="23"/>
+      <c r="S148" s="22"/>
+      <c r="T148" s="22"/>
       <c r="U148" s="7"/>
-      <c r="V148" s="28"/>
+      <c r="V148" s="27"/>
     </row>
     <row r="149" spans="1:22">
       <c r="A149" s="10"/>
@@ -7677,13 +8034,13 @@
       <c r="C149" s="12"/>
       <c r="D149" s="12"/>
       <c r="E149" s="12"/>
-      <c r="F149" s="23"/>
-      <c r="G149" s="23"/>
+      <c r="F149" s="22"/>
+      <c r="G149" s="22"/>
       <c r="H149" s="11"/>
-      <c r="I149" s="26"/>
-      <c r="J149" s="26"/>
-      <c r="K149" s="26"/>
-      <c r="L149" s="26"/>
+      <c r="I149" s="25"/>
+      <c r="J149" s="25"/>
+      <c r="K149" s="25"/>
+      <c r="L149" s="25"/>
       <c r="M149" s="11"/>
       <c r="N149" s="11"/>
       <c r="O149" s="11"/>
@@ -7696,10 +8053,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S149" s="23"/>
-      <c r="T149" s="23"/>
+      <c r="S149" s="22"/>
+      <c r="T149" s="22"/>
       <c r="U149" s="7"/>
-      <c r="V149" s="28"/>
+      <c r="V149" s="27"/>
     </row>
     <row r="150" spans="1:22">
       <c r="A150" s="10"/>
@@ -7707,13 +8064,13 @@
       <c r="C150" s="12"/>
       <c r="D150" s="12"/>
       <c r="E150" s="12"/>
-      <c r="F150" s="23"/>
-      <c r="G150" s="23"/>
+      <c r="F150" s="22"/>
+      <c r="G150" s="22"/>
       <c r="H150" s="11"/>
-      <c r="I150" s="26"/>
-      <c r="J150" s="26"/>
-      <c r="K150" s="26"/>
-      <c r="L150" s="26"/>
+      <c r="I150" s="25"/>
+      <c r="J150" s="25"/>
+      <c r="K150" s="25"/>
+      <c r="L150" s="25"/>
       <c r="M150" s="11"/>
       <c r="N150" s="11"/>
       <c r="O150" s="11"/>
@@ -7726,10 +8083,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S150" s="23"/>
-      <c r="T150" s="23"/>
+      <c r="S150" s="22"/>
+      <c r="T150" s="22"/>
       <c r="U150" s="7"/>
-      <c r="V150" s="28"/>
+      <c r="V150" s="27"/>
     </row>
     <row r="151" spans="1:22">
       <c r="A151" s="10"/>
@@ -7737,13 +8094,13 @@
       <c r="C151" s="12"/>
       <c r="D151" s="12"/>
       <c r="E151" s="12"/>
-      <c r="F151" s="23"/>
-      <c r="G151" s="23"/>
+      <c r="F151" s="22"/>
+      <c r="G151" s="22"/>
       <c r="H151" s="11"/>
-      <c r="I151" s="26"/>
-      <c r="J151" s="26"/>
-      <c r="K151" s="26"/>
-      <c r="L151" s="26"/>
+      <c r="I151" s="25"/>
+      <c r="J151" s="25"/>
+      <c r="K151" s="25"/>
+      <c r="L151" s="25"/>
       <c r="M151" s="11"/>
       <c r="N151" s="11"/>
       <c r="O151" s="11"/>
@@ -7756,10 +8113,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S151" s="23"/>
-      <c r="T151" s="23"/>
+      <c r="S151" s="22"/>
+      <c r="T151" s="22"/>
       <c r="U151" s="7"/>
-      <c r="V151" s="28"/>
+      <c r="V151" s="27"/>
     </row>
     <row r="152" spans="1:22">
       <c r="A152" s="10"/>
@@ -7767,13 +8124,13 @@
       <c r="C152" s="12"/>
       <c r="D152" s="12"/>
       <c r="E152" s="12"/>
-      <c r="F152" s="23"/>
-      <c r="G152" s="23"/>
+      <c r="F152" s="22"/>
+      <c r="G152" s="22"/>
       <c r="H152" s="11"/>
-      <c r="I152" s="26"/>
-      <c r="J152" s="26"/>
-      <c r="K152" s="26"/>
-      <c r="L152" s="26"/>
+      <c r="I152" s="25"/>
+      <c r="J152" s="25"/>
+      <c r="K152" s="25"/>
+      <c r="L152" s="25"/>
       <c r="M152" s="11"/>
       <c r="N152" s="11"/>
       <c r="O152" s="11"/>
@@ -7786,10 +8143,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S152" s="23"/>
-      <c r="T152" s="23"/>
+      <c r="S152" s="22"/>
+      <c r="T152" s="22"/>
       <c r="U152" s="7"/>
-      <c r="V152" s="28"/>
+      <c r="V152" s="27"/>
     </row>
     <row r="153" spans="1:22">
       <c r="A153" s="10"/>
@@ -7797,13 +8154,13 @@
       <c r="C153" s="12"/>
       <c r="D153" s="12"/>
       <c r="E153" s="12"/>
-      <c r="F153" s="23"/>
-      <c r="G153" s="23"/>
+      <c r="F153" s="22"/>
+      <c r="G153" s="22"/>
       <c r="H153" s="11"/>
-      <c r="I153" s="26"/>
-      <c r="J153" s="26"/>
-      <c r="K153" s="26"/>
-      <c r="L153" s="26"/>
+      <c r="I153" s="25"/>
+      <c r="J153" s="25"/>
+      <c r="K153" s="25"/>
+      <c r="L153" s="25"/>
       <c r="M153" s="11"/>
       <c r="N153" s="11"/>
       <c r="O153" s="11"/>
@@ -7816,10 +8173,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S153" s="23"/>
-      <c r="T153" s="23"/>
+      <c r="S153" s="22"/>
+      <c r="T153" s="22"/>
       <c r="U153" s="7"/>
-      <c r="V153" s="28"/>
+      <c r="V153" s="27"/>
     </row>
     <row r="154" spans="1:22">
       <c r="A154" s="10"/>
@@ -7827,13 +8184,13 @@
       <c r="C154" s="12"/>
       <c r="D154" s="12"/>
       <c r="E154" s="12"/>
-      <c r="F154" s="23"/>
-      <c r="G154" s="23"/>
+      <c r="F154" s="22"/>
+      <c r="G154" s="22"/>
       <c r="H154" s="11"/>
-      <c r="I154" s="26"/>
-      <c r="J154" s="26"/>
-      <c r="K154" s="26"/>
-      <c r="L154" s="26"/>
+      <c r="I154" s="25"/>
+      <c r="J154" s="25"/>
+      <c r="K154" s="25"/>
+      <c r="L154" s="25"/>
       <c r="M154" s="11"/>
       <c r="N154" s="11"/>
       <c r="O154" s="11"/>
@@ -7846,10 +8203,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S154" s="23"/>
-      <c r="T154" s="23"/>
+      <c r="S154" s="22"/>
+      <c r="T154" s="22"/>
       <c r="U154" s="7"/>
-      <c r="V154" s="28"/>
+      <c r="V154" s="27"/>
     </row>
     <row r="155" spans="1:22">
       <c r="A155" s="10"/>
@@ -7857,13 +8214,13 @@
       <c r="C155" s="12"/>
       <c r="D155" s="12"/>
       <c r="E155" s="12"/>
-      <c r="F155" s="23"/>
-      <c r="G155" s="23"/>
+      <c r="F155" s="22"/>
+      <c r="G155" s="22"/>
       <c r="H155" s="11"/>
-      <c r="I155" s="26"/>
-      <c r="J155" s="26"/>
-      <c r="K155" s="26"/>
-      <c r="L155" s="26"/>
+      <c r="I155" s="25"/>
+      <c r="J155" s="25"/>
+      <c r="K155" s="25"/>
+      <c r="L155" s="25"/>
       <c r="M155" s="11"/>
       <c r="N155" s="11"/>
       <c r="O155" s="11"/>
@@ -7876,10 +8233,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S155" s="23"/>
-      <c r="T155" s="23"/>
+      <c r="S155" s="22"/>
+      <c r="T155" s="22"/>
       <c r="U155" s="7"/>
-      <c r="V155" s="28"/>
+      <c r="V155" s="27"/>
     </row>
     <row r="156" spans="1:22">
       <c r="A156" s="10"/>
@@ -7887,13 +8244,13 @@
       <c r="C156" s="12"/>
       <c r="D156" s="12"/>
       <c r="E156" s="12"/>
-      <c r="F156" s="23"/>
-      <c r="G156" s="23"/>
+      <c r="F156" s="22"/>
+      <c r="G156" s="22"/>
       <c r="H156" s="11"/>
-      <c r="I156" s="26"/>
-      <c r="J156" s="26"/>
-      <c r="K156" s="26"/>
-      <c r="L156" s="26"/>
+      <c r="I156" s="25"/>
+      <c r="J156" s="25"/>
+      <c r="K156" s="25"/>
+      <c r="L156" s="25"/>
       <c r="M156" s="11"/>
       <c r="N156" s="11"/>
       <c r="O156" s="11"/>
@@ -7906,10 +8263,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S156" s="23"/>
-      <c r="T156" s="23"/>
+      <c r="S156" s="22"/>
+      <c r="T156" s="22"/>
       <c r="U156" s="7"/>
-      <c r="V156" s="28"/>
+      <c r="V156" s="27"/>
     </row>
     <row r="157" spans="1:22">
       <c r="A157" s="10"/>
@@ -7917,13 +8274,13 @@
       <c r="C157" s="12"/>
       <c r="D157" s="12"/>
       <c r="E157" s="12"/>
-      <c r="F157" s="23"/>
-      <c r="G157" s="23"/>
+      <c r="F157" s="22"/>
+      <c r="G157" s="22"/>
       <c r="H157" s="11"/>
-      <c r="I157" s="26"/>
-      <c r="J157" s="26"/>
-      <c r="K157" s="26"/>
-      <c r="L157" s="26"/>
+      <c r="I157" s="25"/>
+      <c r="J157" s="25"/>
+      <c r="K157" s="25"/>
+      <c r="L157" s="25"/>
       <c r="M157" s="11"/>
       <c r="N157" s="11"/>
       <c r="O157" s="11"/>
@@ -7936,10 +8293,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S157" s="23"/>
-      <c r="T157" s="23"/>
+      <c r="S157" s="22"/>
+      <c r="T157" s="22"/>
       <c r="U157" s="7"/>
-      <c r="V157" s="28"/>
+      <c r="V157" s="27"/>
     </row>
     <row r="158" spans="1:22">
       <c r="A158" s="10"/>
@@ -7947,13 +8304,13 @@
       <c r="C158" s="12"/>
       <c r="D158" s="12"/>
       <c r="E158" s="12"/>
-      <c r="F158" s="23"/>
-      <c r="G158" s="23"/>
+      <c r="F158" s="22"/>
+      <c r="G158" s="22"/>
       <c r="H158" s="11"/>
-      <c r="I158" s="26"/>
-      <c r="J158" s="26"/>
-      <c r="K158" s="26"/>
-      <c r="L158" s="26"/>
+      <c r="I158" s="25"/>
+      <c r="J158" s="25"/>
+      <c r="K158" s="25"/>
+      <c r="L158" s="25"/>
       <c r="M158" s="11"/>
       <c r="N158" s="11"/>
       <c r="O158" s="11"/>
@@ -7966,10 +8323,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S158" s="23"/>
-      <c r="T158" s="23"/>
+      <c r="S158" s="22"/>
+      <c r="T158" s="22"/>
       <c r="U158" s="7"/>
-      <c r="V158" s="28"/>
+      <c r="V158" s="27"/>
     </row>
     <row r="159" spans="1:22">
       <c r="A159" s="10"/>
@@ -7977,13 +8334,13 @@
       <c r="C159" s="12"/>
       <c r="D159" s="12"/>
       <c r="E159" s="12"/>
-      <c r="F159" s="23"/>
-      <c r="G159" s="23"/>
+      <c r="F159" s="22"/>
+      <c r="G159" s="22"/>
       <c r="H159" s="11"/>
-      <c r="I159" s="26"/>
-      <c r="J159" s="26"/>
-      <c r="K159" s="26"/>
-      <c r="L159" s="26"/>
+      <c r="I159" s="25"/>
+      <c r="J159" s="25"/>
+      <c r="K159" s="25"/>
+      <c r="L159" s="25"/>
       <c r="M159" s="11"/>
       <c r="N159" s="11"/>
       <c r="O159" s="11"/>
@@ -7996,10 +8353,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S159" s="23"/>
-      <c r="T159" s="23"/>
+      <c r="S159" s="22"/>
+      <c r="T159" s="22"/>
       <c r="U159" s="7"/>
-      <c r="V159" s="28"/>
+      <c r="V159" s="27"/>
     </row>
     <row r="160" spans="1:22">
       <c r="A160" s="10"/>
@@ -8007,13 +8364,13 @@
       <c r="C160" s="12"/>
       <c r="D160" s="12"/>
       <c r="E160" s="12"/>
-      <c r="F160" s="23"/>
-      <c r="G160" s="23"/>
+      <c r="F160" s="22"/>
+      <c r="G160" s="22"/>
       <c r="H160" s="11"/>
-      <c r="I160" s="26"/>
-      <c r="J160" s="26"/>
-      <c r="K160" s="26"/>
-      <c r="L160" s="26"/>
+      <c r="I160" s="25"/>
+      <c r="J160" s="25"/>
+      <c r="K160" s="25"/>
+      <c r="L160" s="25"/>
       <c r="M160" s="11"/>
       <c r="N160" s="11"/>
       <c r="O160" s="11"/>
@@ -8026,10 +8383,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S160" s="23"/>
-      <c r="T160" s="23"/>
+      <c r="S160" s="22"/>
+      <c r="T160" s="22"/>
       <c r="U160" s="7"/>
-      <c r="V160" s="28"/>
+      <c r="V160" s="27"/>
     </row>
     <row r="161" spans="1:22">
       <c r="A161" s="10"/>
@@ -8037,13 +8394,13 @@
       <c r="C161" s="12"/>
       <c r="D161" s="12"/>
       <c r="E161" s="12"/>
-      <c r="F161" s="23"/>
-      <c r="G161" s="23"/>
+      <c r="F161" s="22"/>
+      <c r="G161" s="22"/>
       <c r="H161" s="11"/>
-      <c r="I161" s="26"/>
-      <c r="J161" s="26"/>
-      <c r="K161" s="26"/>
-      <c r="L161" s="26"/>
+      <c r="I161" s="25"/>
+      <c r="J161" s="25"/>
+      <c r="K161" s="25"/>
+      <c r="L161" s="25"/>
       <c r="M161" s="11"/>
       <c r="N161" s="11"/>
       <c r="O161" s="11"/>
@@ -8056,10 +8413,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S161" s="23"/>
-      <c r="T161" s="23"/>
+      <c r="S161" s="22"/>
+      <c r="T161" s="22"/>
       <c r="U161" s="7"/>
-      <c r="V161" s="28"/>
+      <c r="V161" s="27"/>
     </row>
     <row r="162" spans="1:22">
       <c r="A162" s="10"/>
@@ -8067,13 +8424,13 @@
       <c r="C162" s="12"/>
       <c r="D162" s="12"/>
       <c r="E162" s="12"/>
-      <c r="F162" s="23"/>
-      <c r="G162" s="23"/>
+      <c r="F162" s="22"/>
+      <c r="G162" s="22"/>
       <c r="H162" s="11"/>
-      <c r="I162" s="26"/>
-      <c r="J162" s="26"/>
-      <c r="K162" s="26"/>
-      <c r="L162" s="26"/>
+      <c r="I162" s="25"/>
+      <c r="J162" s="25"/>
+      <c r="K162" s="25"/>
+      <c r="L162" s="25"/>
       <c r="M162" s="11"/>
       <c r="N162" s="11"/>
       <c r="O162" s="11"/>
@@ -8086,10 +8443,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S162" s="23"/>
-      <c r="T162" s="23"/>
+      <c r="S162" s="22"/>
+      <c r="T162" s="22"/>
       <c r="U162" s="7"/>
-      <c r="V162" s="28"/>
+      <c r="V162" s="27"/>
     </row>
     <row r="163" spans="1:22">
       <c r="A163" s="10"/>
@@ -8097,13 +8454,13 @@
       <c r="C163" s="12"/>
       <c r="D163" s="12"/>
       <c r="E163" s="12"/>
-      <c r="F163" s="23"/>
-      <c r="G163" s="23"/>
+      <c r="F163" s="22"/>
+      <c r="G163" s="22"/>
       <c r="H163" s="11"/>
-      <c r="I163" s="26"/>
-      <c r="J163" s="26"/>
-      <c r="K163" s="26"/>
-      <c r="L163" s="26"/>
+      <c r="I163" s="25"/>
+      <c r="J163" s="25"/>
+      <c r="K163" s="25"/>
+      <c r="L163" s="25"/>
       <c r="M163" s="11"/>
       <c r="N163" s="11"/>
       <c r="O163" s="11"/>
@@ -8116,10 +8473,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S163" s="23"/>
-      <c r="T163" s="23"/>
+      <c r="S163" s="22"/>
+      <c r="T163" s="22"/>
       <c r="U163" s="7"/>
-      <c r="V163" s="28"/>
+      <c r="V163" s="27"/>
     </row>
     <row r="164" spans="1:22">
       <c r="A164" s="10"/>
@@ -8127,13 +8484,13 @@
       <c r="C164" s="12"/>
       <c r="D164" s="12"/>
       <c r="E164" s="12"/>
-      <c r="F164" s="23"/>
-      <c r="G164" s="23"/>
+      <c r="F164" s="22"/>
+      <c r="G164" s="22"/>
       <c r="H164" s="11"/>
-      <c r="I164" s="26"/>
-      <c r="J164" s="26"/>
-      <c r="K164" s="26"/>
-      <c r="L164" s="26"/>
+      <c r="I164" s="25"/>
+      <c r="J164" s="25"/>
+      <c r="K164" s="25"/>
+      <c r="L164" s="25"/>
       <c r="M164" s="11"/>
       <c r="N164" s="11"/>
       <c r="O164" s="11"/>
@@ -8146,10 +8503,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S164" s="23"/>
-      <c r="T164" s="23"/>
+      <c r="S164" s="22"/>
+      <c r="T164" s="22"/>
       <c r="U164" s="7"/>
-      <c r="V164" s="28"/>
+      <c r="V164" s="27"/>
     </row>
     <row r="165" spans="1:22">
       <c r="A165" s="10"/>
@@ -8157,13 +8514,13 @@
       <c r="C165" s="12"/>
       <c r="D165" s="12"/>
       <c r="E165" s="12"/>
-      <c r="F165" s="23"/>
-      <c r="G165" s="23"/>
+      <c r="F165" s="22"/>
+      <c r="G165" s="22"/>
       <c r="H165" s="11"/>
-      <c r="I165" s="26"/>
-      <c r="J165" s="26"/>
-      <c r="K165" s="26"/>
-      <c r="L165" s="26"/>
+      <c r="I165" s="25"/>
+      <c r="J165" s="25"/>
+      <c r="K165" s="25"/>
+      <c r="L165" s="25"/>
       <c r="M165" s="11"/>
       <c r="N165" s="11"/>
       <c r="O165" s="11"/>
@@ -8176,10 +8533,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S165" s="23"/>
-      <c r="T165" s="23"/>
+      <c r="S165" s="22"/>
+      <c r="T165" s="22"/>
       <c r="U165" s="7"/>
-      <c r="V165" s="28"/>
+      <c r="V165" s="27"/>
     </row>
     <row r="166" spans="1:22">
       <c r="A166" s="10"/>
@@ -8187,13 +8544,13 @@
       <c r="C166" s="12"/>
       <c r="D166" s="12"/>
       <c r="E166" s="12"/>
-      <c r="F166" s="23"/>
-      <c r="G166" s="23"/>
+      <c r="F166" s="22"/>
+      <c r="G166" s="22"/>
       <c r="H166" s="11"/>
-      <c r="I166" s="26"/>
-      <c r="J166" s="26"/>
-      <c r="K166" s="26"/>
-      <c r="L166" s="26"/>
+      <c r="I166" s="25"/>
+      <c r="J166" s="25"/>
+      <c r="K166" s="25"/>
+      <c r="L166" s="25"/>
       <c r="M166" s="11"/>
       <c r="N166" s="11"/>
       <c r="O166" s="11"/>
@@ -8206,10 +8563,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S166" s="23"/>
-      <c r="T166" s="23"/>
+      <c r="S166" s="22"/>
+      <c r="T166" s="22"/>
       <c r="U166" s="7"/>
-      <c r="V166" s="28"/>
+      <c r="V166" s="27"/>
     </row>
     <row r="167" spans="1:22">
       <c r="A167" s="10"/>
@@ -8217,13 +8574,13 @@
       <c r="C167" s="12"/>
       <c r="D167" s="12"/>
       <c r="E167" s="12"/>
-      <c r="F167" s="23"/>
-      <c r="G167" s="23"/>
+      <c r="F167" s="22"/>
+      <c r="G167" s="22"/>
       <c r="H167" s="11"/>
-      <c r="I167" s="26"/>
-      <c r="J167" s="26"/>
-      <c r="K167" s="26"/>
-      <c r="L167" s="26"/>
+      <c r="I167" s="25"/>
+      <c r="J167" s="25"/>
+      <c r="K167" s="25"/>
+      <c r="L167" s="25"/>
       <c r="M167" s="11"/>
       <c r="N167" s="11"/>
       <c r="O167" s="11"/>
@@ -8236,10 +8593,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S167" s="23"/>
-      <c r="T167" s="23"/>
+      <c r="S167" s="22"/>
+      <c r="T167" s="22"/>
       <c r="U167" s="7"/>
-      <c r="V167" s="28"/>
+      <c r="V167" s="27"/>
     </row>
     <row r="168" spans="1:22">
       <c r="A168" s="10"/>
@@ -8247,13 +8604,13 @@
       <c r="C168" s="12"/>
       <c r="D168" s="12"/>
       <c r="E168" s="12"/>
-      <c r="F168" s="23"/>
-      <c r="G168" s="23"/>
+      <c r="F168" s="22"/>
+      <c r="G168" s="22"/>
       <c r="H168" s="11"/>
-      <c r="I168" s="26"/>
-      <c r="J168" s="26"/>
-      <c r="K168" s="26"/>
-      <c r="L168" s="26"/>
+      <c r="I168" s="25"/>
+      <c r="J168" s="25"/>
+      <c r="K168" s="25"/>
+      <c r="L168" s="25"/>
       <c r="M168" s="11"/>
       <c r="N168" s="11"/>
       <c r="O168" s="11"/>
@@ -8266,10 +8623,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S168" s="23"/>
-      <c r="T168" s="23"/>
+      <c r="S168" s="22"/>
+      <c r="T168" s="22"/>
       <c r="U168" s="7"/>
-      <c r="V168" s="28"/>
+      <c r="V168" s="27"/>
     </row>
     <row r="169" spans="1:22">
       <c r="A169" s="10"/>
@@ -8277,13 +8634,13 @@
       <c r="C169" s="12"/>
       <c r="D169" s="12"/>
       <c r="E169" s="12"/>
-      <c r="F169" s="23"/>
-      <c r="G169" s="23"/>
+      <c r="F169" s="22"/>
+      <c r="G169" s="22"/>
       <c r="H169" s="11"/>
-      <c r="I169" s="26"/>
-      <c r="J169" s="26"/>
-      <c r="K169" s="26"/>
-      <c r="L169" s="26"/>
+      <c r="I169" s="25"/>
+      <c r="J169" s="25"/>
+      <c r="K169" s="25"/>
+      <c r="L169" s="25"/>
       <c r="M169" s="11"/>
       <c r="N169" s="11"/>
       <c r="O169" s="11"/>
@@ -8296,10 +8653,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S169" s="23"/>
-      <c r="T169" s="23"/>
+      <c r="S169" s="22"/>
+      <c r="T169" s="22"/>
       <c r="U169" s="7"/>
-      <c r="V169" s="28"/>
+      <c r="V169" s="27"/>
     </row>
     <row r="170" spans="1:22">
       <c r="A170" s="10"/>
@@ -8307,13 +8664,13 @@
       <c r="C170" s="12"/>
       <c r="D170" s="12"/>
       <c r="E170" s="12"/>
-      <c r="F170" s="23"/>
-      <c r="G170" s="23"/>
+      <c r="F170" s="22"/>
+      <c r="G170" s="22"/>
       <c r="H170" s="11"/>
-      <c r="I170" s="26"/>
-      <c r="J170" s="26"/>
-      <c r="K170" s="26"/>
-      <c r="L170" s="26"/>
+      <c r="I170" s="25"/>
+      <c r="J170" s="25"/>
+      <c r="K170" s="25"/>
+      <c r="L170" s="25"/>
       <c r="M170" s="11"/>
       <c r="N170" s="11"/>
       <c r="O170" s="11"/>
@@ -8326,10 +8683,10 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="S170" s="23"/>
-      <c r="T170" s="23"/>
+      <c r="S170" s="22"/>
+      <c r="T170" s="22"/>
       <c r="U170" s="7"/>
-      <c r="V170" s="28"/>
+      <c r="V170" s="27"/>
     </row>
     <row r="171" spans="1:22">
       <c r="A171" s="10"/>
@@ -8337,13 +8694,13 @@
       <c r="C171" s="12"/>
       <c r="D171" s="12"/>
       <c r="E171" s="12"/>
-      <c r="F171" s="23"/>
-      <c r="G171" s="23"/>
+      <c r="F171" s="22"/>
+      <c r="G171" s="22"/>
       <c r="H171" s="11"/>
-      <c r="I171" s="26"/>
-      <c r="J171" s="26"/>
-      <c r="K171" s="26"/>
-      <c r="L171" s="26"/>
+      <c r="I171" s="25"/>
+      <c r="J171" s="25"/>
+      <c r="K171" s="25"/>
+      <c r="L171" s="25"/>
       <c r="M171" s="11"/>
       <c r="N171" s="11"/>
       <c r="O171" s="11"/>
@@ -8356,10 +8713,10 @@
         <f t="shared" ref="R171:R202" ca="1" si="11">IF(E171="","",TODAY()-E171)</f>
         <v/>
       </c>
-      <c r="S171" s="23"/>
-      <c r="T171" s="23"/>
+      <c r="S171" s="22"/>
+      <c r="T171" s="22"/>
       <c r="U171" s="7"/>
-      <c r="V171" s="28"/>
+      <c r="V171" s="27"/>
     </row>
     <row r="172" spans="1:22">
       <c r="A172" s="10"/>
@@ -8367,13 +8724,13 @@
       <c r="C172" s="12"/>
       <c r="D172" s="12"/>
       <c r="E172" s="12"/>
-      <c r="F172" s="23"/>
-      <c r="G172" s="23"/>
+      <c r="F172" s="22"/>
+      <c r="G172" s="22"/>
       <c r="H172" s="11"/>
-      <c r="I172" s="26"/>
-      <c r="J172" s="26"/>
-      <c r="K172" s="26"/>
-      <c r="L172" s="26"/>
+      <c r="I172" s="25"/>
+      <c r="J172" s="25"/>
+      <c r="K172" s="25"/>
+      <c r="L172" s="25"/>
       <c r="M172" s="11"/>
       <c r="N172" s="11"/>
       <c r="O172" s="11"/>
@@ -8386,10 +8743,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S172" s="23"/>
-      <c r="T172" s="23"/>
+      <c r="S172" s="22"/>
+      <c r="T172" s="22"/>
       <c r="U172" s="7"/>
-      <c r="V172" s="28"/>
+      <c r="V172" s="27"/>
     </row>
     <row r="173" spans="1:22">
       <c r="A173" s="10"/>
@@ -8397,13 +8754,13 @@
       <c r="C173" s="12"/>
       <c r="D173" s="12"/>
       <c r="E173" s="12"/>
-      <c r="F173" s="23"/>
-      <c r="G173" s="23"/>
+      <c r="F173" s="22"/>
+      <c r="G173" s="22"/>
       <c r="H173" s="11"/>
-      <c r="I173" s="26"/>
-      <c r="J173" s="26"/>
-      <c r="K173" s="26"/>
-      <c r="L173" s="26"/>
+      <c r="I173" s="25"/>
+      <c r="J173" s="25"/>
+      <c r="K173" s="25"/>
+      <c r="L173" s="25"/>
       <c r="M173" s="11"/>
       <c r="N173" s="11"/>
       <c r="O173" s="11"/>
@@ -8416,10 +8773,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S173" s="23"/>
-      <c r="T173" s="23"/>
+      <c r="S173" s="22"/>
+      <c r="T173" s="22"/>
       <c r="U173" s="7"/>
-      <c r="V173" s="28"/>
+      <c r="V173" s="27"/>
     </row>
     <row r="174" spans="1:22">
       <c r="A174" s="10"/>
@@ -8427,13 +8784,13 @@
       <c r="C174" s="12"/>
       <c r="D174" s="12"/>
       <c r="E174" s="12"/>
-      <c r="F174" s="23"/>
-      <c r="G174" s="23"/>
+      <c r="F174" s="22"/>
+      <c r="G174" s="22"/>
       <c r="H174" s="11"/>
-      <c r="I174" s="26"/>
-      <c r="J174" s="26"/>
-      <c r="K174" s="26"/>
-      <c r="L174" s="26"/>
+      <c r="I174" s="25"/>
+      <c r="J174" s="25"/>
+      <c r="K174" s="25"/>
+      <c r="L174" s="25"/>
       <c r="M174" s="11"/>
       <c r="N174" s="11"/>
       <c r="O174" s="11"/>
@@ -8446,10 +8803,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S174" s="23"/>
-      <c r="T174" s="23"/>
+      <c r="S174" s="22"/>
+      <c r="T174" s="22"/>
       <c r="U174" s="7"/>
-      <c r="V174" s="28"/>
+      <c r="V174" s="27"/>
     </row>
     <row r="175" spans="1:22">
       <c r="A175" s="10"/>
@@ -8457,13 +8814,13 @@
       <c r="C175" s="12"/>
       <c r="D175" s="12"/>
       <c r="E175" s="12"/>
-      <c r="F175" s="23"/>
-      <c r="G175" s="23"/>
+      <c r="F175" s="22"/>
+      <c r="G175" s="22"/>
       <c r="H175" s="11"/>
-      <c r="I175" s="26"/>
-      <c r="J175" s="26"/>
-      <c r="K175" s="26"/>
-      <c r="L175" s="26"/>
+      <c r="I175" s="25"/>
+      <c r="J175" s="25"/>
+      <c r="K175" s="25"/>
+      <c r="L175" s="25"/>
       <c r="M175" s="11"/>
       <c r="N175" s="11"/>
       <c r="O175" s="11"/>
@@ -8476,10 +8833,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S175" s="23"/>
-      <c r="T175" s="23"/>
+      <c r="S175" s="22"/>
+      <c r="T175" s="22"/>
       <c r="U175" s="7"/>
-      <c r="V175" s="28"/>
+      <c r="V175" s="27"/>
     </row>
     <row r="176" spans="1:22">
       <c r="A176" s="10"/>
@@ -8487,13 +8844,13 @@
       <c r="C176" s="12"/>
       <c r="D176" s="12"/>
       <c r="E176" s="12"/>
-      <c r="F176" s="23"/>
-      <c r="G176" s="23"/>
+      <c r="F176" s="22"/>
+      <c r="G176" s="22"/>
       <c r="H176" s="11"/>
-      <c r="I176" s="26"/>
-      <c r="J176" s="26"/>
-      <c r="K176" s="26"/>
-      <c r="L176" s="26"/>
+      <c r="I176" s="25"/>
+      <c r="J176" s="25"/>
+      <c r="K176" s="25"/>
+      <c r="L176" s="25"/>
       <c r="M176" s="11"/>
       <c r="N176" s="11"/>
       <c r="O176" s="11"/>
@@ -8506,10 +8863,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S176" s="23"/>
-      <c r="T176" s="23"/>
+      <c r="S176" s="22"/>
+      <c r="T176" s="22"/>
       <c r="U176" s="7"/>
-      <c r="V176" s="28"/>
+      <c r="V176" s="27"/>
     </row>
     <row r="177" spans="1:22">
       <c r="A177" s="10"/>
@@ -8517,13 +8874,13 @@
       <c r="C177" s="12"/>
       <c r="D177" s="12"/>
       <c r="E177" s="12"/>
-      <c r="F177" s="23"/>
-      <c r="G177" s="23"/>
+      <c r="F177" s="22"/>
+      <c r="G177" s="22"/>
       <c r="H177" s="11"/>
-      <c r="I177" s="26"/>
-      <c r="J177" s="26"/>
-      <c r="K177" s="26"/>
-      <c r="L177" s="26"/>
+      <c r="I177" s="25"/>
+      <c r="J177" s="25"/>
+      <c r="K177" s="25"/>
+      <c r="L177" s="25"/>
       <c r="M177" s="11"/>
       <c r="N177" s="11"/>
       <c r="O177" s="11"/>
@@ -8536,10 +8893,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S177" s="23"/>
-      <c r="T177" s="23"/>
+      <c r="S177" s="22"/>
+      <c r="T177" s="22"/>
       <c r="U177" s="7"/>
-      <c r="V177" s="28"/>
+      <c r="V177" s="27"/>
     </row>
     <row r="178" spans="1:22">
       <c r="A178" s="10"/>
@@ -8547,13 +8904,13 @@
       <c r="C178" s="12"/>
       <c r="D178" s="12"/>
       <c r="E178" s="12"/>
-      <c r="F178" s="23"/>
-      <c r="G178" s="23"/>
+      <c r="F178" s="22"/>
+      <c r="G178" s="22"/>
       <c r="H178" s="11"/>
-      <c r="I178" s="26"/>
-      <c r="J178" s="26"/>
-      <c r="K178" s="26"/>
-      <c r="L178" s="26"/>
+      <c r="I178" s="25"/>
+      <c r="J178" s="25"/>
+      <c r="K178" s="25"/>
+      <c r="L178" s="25"/>
       <c r="M178" s="11"/>
       <c r="N178" s="11"/>
       <c r="O178" s="11"/>
@@ -8566,10 +8923,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S178" s="23"/>
-      <c r="T178" s="23"/>
+      <c r="S178" s="22"/>
+      <c r="T178" s="22"/>
       <c r="U178" s="7"/>
-      <c r="V178" s="28"/>
+      <c r="V178" s="27"/>
     </row>
     <row r="179" spans="1:22">
       <c r="A179" s="10"/>
@@ -8577,13 +8934,13 @@
       <c r="C179" s="12"/>
       <c r="D179" s="12"/>
       <c r="E179" s="12"/>
-      <c r="F179" s="23"/>
-      <c r="G179" s="23"/>
+      <c r="F179" s="22"/>
+      <c r="G179" s="22"/>
       <c r="H179" s="11"/>
-      <c r="I179" s="26"/>
-      <c r="J179" s="26"/>
-      <c r="K179" s="26"/>
-      <c r="L179" s="26"/>
+      <c r="I179" s="25"/>
+      <c r="J179" s="25"/>
+      <c r="K179" s="25"/>
+      <c r="L179" s="25"/>
       <c r="M179" s="11"/>
       <c r="N179" s="11"/>
       <c r="O179" s="11"/>
@@ -8596,10 +8953,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S179" s="23"/>
-      <c r="T179" s="23"/>
+      <c r="S179" s="22"/>
+      <c r="T179" s="22"/>
       <c r="U179" s="7"/>
-      <c r="V179" s="28"/>
+      <c r="V179" s="27"/>
     </row>
     <row r="180" spans="1:22">
       <c r="A180" s="10"/>
@@ -8607,13 +8964,13 @@
       <c r="C180" s="12"/>
       <c r="D180" s="12"/>
       <c r="E180" s="12"/>
-      <c r="F180" s="23"/>
-      <c r="G180" s="23"/>
+      <c r="F180" s="22"/>
+      <c r="G180" s="22"/>
       <c r="H180" s="11"/>
-      <c r="I180" s="26"/>
-      <c r="J180" s="26"/>
-      <c r="K180" s="26"/>
-      <c r="L180" s="26"/>
+      <c r="I180" s="25"/>
+      <c r="J180" s="25"/>
+      <c r="K180" s="25"/>
+      <c r="L180" s="25"/>
       <c r="M180" s="11"/>
       <c r="N180" s="11"/>
       <c r="O180" s="11"/>
@@ -8626,10 +8983,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S180" s="23"/>
-      <c r="T180" s="23"/>
+      <c r="S180" s="22"/>
+      <c r="T180" s="22"/>
       <c r="U180" s="7"/>
-      <c r="V180" s="28"/>
+      <c r="V180" s="27"/>
     </row>
     <row r="181" spans="1:22">
       <c r="A181" s="10"/>
@@ -8637,13 +8994,13 @@
       <c r="C181" s="12"/>
       <c r="D181" s="12"/>
       <c r="E181" s="12"/>
-      <c r="F181" s="23"/>
-      <c r="G181" s="23"/>
+      <c r="F181" s="22"/>
+      <c r="G181" s="22"/>
       <c r="H181" s="11"/>
-      <c r="I181" s="26"/>
-      <c r="J181" s="26"/>
-      <c r="K181" s="26"/>
-      <c r="L181" s="26"/>
+      <c r="I181" s="25"/>
+      <c r="J181" s="25"/>
+      <c r="K181" s="25"/>
+      <c r="L181" s="25"/>
       <c r="M181" s="11"/>
       <c r="N181" s="11"/>
       <c r="O181" s="11"/>
@@ -8656,10 +9013,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S181" s="23"/>
-      <c r="T181" s="23"/>
+      <c r="S181" s="22"/>
+      <c r="T181" s="22"/>
       <c r="U181" s="7"/>
-      <c r="V181" s="28"/>
+      <c r="V181" s="27"/>
     </row>
     <row r="182" spans="1:22">
       <c r="A182" s="10"/>
@@ -8667,13 +9024,13 @@
       <c r="C182" s="12"/>
       <c r="D182" s="12"/>
       <c r="E182" s="12"/>
-      <c r="F182" s="23"/>
-      <c r="G182" s="23"/>
+      <c r="F182" s="22"/>
+      <c r="G182" s="22"/>
       <c r="H182" s="11"/>
-      <c r="I182" s="26"/>
-      <c r="J182" s="26"/>
-      <c r="K182" s="26"/>
-      <c r="L182" s="26"/>
+      <c r="I182" s="25"/>
+      <c r="J182" s="25"/>
+      <c r="K182" s="25"/>
+      <c r="L182" s="25"/>
       <c r="M182" s="11"/>
       <c r="N182" s="11"/>
       <c r="O182" s="11"/>
@@ -8686,10 +9043,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S182" s="23"/>
-      <c r="T182" s="23"/>
+      <c r="S182" s="22"/>
+      <c r="T182" s="22"/>
       <c r="U182" s="7"/>
-      <c r="V182" s="28"/>
+      <c r="V182" s="27"/>
     </row>
     <row r="183" spans="1:22">
       <c r="A183" s="10"/>
@@ -8697,13 +9054,13 @@
       <c r="C183" s="12"/>
       <c r="D183" s="12"/>
       <c r="E183" s="12"/>
-      <c r="F183" s="23"/>
-      <c r="G183" s="23"/>
+      <c r="F183" s="22"/>
+      <c r="G183" s="22"/>
       <c r="H183" s="11"/>
-      <c r="I183" s="26"/>
-      <c r="J183" s="26"/>
-      <c r="K183" s="26"/>
-      <c r="L183" s="26"/>
+      <c r="I183" s="25"/>
+      <c r="J183" s="25"/>
+      <c r="K183" s="25"/>
+      <c r="L183" s="25"/>
       <c r="M183" s="11"/>
       <c r="N183" s="11"/>
       <c r="O183" s="11"/>
@@ -8716,10 +9073,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S183" s="23"/>
-      <c r="T183" s="23"/>
+      <c r="S183" s="22"/>
+      <c r="T183" s="22"/>
       <c r="U183" s="7"/>
-      <c r="V183" s="28"/>
+      <c r="V183" s="27"/>
     </row>
     <row r="184" spans="1:22">
       <c r="A184" s="10"/>
@@ -8727,13 +9084,13 @@
       <c r="C184" s="12"/>
       <c r="D184" s="12"/>
       <c r="E184" s="12"/>
-      <c r="F184" s="23"/>
-      <c r="G184" s="23"/>
+      <c r="F184" s="22"/>
+      <c r="G184" s="22"/>
       <c r="H184" s="11"/>
-      <c r="I184" s="26"/>
-      <c r="J184" s="26"/>
-      <c r="K184" s="26"/>
-      <c r="L184" s="26"/>
+      <c r="I184" s="25"/>
+      <c r="J184" s="25"/>
+      <c r="K184" s="25"/>
+      <c r="L184" s="25"/>
       <c r="M184" s="11"/>
       <c r="N184" s="11"/>
       <c r="O184" s="11"/>
@@ -8746,10 +9103,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S184" s="23"/>
-      <c r="T184" s="23"/>
+      <c r="S184" s="22"/>
+      <c r="T184" s="22"/>
       <c r="U184" s="7"/>
-      <c r="V184" s="28"/>
+      <c r="V184" s="27"/>
     </row>
     <row r="185" spans="1:22">
       <c r="A185" s="10"/>
@@ -8757,13 +9114,13 @@
       <c r="C185" s="12"/>
       <c r="D185" s="12"/>
       <c r="E185" s="12"/>
-      <c r="F185" s="23"/>
-      <c r="G185" s="23"/>
+      <c r="F185" s="22"/>
+      <c r="G185" s="22"/>
       <c r="H185" s="11"/>
-      <c r="I185" s="26"/>
-      <c r="J185" s="26"/>
-      <c r="K185" s="26"/>
-      <c r="L185" s="26"/>
+      <c r="I185" s="25"/>
+      <c r="J185" s="25"/>
+      <c r="K185" s="25"/>
+      <c r="L185" s="25"/>
       <c r="M185" s="11"/>
       <c r="N185" s="11"/>
       <c r="O185" s="11"/>
@@ -8776,10 +9133,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S185" s="23"/>
-      <c r="T185" s="23"/>
+      <c r="S185" s="22"/>
+      <c r="T185" s="22"/>
       <c r="U185" s="7"/>
-      <c r="V185" s="28"/>
+      <c r="V185" s="27"/>
     </row>
     <row r="186" spans="1:22">
       <c r="A186" s="10"/>
@@ -8787,13 +9144,13 @@
       <c r="C186" s="12"/>
       <c r="D186" s="12"/>
       <c r="E186" s="12"/>
-      <c r="F186" s="23"/>
-      <c r="G186" s="23"/>
+      <c r="F186" s="22"/>
+      <c r="G186" s="22"/>
       <c r="H186" s="11"/>
-      <c r="I186" s="26"/>
-      <c r="J186" s="26"/>
-      <c r="K186" s="26"/>
-      <c r="L186" s="26"/>
+      <c r="I186" s="25"/>
+      <c r="J186" s="25"/>
+      <c r="K186" s="25"/>
+      <c r="L186" s="25"/>
       <c r="M186" s="11"/>
       <c r="N186" s="11"/>
       <c r="O186" s="11"/>
@@ -8806,10 +9163,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S186" s="23"/>
-      <c r="T186" s="23"/>
+      <c r="S186" s="22"/>
+      <c r="T186" s="22"/>
       <c r="U186" s="7"/>
-      <c r="V186" s="28"/>
+      <c r="V186" s="27"/>
     </row>
     <row r="187" spans="1:22">
       <c r="A187" s="10"/>
@@ -8817,13 +9174,13 @@
       <c r="C187" s="12"/>
       <c r="D187" s="12"/>
       <c r="E187" s="12"/>
-      <c r="F187" s="23"/>
-      <c r="G187" s="23"/>
+      <c r="F187" s="22"/>
+      <c r="G187" s="22"/>
       <c r="H187" s="11"/>
-      <c r="I187" s="26"/>
-      <c r="J187" s="26"/>
-      <c r="K187" s="26"/>
-      <c r="L187" s="26"/>
+      <c r="I187" s="25"/>
+      <c r="J187" s="25"/>
+      <c r="K187" s="25"/>
+      <c r="L187" s="25"/>
       <c r="M187" s="11"/>
       <c r="N187" s="11"/>
       <c r="O187" s="11"/>
@@ -8836,10 +9193,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S187" s="23"/>
-      <c r="T187" s="23"/>
+      <c r="S187" s="22"/>
+      <c r="T187" s="22"/>
       <c r="U187" s="7"/>
-      <c r="V187" s="28"/>
+      <c r="V187" s="27"/>
     </row>
     <row r="188" spans="1:22">
       <c r="A188" s="10"/>
@@ -8847,13 +9204,13 @@
       <c r="C188" s="12"/>
       <c r="D188" s="12"/>
       <c r="E188" s="12"/>
-      <c r="F188" s="23"/>
-      <c r="G188" s="23"/>
+      <c r="F188" s="22"/>
+      <c r="G188" s="22"/>
       <c r="H188" s="11"/>
-      <c r="I188" s="26"/>
-      <c r="J188" s="26"/>
-      <c r="K188" s="26"/>
-      <c r="L188" s="26"/>
+      <c r="I188" s="25"/>
+      <c r="J188" s="25"/>
+      <c r="K188" s="25"/>
+      <c r="L188" s="25"/>
       <c r="M188" s="11"/>
       <c r="N188" s="11"/>
       <c r="O188" s="11"/>
@@ -8866,10 +9223,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S188" s="23"/>
-      <c r="T188" s="23"/>
+      <c r="S188" s="22"/>
+      <c r="T188" s="22"/>
       <c r="U188" s="7"/>
-      <c r="V188" s="28"/>
+      <c r="V188" s="27"/>
     </row>
     <row r="189" spans="1:22">
       <c r="A189" s="10"/>
@@ -8877,13 +9234,13 @@
       <c r="C189" s="12"/>
       <c r="D189" s="12"/>
       <c r="E189" s="12"/>
-      <c r="F189" s="23"/>
-      <c r="G189" s="23"/>
+      <c r="F189" s="22"/>
+      <c r="G189" s="22"/>
       <c r="H189" s="11"/>
-      <c r="I189" s="26"/>
-      <c r="J189" s="26"/>
-      <c r="K189" s="26"/>
-      <c r="L189" s="26"/>
+      <c r="I189" s="25"/>
+      <c r="J189" s="25"/>
+      <c r="K189" s="25"/>
+      <c r="L189" s="25"/>
       <c r="M189" s="11"/>
       <c r="N189" s="11"/>
       <c r="O189" s="11"/>
@@ -8896,10 +9253,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S189" s="23"/>
-      <c r="T189" s="23"/>
+      <c r="S189" s="22"/>
+      <c r="T189" s="22"/>
       <c r="U189" s="7"/>
-      <c r="V189" s="28"/>
+      <c r="V189" s="27"/>
     </row>
     <row r="190" spans="1:22">
       <c r="A190" s="10"/>
@@ -8907,13 +9264,13 @@
       <c r="C190" s="12"/>
       <c r="D190" s="12"/>
       <c r="E190" s="12"/>
-      <c r="F190" s="23"/>
-      <c r="G190" s="23"/>
+      <c r="F190" s="22"/>
+      <c r="G190" s="22"/>
       <c r="H190" s="11"/>
-      <c r="I190" s="26"/>
-      <c r="J190" s="26"/>
-      <c r="K190" s="26"/>
-      <c r="L190" s="26"/>
+      <c r="I190" s="25"/>
+      <c r="J190" s="25"/>
+      <c r="K190" s="25"/>
+      <c r="L190" s="25"/>
       <c r="M190" s="11"/>
       <c r="N190" s="11"/>
       <c r="O190" s="11"/>
@@ -8926,10 +9283,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S190" s="23"/>
-      <c r="T190" s="23"/>
+      <c r="S190" s="22"/>
+      <c r="T190" s="22"/>
       <c r="U190" s="7"/>
-      <c r="V190" s="28"/>
+      <c r="V190" s="27"/>
     </row>
     <row r="191" spans="1:22">
       <c r="A191" s="10"/>
@@ -8937,13 +9294,13 @@
       <c r="C191" s="12"/>
       <c r="D191" s="12"/>
       <c r="E191" s="12"/>
-      <c r="F191" s="23"/>
-      <c r="G191" s="23"/>
+      <c r="F191" s="22"/>
+      <c r="G191" s="22"/>
       <c r="H191" s="11"/>
-      <c r="I191" s="26"/>
-      <c r="J191" s="26"/>
-      <c r="K191" s="26"/>
-      <c r="L191" s="26"/>
+      <c r="I191" s="25"/>
+      <c r="J191" s="25"/>
+      <c r="K191" s="25"/>
+      <c r="L191" s="25"/>
       <c r="M191" s="11"/>
       <c r="N191" s="11"/>
       <c r="O191" s="11"/>
@@ -8956,10 +9313,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S191" s="23"/>
-      <c r="T191" s="23"/>
+      <c r="S191" s="22"/>
+      <c r="T191" s="22"/>
       <c r="U191" s="7"/>
-      <c r="V191" s="28"/>
+      <c r="V191" s="27"/>
     </row>
     <row r="192" spans="1:22">
       <c r="A192" s="10"/>
@@ -8967,13 +9324,13 @@
       <c r="C192" s="12"/>
       <c r="D192" s="12"/>
       <c r="E192" s="12"/>
-      <c r="F192" s="23"/>
-      <c r="G192" s="23"/>
+      <c r="F192" s="22"/>
+      <c r="G192" s="22"/>
       <c r="H192" s="11"/>
-      <c r="I192" s="26"/>
-      <c r="J192" s="26"/>
-      <c r="K192" s="26"/>
-      <c r="L192" s="26"/>
+      <c r="I192" s="25"/>
+      <c r="J192" s="25"/>
+      <c r="K192" s="25"/>
+      <c r="L192" s="25"/>
       <c r="M192" s="11"/>
       <c r="N192" s="11"/>
       <c r="O192" s="11"/>
@@ -8986,10 +9343,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S192" s="23"/>
-      <c r="T192" s="23"/>
+      <c r="S192" s="22"/>
+      <c r="T192" s="22"/>
       <c r="U192" s="7"/>
-      <c r="V192" s="28"/>
+      <c r="V192" s="27"/>
     </row>
     <row r="193" spans="1:22">
       <c r="A193" s="10"/>
@@ -8997,13 +9354,13 @@
       <c r="C193" s="12"/>
       <c r="D193" s="12"/>
       <c r="E193" s="12"/>
-      <c r="F193" s="23"/>
-      <c r="G193" s="23"/>
+      <c r="F193" s="22"/>
+      <c r="G193" s="22"/>
       <c r="H193" s="11"/>
-      <c r="I193" s="26"/>
-      <c r="J193" s="26"/>
-      <c r="K193" s="26"/>
-      <c r="L193" s="26"/>
+      <c r="I193" s="25"/>
+      <c r="J193" s="25"/>
+      <c r="K193" s="25"/>
+      <c r="L193" s="25"/>
       <c r="M193" s="11"/>
       <c r="N193" s="11"/>
       <c r="O193" s="11"/>
@@ -9016,10 +9373,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S193" s="23"/>
-      <c r="T193" s="23"/>
+      <c r="S193" s="22"/>
+      <c r="T193" s="22"/>
       <c r="U193" s="7"/>
-      <c r="V193" s="28"/>
+      <c r="V193" s="27"/>
     </row>
     <row r="194" spans="1:22">
       <c r="A194" s="10"/>
@@ -9027,13 +9384,13 @@
       <c r="C194" s="12"/>
       <c r="D194" s="12"/>
       <c r="E194" s="12"/>
-      <c r="F194" s="23"/>
-      <c r="G194" s="23"/>
+      <c r="F194" s="22"/>
+      <c r="G194" s="22"/>
       <c r="H194" s="11"/>
-      <c r="I194" s="26"/>
-      <c r="J194" s="26"/>
-      <c r="K194" s="26"/>
-      <c r="L194" s="26"/>
+      <c r="I194" s="25"/>
+      <c r="J194" s="25"/>
+      <c r="K194" s="25"/>
+      <c r="L194" s="25"/>
       <c r="M194" s="11"/>
       <c r="N194" s="11"/>
       <c r="O194" s="11"/>
@@ -9046,10 +9403,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S194" s="23"/>
-      <c r="T194" s="23"/>
+      <c r="S194" s="22"/>
+      <c r="T194" s="22"/>
       <c r="U194" s="7"/>
-      <c r="V194" s="28"/>
+      <c r="V194" s="27"/>
     </row>
     <row r="195" spans="1:22">
       <c r="A195" s="10"/>
@@ -9057,13 +9414,13 @@
       <c r="C195" s="12"/>
       <c r="D195" s="12"/>
       <c r="E195" s="12"/>
-      <c r="F195" s="23"/>
-      <c r="G195" s="23"/>
+      <c r="F195" s="22"/>
+      <c r="G195" s="22"/>
       <c r="H195" s="11"/>
-      <c r="I195" s="26"/>
-      <c r="J195" s="26"/>
-      <c r="K195" s="26"/>
-      <c r="L195" s="26"/>
+      <c r="I195" s="25"/>
+      <c r="J195" s="25"/>
+      <c r="K195" s="25"/>
+      <c r="L195" s="25"/>
       <c r="M195" s="11"/>
       <c r="N195" s="11"/>
       <c r="O195" s="11"/>
@@ -9076,10 +9433,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S195" s="23"/>
-      <c r="T195" s="23"/>
+      <c r="S195" s="22"/>
+      <c r="T195" s="22"/>
       <c r="U195" s="7"/>
-      <c r="V195" s="28"/>
+      <c r="V195" s="27"/>
     </row>
     <row r="196" spans="1:22">
       <c r="A196" s="10"/>
@@ -9087,13 +9444,13 @@
       <c r="C196" s="12"/>
       <c r="D196" s="12"/>
       <c r="E196" s="12"/>
-      <c r="F196" s="23"/>
-      <c r="G196" s="23"/>
+      <c r="F196" s="22"/>
+      <c r="G196" s="22"/>
       <c r="H196" s="11"/>
-      <c r="I196" s="26"/>
-      <c r="J196" s="26"/>
-      <c r="K196" s="26"/>
-      <c r="L196" s="26"/>
+      <c r="I196" s="25"/>
+      <c r="J196" s="25"/>
+      <c r="K196" s="25"/>
+      <c r="L196" s="25"/>
       <c r="M196" s="11"/>
       <c r="N196" s="11"/>
       <c r="O196" s="11"/>
@@ -9106,10 +9463,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S196" s="23"/>
-      <c r="T196" s="23"/>
+      <c r="S196" s="22"/>
+      <c r="T196" s="22"/>
       <c r="U196" s="7"/>
-      <c r="V196" s="28"/>
+      <c r="V196" s="27"/>
     </row>
     <row r="197" spans="1:22">
       <c r="A197" s="10"/>
@@ -9117,13 +9474,13 @@
       <c r="C197" s="12"/>
       <c r="D197" s="12"/>
       <c r="E197" s="12"/>
-      <c r="F197" s="23"/>
-      <c r="G197" s="23"/>
+      <c r="F197" s="22"/>
+      <c r="G197" s="22"/>
       <c r="H197" s="11"/>
-      <c r="I197" s="26"/>
-      <c r="J197" s="26"/>
-      <c r="K197" s="26"/>
-      <c r="L197" s="26"/>
+      <c r="I197" s="25"/>
+      <c r="J197" s="25"/>
+      <c r="K197" s="25"/>
+      <c r="L197" s="25"/>
       <c r="M197" s="11"/>
       <c r="N197" s="11"/>
       <c r="O197" s="11"/>
@@ -9136,10 +9493,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S197" s="23"/>
-      <c r="T197" s="23"/>
+      <c r="S197" s="22"/>
+      <c r="T197" s="22"/>
       <c r="U197" s="7"/>
-      <c r="V197" s="28"/>
+      <c r="V197" s="27"/>
     </row>
     <row r="198" spans="1:22">
       <c r="A198" s="10"/>
@@ -9147,13 +9504,13 @@
       <c r="C198" s="12"/>
       <c r="D198" s="12"/>
       <c r="E198" s="12"/>
-      <c r="F198" s="23"/>
-      <c r="G198" s="23"/>
+      <c r="F198" s="22"/>
+      <c r="G198" s="22"/>
       <c r="H198" s="11"/>
-      <c r="I198" s="26"/>
-      <c r="J198" s="26"/>
-      <c r="K198" s="26"/>
-      <c r="L198" s="26"/>
+      <c r="I198" s="25"/>
+      <c r="J198" s="25"/>
+      <c r="K198" s="25"/>
+      <c r="L198" s="25"/>
       <c r="M198" s="11"/>
       <c r="N198" s="11"/>
       <c r="O198" s="11"/>
@@ -9166,10 +9523,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S198" s="23"/>
-      <c r="T198" s="23"/>
+      <c r="S198" s="22"/>
+      <c r="T198" s="22"/>
       <c r="U198" s="7"/>
-      <c r="V198" s="28"/>
+      <c r="V198" s="27"/>
     </row>
     <row r="199" spans="1:22">
       <c r="A199" s="10"/>
@@ -9177,13 +9534,13 @@
       <c r="C199" s="12"/>
       <c r="D199" s="12"/>
       <c r="E199" s="12"/>
-      <c r="F199" s="23"/>
-      <c r="G199" s="23"/>
+      <c r="F199" s="22"/>
+      <c r="G199" s="22"/>
       <c r="H199" s="11"/>
-      <c r="I199" s="26"/>
-      <c r="J199" s="26"/>
-      <c r="K199" s="26"/>
-      <c r="L199" s="26"/>
+      <c r="I199" s="25"/>
+      <c r="J199" s="25"/>
+      <c r="K199" s="25"/>
+      <c r="L199" s="25"/>
       <c r="M199" s="11"/>
       <c r="N199" s="11"/>
       <c r="O199" s="11"/>
@@ -9196,10 +9553,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S199" s="23"/>
-      <c r="T199" s="23"/>
+      <c r="S199" s="22"/>
+      <c r="T199" s="22"/>
       <c r="U199" s="7"/>
-      <c r="V199" s="28"/>
+      <c r="V199" s="27"/>
     </row>
     <row r="200" spans="1:22">
       <c r="A200" s="10"/>
@@ -9207,13 +9564,13 @@
       <c r="C200" s="12"/>
       <c r="D200" s="12"/>
       <c r="E200" s="12"/>
-      <c r="F200" s="23"/>
-      <c r="G200" s="23"/>
+      <c r="F200" s="22"/>
+      <c r="G200" s="22"/>
       <c r="H200" s="11"/>
-      <c r="I200" s="26"/>
-      <c r="J200" s="26"/>
-      <c r="K200" s="26"/>
-      <c r="L200" s="26"/>
+      <c r="I200" s="25"/>
+      <c r="J200" s="25"/>
+      <c r="K200" s="25"/>
+      <c r="L200" s="25"/>
       <c r="M200" s="11"/>
       <c r="N200" s="11"/>
       <c r="O200" s="11"/>
@@ -9226,10 +9583,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S200" s="23"/>
-      <c r="T200" s="23"/>
+      <c r="S200" s="22"/>
+      <c r="T200" s="22"/>
       <c r="U200" s="7"/>
-      <c r="V200" s="28"/>
+      <c r="V200" s="27"/>
     </row>
     <row r="201" spans="1:22">
       <c r="A201" s="10"/>
@@ -9237,13 +9594,13 @@
       <c r="C201" s="12"/>
       <c r="D201" s="12"/>
       <c r="E201" s="12"/>
-      <c r="F201" s="23"/>
-      <c r="G201" s="23"/>
+      <c r="F201" s="22"/>
+      <c r="G201" s="22"/>
       <c r="H201" s="11"/>
-      <c r="I201" s="26"/>
-      <c r="J201" s="26"/>
-      <c r="K201" s="26"/>
-      <c r="L201" s="26"/>
+      <c r="I201" s="25"/>
+      <c r="J201" s="25"/>
+      <c r="K201" s="25"/>
+      <c r="L201" s="25"/>
       <c r="M201" s="11"/>
       <c r="N201" s="11"/>
       <c r="O201" s="11"/>
@@ -9256,10 +9613,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S201" s="23"/>
-      <c r="T201" s="23"/>
+      <c r="S201" s="22"/>
+      <c r="T201" s="22"/>
       <c r="U201" s="7"/>
-      <c r="V201" s="28"/>
+      <c r="V201" s="27"/>
     </row>
     <row r="202" spans="1:22">
       <c r="A202" s="10"/>
@@ -9267,13 +9624,13 @@
       <c r="C202" s="12"/>
       <c r="D202" s="12"/>
       <c r="E202" s="12"/>
-      <c r="F202" s="23"/>
-      <c r="G202" s="23"/>
+      <c r="F202" s="22"/>
+      <c r="G202" s="22"/>
       <c r="H202" s="11"/>
-      <c r="I202" s="26"/>
-      <c r="J202" s="26"/>
-      <c r="K202" s="26"/>
-      <c r="L202" s="26"/>
+      <c r="I202" s="25"/>
+      <c r="J202" s="25"/>
+      <c r="K202" s="25"/>
+      <c r="L202" s="25"/>
       <c r="M202" s="11"/>
       <c r="N202" s="11"/>
       <c r="O202" s="11"/>
@@ -9286,10 +9643,10 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="S202" s="23"/>
-      <c r="T202" s="23"/>
+      <c r="S202" s="22"/>
+      <c r="T202" s="22"/>
       <c r="U202" s="7"/>
-      <c r="V202" s="28"/>
+      <c r="V202" s="27"/>
     </row>
     <row r="203" spans="1:22">
       <c r="A203" s="10"/>
@@ -9297,13 +9654,13 @@
       <c r="C203" s="12"/>
       <c r="D203" s="12"/>
       <c r="E203" s="12"/>
-      <c r="F203" s="23"/>
-      <c r="G203" s="23"/>
+      <c r="F203" s="22"/>
+      <c r="G203" s="22"/>
       <c r="H203" s="11"/>
-      <c r="I203" s="26"/>
-      <c r="J203" s="26"/>
-      <c r="K203" s="26"/>
-      <c r="L203" s="26"/>
+      <c r="I203" s="25"/>
+      <c r="J203" s="25"/>
+      <c r="K203" s="25"/>
+      <c r="L203" s="25"/>
       <c r="M203" s="11"/>
       <c r="N203" s="11"/>
       <c r="O203" s="11"/>
@@ -9316,10 +9673,10 @@
         <f t="shared" ref="R203:R210" ca="1" si="13">IF(E203="","",TODAY()-E203)</f>
         <v/>
       </c>
-      <c r="S203" s="23"/>
-      <c r="T203" s="23"/>
+      <c r="S203" s="22"/>
+      <c r="T203" s="22"/>
       <c r="U203" s="7"/>
-      <c r="V203" s="28"/>
+      <c r="V203" s="27"/>
     </row>
     <row r="204" spans="1:22">
       <c r="A204" s="10"/>
@@ -9327,13 +9684,13 @@
       <c r="C204" s="12"/>
       <c r="D204" s="12"/>
       <c r="E204" s="12"/>
-      <c r="F204" s="23"/>
-      <c r="G204" s="23"/>
+      <c r="F204" s="22"/>
+      <c r="G204" s="22"/>
       <c r="H204" s="11"/>
-      <c r="I204" s="26"/>
-      <c r="J204" s="26"/>
-      <c r="K204" s="26"/>
-      <c r="L204" s="26"/>
+      <c r="I204" s="25"/>
+      <c r="J204" s="25"/>
+      <c r="K204" s="25"/>
+      <c r="L204" s="25"/>
       <c r="M204" s="11"/>
       <c r="N204" s="11"/>
       <c r="O204" s="11"/>
@@ -9346,10 +9703,10 @@
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="S204" s="23"/>
-      <c r="T204" s="23"/>
+      <c r="S204" s="22"/>
+      <c r="T204" s="22"/>
       <c r="U204" s="7"/>
-      <c r="V204" s="28"/>
+      <c r="V204" s="27"/>
     </row>
     <row r="205" spans="1:22">
       <c r="A205" s="10"/>
@@ -9357,13 +9714,13 @@
       <c r="C205" s="12"/>
       <c r="D205" s="12"/>
       <c r="E205" s="12"/>
-      <c r="F205" s="23"/>
-      <c r="G205" s="23"/>
+      <c r="F205" s="22"/>
+      <c r="G205" s="22"/>
       <c r="H205" s="11"/>
-      <c r="I205" s="26"/>
-      <c r="J205" s="26"/>
-      <c r="K205" s="26"/>
-      <c r="L205" s="26"/>
+      <c r="I205" s="25"/>
+      <c r="J205" s="25"/>
+      <c r="K205" s="25"/>
+      <c r="L205" s="25"/>
       <c r="M205" s="11"/>
       <c r="N205" s="11"/>
       <c r="O205" s="11"/>
@@ -9376,10 +9733,10 @@
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="S205" s="23"/>
-      <c r="T205" s="23"/>
+      <c r="S205" s="22"/>
+      <c r="T205" s="22"/>
       <c r="U205" s="7"/>
-      <c r="V205" s="28"/>
+      <c r="V205" s="27"/>
     </row>
     <row r="206" spans="1:22">
       <c r="A206" s="10"/>
@@ -9387,13 +9744,13 @@
       <c r="C206" s="12"/>
       <c r="D206" s="12"/>
       <c r="E206" s="12"/>
-      <c r="F206" s="23"/>
-      <c r="G206" s="23"/>
+      <c r="F206" s="22"/>
+      <c r="G206" s="22"/>
       <c r="H206" s="11"/>
-      <c r="I206" s="26"/>
-      <c r="J206" s="26"/>
-      <c r="K206" s="26"/>
-      <c r="L206" s="26"/>
+      <c r="I206" s="25"/>
+      <c r="J206" s="25"/>
+      <c r="K206" s="25"/>
+      <c r="L206" s="25"/>
       <c r="M206" s="11"/>
       <c r="N206" s="11"/>
       <c r="O206" s="11"/>
@@ -9406,10 +9763,10 @@
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="S206" s="23"/>
-      <c r="T206" s="23"/>
+      <c r="S206" s="22"/>
+      <c r="T206" s="22"/>
       <c r="U206" s="7"/>
-      <c r="V206" s="28"/>
+      <c r="V206" s="27"/>
     </row>
     <row r="207" spans="1:22">
       <c r="A207" s="10"/>
@@ -9417,13 +9774,13 @@
       <c r="C207" s="12"/>
       <c r="D207" s="12"/>
       <c r="E207" s="12"/>
-      <c r="F207" s="23"/>
-      <c r="G207" s="23"/>
+      <c r="F207" s="22"/>
+      <c r="G207" s="22"/>
       <c r="H207" s="11"/>
-      <c r="I207" s="26"/>
-      <c r="J207" s="26"/>
-      <c r="K207" s="26"/>
-      <c r="L207" s="26"/>
+      <c r="I207" s="25"/>
+      <c r="J207" s="25"/>
+      <c r="K207" s="25"/>
+      <c r="L207" s="25"/>
       <c r="M207" s="11"/>
       <c r="N207" s="11"/>
       <c r="O207" s="11"/>
@@ -9436,10 +9793,10 @@
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="S207" s="23"/>
-      <c r="T207" s="23"/>
+      <c r="S207" s="22"/>
+      <c r="T207" s="22"/>
       <c r="U207" s="7"/>
-      <c r="V207" s="28"/>
+      <c r="V207" s="27"/>
     </row>
     <row r="208" spans="1:22">
       <c r="A208" s="10"/>
@@ -9447,13 +9804,13 @@
       <c r="C208" s="12"/>
       <c r="D208" s="12"/>
       <c r="E208" s="12"/>
-      <c r="F208" s="23"/>
-      <c r="G208" s="23"/>
+      <c r="F208" s="22"/>
+      <c r="G208" s="22"/>
       <c r="H208" s="11"/>
-      <c r="I208" s="26"/>
-      <c r="J208" s="26"/>
-      <c r="K208" s="26"/>
-      <c r="L208" s="26"/>
+      <c r="I208" s="25"/>
+      <c r="J208" s="25"/>
+      <c r="K208" s="25"/>
+      <c r="L208" s="25"/>
       <c r="M208" s="11"/>
       <c r="N208" s="11"/>
       <c r="O208" s="11"/>
@@ -9466,10 +9823,10 @@
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="S208" s="23"/>
-      <c r="T208" s="23"/>
+      <c r="S208" s="22"/>
+      <c r="T208" s="22"/>
       <c r="U208" s="7"/>
-      <c r="V208" s="28"/>
+      <c r="V208" s="27"/>
     </row>
     <row r="209" spans="1:22">
       <c r="A209" s="10"/>
@@ -9477,13 +9834,13 @@
       <c r="C209" s="12"/>
       <c r="D209" s="12"/>
       <c r="E209" s="12"/>
-      <c r="F209" s="23"/>
-      <c r="G209" s="23"/>
+      <c r="F209" s="22"/>
+      <c r="G209" s="22"/>
       <c r="H209" s="11"/>
-      <c r="I209" s="26"/>
-      <c r="J209" s="26"/>
-      <c r="K209" s="26"/>
-      <c r="L209" s="26"/>
+      <c r="I209" s="25"/>
+      <c r="J209" s="25"/>
+      <c r="K209" s="25"/>
+      <c r="L209" s="25"/>
       <c r="M209" s="11"/>
       <c r="N209" s="11"/>
       <c r="O209" s="11"/>
@@ -9496,10 +9853,10 @@
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="S209" s="23"/>
-      <c r="T209" s="23"/>
+      <c r="S209" s="22"/>
+      <c r="T209" s="22"/>
       <c r="U209" s="7"/>
-      <c r="V209" s="28"/>
+      <c r="V209" s="27"/>
     </row>
     <row r="210" spans="1:22">
       <c r="A210" s="13"/>
@@ -9507,13 +9864,13 @@
       <c r="C210" s="15"/>
       <c r="D210" s="15"/>
       <c r="E210" s="15"/>
-      <c r="F210" s="24"/>
-      <c r="G210" s="24"/>
+      <c r="F210" s="23"/>
+      <c r="G210" s="23"/>
       <c r="H210" s="14"/>
-      <c r="I210" s="27"/>
-      <c r="J210" s="27"/>
-      <c r="K210" s="27"/>
-      <c r="L210" s="27"/>
+      <c r="I210" s="26"/>
+      <c r="J210" s="26"/>
+      <c r="K210" s="26"/>
+      <c r="L210" s="26"/>
       <c r="M210" s="14"/>
       <c r="N210" s="14"/>
       <c r="O210" s="14"/>
@@ -9526,10 +9883,10 @@
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="S210" s="24"/>
-      <c r="T210" s="24"/>
+      <c r="S210" s="23"/>
+      <c r="T210" s="23"/>
       <c r="U210" s="8"/>
-      <c r="V210" s="29"/>
+      <c r="V210" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -9540,25 +9897,25 @@
     <mergeCell ref="A8:V8"/>
   </mergeCells>
   <conditionalFormatting sqref="P11:P210">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>P11="RECOMENDADA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="19" priority="2">
       <formula>P11="APROVADA - AGUARDANDO EXECUÇÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="18" priority="3">
       <formula>P11="EXECUTADA - EM MATURAÇÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="17" priority="4">
       <formula>P11="EXECUTADA - AVALIADA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="5">
+    <cfRule type="expression" dxfId="16" priority="5">
       <formula>P11="APROVADA - NÃO EXECUTADA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="6">
+    <cfRule type="expression" dxfId="15" priority="6">
       <formula>P11="REJEITADA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="14" priority="7">
       <formula>LEFT(P11,9)="BLOQUEADA"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9619,190 +9976,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="3" spans="1:8" ht="15">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="31" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="G4" s="29" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="30" t="s">
+      <c r="G5" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="G6" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="29" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="29" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="29" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="29" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="30" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="29" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="29" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="29" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="30" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="51"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="50"/>
     </row>
     <row r="19" spans="1:8" ht="29.25">
-      <c r="A19" s="33" t="s">
+      <c r="A19" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="33" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="29.25">
-      <c r="A20" s="35" t="s">
+      <c r="A20" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="35" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="29.25">
-      <c r="A21" s="35" t="s">
+      <c r="A21" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="36" t="s">
+      <c r="B21" s="35" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15">
-      <c r="A22" s="35" t="s">
+      <c r="A22" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="B22" s="36" t="s">
+      <c r="B22" s="35" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="29.25">
-      <c r="A23" s="35" t="s">
+      <c r="A23" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="35" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="29.25">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="38" t="s">
+      <c r="B24" s="37" t="s">
         <v>76</v>
       </c>
     </row>
